--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -5318,7 +5318,7 @@
         <v>125</v>
       </c>
       <c r="C60" s="3">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="D60" s="3">
         <v>49.0</v>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="1079">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1972,7 +1972,7 @@
     <t>price_distr</t>
   </si>
   <si>
-    <t>ACTUALIZADO</t>
+    <t>ACTUALIZAR</t>
   </si>
   <si>
     <t>CAMBIAR REFERENCIA</t>
@@ -3044,6 +3044,15 @@
   </si>
   <si>
     <t>BY-BTM01G, BY-BCS02E, BY-RBC01</t>
+  </si>
+  <si>
+    <t>JW-DF20WB</t>
+  </si>
+  <si>
+    <t>BY-BCS03</t>
+  </si>
+  <si>
+    <t>BY-BHC01H</t>
   </si>
   <si>
     <t xml:space="preserve">  </t>
@@ -3793,7 +3802,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E404" displayName="Tabla_1" name="Tabla_1" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E405" displayName="Tabla_1" name="Tabla_1" id="2">
   <tableColumns count="5">
     <tableColumn name="platform_sku" id="1"/>
     <tableColumn name="excel_sku" id="2"/>
@@ -10277,22 +10286,22 @@
       <c r="E51" s="16"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>706</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
+      <c r="A52" s="11">
+        <v>6.15402845588E11</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="28" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C53" s="29"/>
       <c r="D53" s="29"/>
@@ -10300,10 +10309,10 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="28" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>396</v>
+        <v>272</v>
       </c>
       <c r="C54" s="29"/>
       <c r="D54" s="29"/>
@@ -10311,10 +10320,10 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="28" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B55" s="28" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C55" s="29"/>
       <c r="D55" s="29"/>
@@ -10322,10 +10331,10 @@
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="28" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C56" s="29"/>
       <c r="D56" s="29"/>
@@ -10333,10 +10342,10 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="28" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C57" s="29"/>
       <c r="D57" s="29"/>
@@ -10344,10 +10353,10 @@
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="28" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C58" s="29"/>
       <c r="D58" s="29"/>
@@ -10355,10 +10364,10 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="28" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C59" s="29"/>
       <c r="D59" s="29"/>
@@ -10366,32 +10375,32 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="28" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+        <v>408</v>
+      </c>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
+        <v>24</v>
+      </c>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="28" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -10399,10 +10408,10 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="28" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C63" s="29"/>
       <c r="D63" s="29"/>
@@ -10410,10 +10419,10 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="28" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C64" s="29"/>
       <c r="D64" s="29"/>
@@ -10421,10 +10430,10 @@
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="28" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C65" s="29"/>
       <c r="D65" s="29"/>
@@ -10432,10 +10441,10 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="28" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C66" s="29"/>
       <c r="D66" s="29"/>
@@ -10443,10 +10452,10 @@
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="28" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C67" s="29"/>
       <c r="D67" s="29"/>
@@ -10454,10 +10463,10 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="28" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>723</v>
+        <v>40</v>
       </c>
       <c r="C68" s="29"/>
       <c r="D68" s="29"/>
@@ -10465,10 +10474,10 @@
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="28" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>46</v>
+        <v>723</v>
       </c>
       <c r="C69" s="29"/>
       <c r="D69" s="29"/>
@@ -10476,10 +10485,10 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="28" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C70" s="29"/>
       <c r="D70" s="29"/>
@@ -10487,10 +10496,10 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="28" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C71" s="29"/>
       <c r="D71" s="29"/>
@@ -10498,10 +10507,10 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="28" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C72" s="29"/>
       <c r="D72" s="29"/>
@@ -10509,10 +10518,10 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="28" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C73" s="29"/>
       <c r="D73" s="29"/>
@@ -10520,10 +10529,10 @@
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="28" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C74" s="29"/>
       <c r="D74" s="29"/>
@@ -10531,10 +10540,10 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="28" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C75" s="29"/>
       <c r="D75" s="29"/>
@@ -10542,10 +10551,10 @@
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="28" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C76" s="29"/>
       <c r="D76" s="29"/>
@@ -10553,10 +10562,10 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="28" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C77" s="29"/>
       <c r="D77" s="29"/>
@@ -10564,10 +10573,10 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="28" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C78" s="29"/>
       <c r="D78" s="29"/>
@@ -10575,10 +10584,10 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="28" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B79" s="28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C79" s="29"/>
       <c r="D79" s="29"/>
@@ -10586,10 +10595,10 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="28" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C80" s="29"/>
       <c r="D80" s="29"/>
@@ -10597,31 +10606,29 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="28" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>723</v>
+        <v>40</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
       <c r="E81" s="29"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" s="31" t="s">
-        <v>737</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>698</v>
-      </c>
-      <c r="C82" s="32"/>
-      <c r="D82" s="32"/>
-      <c r="E82" s="32" t="s">
-        <v>738</v>
-      </c>
+      <c r="A82" s="28" t="s">
+        <v>736</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>723</v>
+      </c>
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="31" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B83" s="31" t="s">
         <v>698</v>
@@ -10634,10 +10641,10 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="31" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C84" s="32"/>
       <c r="D84" s="32"/>
@@ -10646,22 +10653,24 @@
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="28" t="s">
-        <v>741</v>
-      </c>
-      <c r="B85" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
+      <c r="A85" s="31" t="s">
+        <v>740</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>703</v>
+      </c>
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32" t="s">
+        <v>738</v>
+      </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="28" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C86" s="29"/>
       <c r="D86" s="29"/>
@@ -10669,10 +10678,10 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="28" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C87" s="29"/>
       <c r="D87" s="29"/>
@@ -10680,10 +10689,10 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="28" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="C88" s="29"/>
       <c r="D88" s="29"/>
@@ -10691,10 +10700,10 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="28" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C89" s="29"/>
       <c r="D89" s="29"/>
@@ -10702,10 +10711,10 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="28" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C90" s="29"/>
       <c r="D90" s="29"/>
@@ -10713,10 +10722,10 @@
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="28" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C91" s="29"/>
       <c r="D91" s="29"/>
@@ -10724,10 +10733,10 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="28" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B92" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C92" s="29"/>
       <c r="D92" s="29"/>
@@ -10735,10 +10744,10 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="28" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B93" s="28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C93" s="29"/>
       <c r="D93" s="29"/>
@@ -10746,10 +10755,10 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="28" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B94" s="28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C94" s="29"/>
       <c r="D94" s="29"/>
@@ -10757,10 +10766,10 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="28" t="s">
-        <v>751</v>
-      </c>
-      <c r="B95" s="33" t="s">
-        <v>66</v>
+        <v>750</v>
+      </c>
+      <c r="B95" s="28" t="s">
+        <v>76</v>
       </c>
       <c r="C95" s="29"/>
       <c r="D95" s="29"/>
@@ -10768,10 +10777,10 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="28" t="s">
-        <v>752</v>
-      </c>
-      <c r="B96" s="34" t="s">
-        <v>68</v>
+        <v>751</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>66</v>
       </c>
       <c r="C96" s="29"/>
       <c r="D96" s="29"/>
@@ -10779,10 +10788,10 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="28" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C97" s="29"/>
       <c r="D97" s="29"/>
@@ -10790,10 +10799,10 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="28" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B98" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C98" s="29"/>
       <c r="D98" s="29"/>
@@ -10801,10 +10810,10 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="28" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B99" s="34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C99" s="29"/>
       <c r="D99" s="29"/>
@@ -10812,10 +10821,10 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="28" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C100" s="29"/>
       <c r="D100" s="29"/>
@@ -10823,10 +10832,10 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="28" t="s">
-        <v>757</v>
-      </c>
-      <c r="B101" s="28" t="s">
-        <v>78</v>
+        <v>756</v>
+      </c>
+      <c r="B101" s="34" t="s">
+        <v>76</v>
       </c>
       <c r="C101" s="29"/>
       <c r="D101" s="29"/>
@@ -10834,10 +10843,10 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="28" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B102" s="28" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C102" s="29"/>
       <c r="D102" s="29"/>
@@ -10845,10 +10854,10 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="28" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B103" s="28" t="s">
-        <v>760</v>
+        <v>86</v>
       </c>
       <c r="C103" s="29"/>
       <c r="D103" s="29"/>
@@ -10856,10 +10865,10 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="28" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B104" s="28" t="s">
-        <v>98</v>
+        <v>760</v>
       </c>
       <c r="C104" s="29"/>
       <c r="D104" s="29"/>
@@ -10867,10 +10876,10 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="28" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C105" s="29"/>
       <c r="D105" s="29"/>
@@ -10878,10 +10887,10 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="28" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="C106" s="29"/>
       <c r="D106" s="29"/>
@@ -10889,10 +10898,10 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="28" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C107" s="29"/>
       <c r="D107" s="29"/>
@@ -10900,7 +10909,7 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="28" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B108" s="28" t="s">
         <v>150</v>
@@ -10911,34 +10920,32 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B109" s="28" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C109" s="29"/>
       <c r="D109" s="29"/>
       <c r="E109" s="29"/>
     </row>
     <row r="110" ht="22.5" customHeight="1">
-      <c r="A110" s="31" t="s">
-        <v>767</v>
-      </c>
-      <c r="B110" s="35" t="s">
-        <v>768</v>
-      </c>
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="32" t="s">
-        <v>769</v>
-      </c>
+      <c r="A110" s="28" t="s">
+        <v>766</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C110" s="29"/>
+      <c r="D110" s="29"/>
+      <c r="E110" s="29"/>
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="31" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B111" s="35" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C111" s="36"/>
       <c r="D111" s="36"/>
@@ -10948,10 +10955,10 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="31" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B112" s="35" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C112" s="36"/>
       <c r="D112" s="36"/>
@@ -10961,23 +10968,23 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="31" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B113" s="35" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C113" s="36"/>
       <c r="D113" s="36"/>
       <c r="E113" s="32" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="31" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B114" s="35" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C114" s="36"/>
       <c r="D114" s="36"/>
@@ -10987,10 +10994,10 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="31" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B115" s="35" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C115" s="36"/>
       <c r="D115" s="36"/>
@@ -11000,10 +11007,10 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="31" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B116" s="35" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C116" s="36"/>
       <c r="D116" s="36"/>
@@ -11013,7 +11020,7 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="31" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B117" s="35" t="s">
         <v>782</v>
@@ -11026,10 +11033,10 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="31" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B118" s="35" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C118" s="36"/>
       <c r="D118" s="36"/>
@@ -11038,22 +11045,24 @@
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
-      <c r="A119" s="28" t="s">
-        <v>785</v>
-      </c>
-      <c r="B119" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="C119" s="29"/>
-      <c r="D119" s="29"/>
-      <c r="E119" s="29"/>
+      <c r="A119" s="31" t="s">
+        <v>784</v>
+      </c>
+      <c r="B119" s="35" t="s">
+        <v>780</v>
+      </c>
+      <c r="C119" s="36"/>
+      <c r="D119" s="36"/>
+      <c r="E119" s="32" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="28" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C120" s="29"/>
       <c r="D120" s="29"/>
@@ -11061,10 +11070,10 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="28" t="s">
-        <v>787</v>
-      </c>
-      <c r="B121" s="33" t="s">
-        <v>78</v>
+        <v>786</v>
+      </c>
+      <c r="B121" s="28" t="s">
+        <v>152</v>
       </c>
       <c r="C121" s="29"/>
       <c r="D121" s="29"/>
@@ -11072,10 +11081,10 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="28" t="s">
-        <v>788</v>
-      </c>
-      <c r="B122" s="28" t="s">
-        <v>60</v>
+        <v>787</v>
+      </c>
+      <c r="B122" s="33" t="s">
+        <v>78</v>
       </c>
       <c r="C122" s="29"/>
       <c r="D122" s="29"/>
@@ -11083,10 +11092,10 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="28" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C123" s="29"/>
       <c r="D123" s="29"/>
@@ -11094,10 +11103,10 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="28" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B124" s="28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C124" s="29"/>
       <c r="D124" s="29"/>
@@ -11105,10 +11114,10 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="28" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C125" s="29"/>
       <c r="D125" s="29"/>
@@ -11116,10 +11125,10 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="28" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B126" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C126" s="29"/>
       <c r="D126" s="29"/>
@@ -11127,10 +11136,10 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="28" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C127" s="29"/>
       <c r="D127" s="29"/>
@@ -11138,10 +11147,10 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="28" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B128" s="28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C128" s="29"/>
       <c r="D128" s="29"/>
@@ -11149,10 +11158,10 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="28" t="s">
-        <v>795</v>
-      </c>
-      <c r="B129" s="33" t="s">
-        <v>78</v>
+        <v>794</v>
+      </c>
+      <c r="B129" s="28" t="s">
+        <v>76</v>
       </c>
       <c r="C129" s="29"/>
       <c r="D129" s="29"/>
@@ -11160,10 +11169,10 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="28" t="s">
-        <v>796</v>
-      </c>
-      <c r="B130" s="28" t="s">
-        <v>110</v>
+        <v>795</v>
+      </c>
+      <c r="B130" s="33" t="s">
+        <v>78</v>
       </c>
       <c r="C130" s="29"/>
       <c r="D130" s="29"/>
@@ -11171,10 +11180,10 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="28" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C131" s="29"/>
       <c r="D131" s="29"/>
@@ -11182,34 +11191,32 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="28" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B132" s="28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C132" s="29"/>
       <c r="D132" s="29"/>
       <c r="E132" s="29"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
-      <c r="A133" s="37" t="s">
-        <v>799</v>
-      </c>
-      <c r="B133" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="C133" s="38"/>
-      <c r="D133" s="38">
-        <v>2.0</v>
-      </c>
-      <c r="E133" s="38"/>
+      <c r="A133" s="28" t="s">
+        <v>798</v>
+      </c>
+      <c r="B133" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C133" s="29"/>
+      <c r="D133" s="29"/>
+      <c r="E133" s="29"/>
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="37" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B134" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C134" s="38"/>
       <c r="D134" s="38">
@@ -11218,22 +11225,24 @@
       <c r="E134" s="38"/>
     </row>
     <row r="135" ht="22.5" customHeight="1">
-      <c r="A135" s="28" t="s">
-        <v>801</v>
-      </c>
-      <c r="B135" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="C135" s="29"/>
-      <c r="D135" s="29"/>
-      <c r="E135" s="29"/>
+      <c r="A135" s="37" t="s">
+        <v>800</v>
+      </c>
+      <c r="B135" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="C135" s="38"/>
+      <c r="D135" s="38">
+        <v>2.0</v>
+      </c>
+      <c r="E135" s="38"/>
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="28" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B136" s="28" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C136" s="29"/>
       <c r="D136" s="29"/>
@@ -11241,10 +11250,10 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="28" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B137" s="28" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C137" s="29"/>
       <c r="D137" s="29"/>
@@ -11252,10 +11261,10 @@
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="28" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B138" s="28" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C138" s="29"/>
       <c r="D138" s="29"/>
@@ -11263,10 +11272,10 @@
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="28" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B139" s="28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C139" s="29"/>
       <c r="D139" s="29"/>
@@ -11274,29 +11283,29 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="28" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B140" s="28" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C140" s="29"/>
       <c r="D140" s="29"/>
       <c r="E140" s="29"/>
     </row>
     <row r="141" ht="22.5" customHeight="1">
-      <c r="A141" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="B141" s="40"/>
-      <c r="C141" s="41"/>
-      <c r="D141" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="E141" s="41"/>
+      <c r="A141" s="28" t="s">
+        <v>806</v>
+      </c>
+      <c r="B141" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="C141" s="29"/>
+      <c r="D141" s="29"/>
+      <c r="E141" s="29"/>
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="39" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B142" s="40"/>
       <c r="C142" s="41"/>
@@ -11307,7 +11316,7 @@
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B143" s="40"/>
       <c r="C143" s="41"/>
@@ -11318,7 +11327,7 @@
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B144" s="40"/>
       <c r="C144" s="41"/>
@@ -11329,7 +11338,7 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="39" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B145" s="40"/>
       <c r="C145" s="41"/>
@@ -11340,7 +11349,7 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B146" s="40"/>
       <c r="C146" s="41"/>
@@ -11350,19 +11359,19 @@
       <c r="E146" s="41"/>
     </row>
     <row r="147" ht="22.5" customHeight="1">
-      <c r="A147" s="42" t="s">
-        <v>807</v>
-      </c>
-      <c r="B147" s="43"/>
-      <c r="C147" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="D147" s="43"/>
-      <c r="E147" s="43"/>
+      <c r="A147" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="B147" s="40"/>
+      <c r="C147" s="41"/>
+      <c r="D147" s="41">
+        <v>2.0</v>
+      </c>
+      <c r="E147" s="41"/>
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="42" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B148" s="43"/>
       <c r="C148" s="44" t="s">
@@ -11373,7 +11382,7 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="42" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B149" s="43"/>
       <c r="C149" s="44" t="s">
@@ -11384,7 +11393,7 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="42" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B150" s="43"/>
       <c r="C150" s="44" t="s">
@@ -11395,18 +11404,18 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="42" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B151" s="43"/>
       <c r="C151" s="44" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D151" s="43"/>
       <c r="E151" s="43"/>
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="42" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B152" s="43"/>
       <c r="C152" s="44" t="s">
@@ -11417,7 +11426,7 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="42" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B153" s="43"/>
       <c r="C153" s="44" t="s">
@@ -11428,7 +11437,7 @@
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="42" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B154" s="43"/>
       <c r="C154" s="44" t="s">
@@ -11439,7 +11448,7 @@
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="42" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B155" s="43"/>
       <c r="C155" s="44" t="s">
@@ -11450,18 +11459,18 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="42" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B156" s="43"/>
       <c r="C156" s="44" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D156" s="43"/>
       <c r="E156" s="43"/>
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="42" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B157" s="43"/>
       <c r="C157" s="44" t="s">
@@ -11472,7 +11481,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="42" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B158" s="43"/>
       <c r="C158" s="44" t="s">
@@ -11483,7 +11492,7 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="42" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B159" s="43"/>
       <c r="C159" s="44" t="s">
@@ -11494,18 +11503,18 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="42" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B160" s="43"/>
       <c r="C160" s="44" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D160" s="43"/>
       <c r="E160" s="43"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="42" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B161" s="43"/>
       <c r="C161" s="44" t="s">
@@ -11516,7 +11525,7 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="42" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B162" s="43"/>
       <c r="C162" s="44" t="s">
@@ -11527,7 +11536,7 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="42" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B163" s="43"/>
       <c r="C163" s="44" t="s">
@@ -11538,7 +11547,7 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="42" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B164" s="43"/>
       <c r="C164" s="44" t="s">
@@ -11548,35 +11557,33 @@
       <c r="E164" s="43"/>
     </row>
     <row r="165" ht="22.5" customHeight="1">
-      <c r="A165" s="28" t="s">
+      <c r="A165" s="42" t="s">
+        <v>824</v>
+      </c>
+      <c r="B165" s="43"/>
+      <c r="C165" s="44" t="s">
+        <v>330</v>
+      </c>
+      <c r="D165" s="43"/>
+      <c r="E165" s="43"/>
+    </row>
+    <row r="166" ht="22.5" customHeight="1">
+      <c r="A166" s="28" t="s">
         <v>825</v>
       </c>
-      <c r="B165" s="28" t="s">
+      <c r="B166" s="28" t="s">
         <v>362</v>
       </c>
-      <c r="C165" s="29"/>
-      <c r="D165" s="29"/>
-      <c r="E165" s="29"/>
-    </row>
-    <row r="166" ht="22.5" customHeight="1">
-      <c r="A166" s="37" t="s">
-        <v>826</v>
-      </c>
-      <c r="B166" s="45" t="s">
-        <v>416</v>
-      </c>
-      <c r="C166" s="38"/>
-      <c r="D166" s="38">
-        <v>10.0</v>
-      </c>
-      <c r="E166" s="38"/>
+      <c r="C166" s="29"/>
+      <c r="D166" s="29"/>
+      <c r="E166" s="29"/>
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="37" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B167" s="45" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C167" s="38"/>
       <c r="D167" s="38">
@@ -11586,10 +11593,10 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="37" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B168" s="45" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="C168" s="38"/>
       <c r="D168" s="38">
@@ -11599,10 +11606,10 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="37" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B169" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C169" s="38"/>
       <c r="D169" s="38">
@@ -11612,23 +11619,23 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="37" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B170" s="45" t="s">
-        <v>416</v>
+        <v>477</v>
       </c>
       <c r="C170" s="38"/>
       <c r="D170" s="38">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E170" s="38"/>
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="37" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B171" s="45" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C171" s="38"/>
       <c r="D171" s="38">
@@ -11638,10 +11645,10 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="37" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B172" s="45" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="C172" s="38"/>
       <c r="D172" s="38">
@@ -11651,10 +11658,10 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="37" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B173" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C173" s="38"/>
       <c r="D173" s="38">
@@ -11664,23 +11671,23 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B174" s="45" t="s">
-        <v>835</v>
+        <v>477</v>
       </c>
       <c r="C174" s="38"/>
       <c r="D174" s="38">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="E174" s="38"/>
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B175" s="45" t="s">
-        <v>437</v>
+        <v>835</v>
       </c>
       <c r="C175" s="38"/>
       <c r="D175" s="38">
@@ -11690,10 +11697,10 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="37" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B176" s="45" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C176" s="38"/>
       <c r="D176" s="38">
@@ -11703,10 +11710,10 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="37" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B177" s="45" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C177" s="38"/>
       <c r="D177" s="38">
@@ -11716,10 +11723,10 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B178" s="45" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C178" s="38"/>
       <c r="D178" s="38">
@@ -11729,10 +11736,10 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B179" s="45" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C179" s="38"/>
       <c r="D179" s="38">
@@ -11742,10 +11749,10 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="37" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B180" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C180" s="38"/>
       <c r="D180" s="38">
@@ -11755,10 +11762,10 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="37" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B181" s="45" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C181" s="38"/>
       <c r="D181" s="38">
@@ -11768,23 +11775,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="37" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B182" s="45" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="C182" s="38"/>
       <c r="D182" s="38">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E182" s="38"/>
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="37" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B183" s="45" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C183" s="38"/>
       <c r="D183" s="38">
@@ -11794,10 +11801,10 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="37" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B184" s="45" t="s">
-        <v>835</v>
+        <v>424</v>
       </c>
       <c r="C184" s="38"/>
       <c r="D184" s="38">
@@ -11807,10 +11814,10 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="37" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B185" s="45" t="s">
-        <v>437</v>
+        <v>835</v>
       </c>
       <c r="C185" s="38"/>
       <c r="D185" s="38">
@@ -11820,10 +11827,10 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="37" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B186" s="45" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C186" s="38"/>
       <c r="D186" s="38">
@@ -11833,10 +11840,10 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="37" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B187" s="45" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C187" s="38"/>
       <c r="D187" s="38">
@@ -11846,10 +11853,10 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="37" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B188" s="45" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C188" s="38"/>
       <c r="D188" s="38">
@@ -11859,10 +11866,10 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="37" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B189" s="45" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C189" s="38"/>
       <c r="D189" s="38">
@@ -11872,10 +11879,10 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B190" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C190" s="38"/>
       <c r="D190" s="38">
@@ -11885,10 +11892,10 @@
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B191" s="45" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C191" s="38"/>
       <c r="D191" s="38">
@@ -11898,10 +11905,10 @@
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="37" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B192" s="45" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="C192" s="38"/>
       <c r="D192" s="38">
@@ -11911,10 +11918,10 @@
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="37" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B193" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C193" s="38"/>
       <c r="D193" s="38">
@@ -11924,23 +11931,23 @@
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="37" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B194" s="45" t="s">
-        <v>416</v>
+        <v>477</v>
       </c>
       <c r="C194" s="38"/>
       <c r="D194" s="38">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E194" s="38"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="37" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B195" s="45" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C195" s="38"/>
       <c r="D195" s="38">
@@ -11950,10 +11957,10 @@
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="37" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>835</v>
+        <v>424</v>
       </c>
       <c r="C196" s="38"/>
       <c r="D196" s="38">
@@ -11963,7 +11970,7 @@
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="37" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B197" s="45" t="s">
         <v>835</v>
@@ -11976,10 +11983,10 @@
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="37" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>439</v>
+        <v>835</v>
       </c>
       <c r="C198" s="38"/>
       <c r="D198" s="38">
@@ -11989,10 +11996,10 @@
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C199" s="38"/>
       <c r="D199" s="38">
@@ -12002,10 +12009,10 @@
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B200" s="45" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C200" s="38"/>
       <c r="D200" s="38">
@@ -12015,10 +12022,10 @@
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B201" s="45" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C201" s="38"/>
       <c r="D201" s="38">
@@ -12028,10 +12035,10 @@
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B202" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C202" s="38"/>
       <c r="D202" s="38">
@@ -12041,10 +12048,10 @@
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="37" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B203" s="45" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C203" s="38"/>
       <c r="D203" s="38">
@@ -12054,10 +12061,10 @@
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="37" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B204" s="45" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="C204" s="38"/>
       <c r="D204" s="38">
@@ -12067,10 +12074,10 @@
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="37" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B205" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C205" s="38"/>
       <c r="D205" s="38">
@@ -12080,23 +12087,23 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="37" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B206" s="45" t="s">
-        <v>835</v>
+        <v>477</v>
       </c>
       <c r="C206" s="38"/>
       <c r="D206" s="38">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E206" s="38"/>
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="37" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B207" s="45" t="s">
-        <v>437</v>
+        <v>835</v>
       </c>
       <c r="C207" s="38"/>
       <c r="D207" s="38">
@@ -12106,10 +12113,10 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="37" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B208" s="45" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C208" s="38"/>
       <c r="D208" s="38">
@@ -12119,10 +12126,10 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="37" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B209" s="45" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C209" s="38"/>
       <c r="D209" s="38">
@@ -12132,10 +12139,10 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="37" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B210" s="45" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C210" s="38"/>
       <c r="D210" s="38">
@@ -12145,10 +12152,10 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="37" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B211" s="45" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C211" s="38"/>
       <c r="D211" s="38">
@@ -12158,10 +12165,10 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="37" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B212" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C212" s="38"/>
       <c r="D212" s="38">
@@ -12171,10 +12178,10 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="37" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B213" s="45" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C213" s="38"/>
       <c r="D213" s="38">
@@ -12184,23 +12191,23 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="37" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B214" s="45" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="C214" s="38"/>
       <c r="D214" s="38">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E214" s="38"/>
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="37" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B215" s="45" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C215" s="38"/>
       <c r="D215" s="38">
@@ -12210,10 +12217,10 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="37" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B216" s="45" t="s">
-        <v>835</v>
+        <v>424</v>
       </c>
       <c r="C216" s="38"/>
       <c r="D216" s="38">
@@ -12223,10 +12230,10 @@
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="37" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B217" s="45" t="s">
-        <v>437</v>
+        <v>835</v>
       </c>
       <c r="C217" s="38"/>
       <c r="D217" s="38">
@@ -12236,10 +12243,10 @@
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="37" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B218" s="45" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C218" s="38"/>
       <c r="D218" s="38">
@@ -12249,10 +12256,10 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="37" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B219" s="45" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C219" s="38"/>
       <c r="D219" s="38">
@@ -12262,10 +12269,10 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="37" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B220" s="45" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C220" s="38"/>
       <c r="D220" s="38">
@@ -12275,10 +12282,10 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="37" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B221" s="45" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="C221" s="38"/>
       <c r="D221" s="38">
@@ -12288,10 +12295,10 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="37" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B222" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C222" s="38"/>
       <c r="D222" s="38">
@@ -12301,23 +12308,23 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="37" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B223" s="45" t="s">
-        <v>416</v>
+        <v>477</v>
       </c>
       <c r="C223" s="38"/>
       <c r="D223" s="38">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E223" s="38"/>
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="37" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B224" s="45" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C224" s="38"/>
       <c r="D224" s="38">
@@ -12327,10 +12334,10 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="37" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B225" s="45" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="C225" s="38"/>
       <c r="D225" s="38">
@@ -12340,10 +12347,10 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="37" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B226" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C226" s="38"/>
       <c r="D226" s="38">
@@ -12352,22 +12359,24 @@
       <c r="E226" s="38"/>
     </row>
     <row r="227" ht="22.5" customHeight="1">
-      <c r="A227" s="28" t="s">
+      <c r="A227" s="37" t="s">
+        <v>887</v>
+      </c>
+      <c r="B227" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="C227" s="38"/>
+      <c r="D227" s="38">
+        <v>8.0</v>
+      </c>
+      <c r="E227" s="38"/>
+    </row>
+    <row r="228" ht="22.5" customHeight="1">
+      <c r="A228" s="28" t="s">
         <v>888</v>
       </c>
-      <c r="B227" s="33" t="s">
+      <c r="B228" s="33" t="s">
         <v>416</v>
-      </c>
-      <c r="C227" s="30"/>
-      <c r="D227" s="30"/>
-      <c r="E227" s="30"/>
-    </row>
-    <row r="228" ht="22.5" customHeight="1">
-      <c r="A228" s="46" t="s">
-        <v>889</v>
-      </c>
-      <c r="B228" s="33" t="s">
-        <v>418</v>
       </c>
       <c r="C228" s="30"/>
       <c r="D228" s="30"/>
@@ -12375,10 +12384,10 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="46" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B229" s="33" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C229" s="30"/>
       <c r="D229" s="30"/>
@@ -12386,10 +12395,10 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="46" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B230" s="33" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C230" s="30"/>
       <c r="D230" s="30"/>
@@ -12397,10 +12406,10 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="46" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B231" s="33" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C231" s="30"/>
       <c r="D231" s="30"/>
@@ -12408,10 +12417,10 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="46" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B232" s="33" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C232" s="30"/>
       <c r="D232" s="30"/>
@@ -12419,10 +12428,10 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="46" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B233" s="33" t="s">
-        <v>835</v>
+        <v>430</v>
       </c>
       <c r="C233" s="30"/>
       <c r="D233" s="30"/>
@@ -12430,10 +12439,10 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="46" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B234" s="33" t="s">
-        <v>437</v>
+        <v>835</v>
       </c>
       <c r="C234" s="30"/>
       <c r="D234" s="30"/>
@@ -12441,10 +12450,10 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="46" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B235" s="33" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C235" s="30"/>
       <c r="D235" s="30"/>
@@ -12452,10 +12461,10 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="46" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B236" s="33" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C236" s="30"/>
       <c r="D236" s="30"/>
@@ -12463,10 +12472,10 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="46" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B237" s="33" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C237" s="30"/>
       <c r="D237" s="30"/>
@@ -12474,10 +12483,10 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="46" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B238" s="33" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C238" s="30"/>
       <c r="D238" s="30"/>
@@ -12485,10 +12494,10 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="46" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B239" s="33" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C239" s="30"/>
       <c r="D239" s="30"/>
@@ -12496,10 +12505,10 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="46" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B240" s="33" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C240" s="30"/>
       <c r="D240" s="30"/>
@@ -12507,10 +12516,10 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="46" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B241" s="33" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C241" s="30"/>
       <c r="D241" s="30"/>
@@ -12518,32 +12527,32 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="46" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B242" s="33" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C242" s="30"/>
       <c r="D242" s="30"/>
       <c r="E242" s="30"/>
     </row>
     <row r="243" ht="22.5" customHeight="1">
-      <c r="A243" s="28" t="s">
-        <v>904</v>
+      <c r="A243" s="46" t="s">
+        <v>903</v>
       </c>
       <c r="B243" s="33" t="s">
-        <v>603</v>
+        <v>461</v>
       </c>
       <c r="C243" s="30"/>
       <c r="D243" s="30"/>
       <c r="E243" s="30"/>
     </row>
     <row r="244" ht="22.5" customHeight="1">
-      <c r="A244" s="46" t="s">
-        <v>905</v>
+      <c r="A244" s="28" t="s">
+        <v>904</v>
       </c>
       <c r="B244" s="33" t="s">
-        <v>467</v>
+        <v>603</v>
       </c>
       <c r="C244" s="30"/>
       <c r="D244" s="30"/>
@@ -12551,10 +12560,10 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="46" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B245" s="33" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C245" s="30"/>
       <c r="D245" s="30"/>
@@ -12562,32 +12571,32 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="46" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B246" s="33" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C246" s="30"/>
       <c r="D246" s="30"/>
       <c r="E246" s="30"/>
     </row>
     <row r="247" ht="22.5" customHeight="1">
-      <c r="A247" s="28" t="s">
-        <v>908</v>
+      <c r="A247" s="46" t="s">
+        <v>907</v>
       </c>
       <c r="B247" s="33" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C247" s="30"/>
       <c r="D247" s="30"/>
       <c r="E247" s="30"/>
     </row>
     <row r="248" ht="22.5" customHeight="1">
-      <c r="A248" s="46" t="s">
-        <v>909</v>
+      <c r="A248" s="28" t="s">
+        <v>908</v>
       </c>
       <c r="B248" s="33" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C248" s="30"/>
       <c r="D248" s="30"/>
@@ -12595,10 +12604,10 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="46" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B249" s="33" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C249" s="30"/>
       <c r="D249" s="30"/>
@@ -12606,10 +12615,10 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="46" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B250" s="33" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C250" s="30"/>
       <c r="D250" s="30"/>
@@ -12617,1034 +12626,1034 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="46" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B251" s="33" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C251" s="30"/>
       <c r="D251" s="30"/>
       <c r="E251" s="30"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
-      <c r="A252" s="39" t="s">
+      <c r="A252" s="46" t="s">
+        <v>912</v>
+      </c>
+      <c r="B252" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="C252" s="30"/>
+      <c r="D252" s="30"/>
+      <c r="E252" s="30"/>
+    </row>
+    <row r="253" ht="22.5" customHeight="1">
+      <c r="A253" s="39" t="s">
         <v>533</v>
       </c>
-      <c r="B252" s="40"/>
-      <c r="C252" s="41"/>
-      <c r="D252" s="41">
+      <c r="B253" s="40"/>
+      <c r="C253" s="41"/>
+      <c r="D253" s="41">
         <v>4.0</v>
       </c>
-      <c r="E252" s="41"/>
-    </row>
-    <row r="253" ht="22.5" customHeight="1">
-      <c r="A253" s="37" t="s">
-        <v>913</v>
-      </c>
-      <c r="B253" s="45" t="s">
-        <v>533</v>
-      </c>
-      <c r="C253" s="38"/>
-      <c r="D253" s="38">
-        <v>12.0</v>
-      </c>
-      <c r="E253" s="38"/>
+      <c r="E253" s="41"/>
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="37" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B254" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C254" s="38"/>
       <c r="D254" s="38">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E254" s="38"/>
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="37" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B255" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C255" s="38"/>
       <c r="D255" s="38">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E255" s="38"/>
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="37" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B256" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C256" s="38"/>
       <c r="D256" s="38">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E256" s="38"/>
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="37" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B257" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C257" s="38"/>
       <c r="D257" s="38">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="E257" s="38"/>
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="37" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B258" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C258" s="38"/>
       <c r="D258" s="38">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="E258" s="38"/>
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="37" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B259" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C259" s="38"/>
       <c r="D259" s="38">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="E259" s="38"/>
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="37" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B260" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C260" s="38"/>
       <c r="D260" s="38">
-        <v>4.0</v>
+        <v>36.0</v>
       </c>
       <c r="E260" s="38"/>
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="37" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B261" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C261" s="38"/>
       <c r="D261" s="38">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="E261" s="38"/>
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="37" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B262" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C262" s="38"/>
       <c r="D262" s="38">
-        <v>44.0</v>
+        <v>40.0</v>
       </c>
       <c r="E262" s="38"/>
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="37" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B263" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C263" s="38"/>
       <c r="D263" s="38">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="E263" s="38"/>
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="37" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B264" s="45" t="s">
         <v>533</v>
       </c>
       <c r="C264" s="38"/>
       <c r="D264" s="38">
+        <v>48.0</v>
+      </c>
+      <c r="E264" s="38"/>
+    </row>
+    <row r="265" ht="22.5" customHeight="1">
+      <c r="A265" s="37" t="s">
+        <v>924</v>
+      </c>
+      <c r="B265" s="45" t="s">
+        <v>533</v>
+      </c>
+      <c r="C265" s="38"/>
+      <c r="D265" s="38">
         <v>8.0</v>
       </c>
-      <c r="E264" s="38"/>
-    </row>
-    <row r="265" ht="22.5" customHeight="1">
-      <c r="A265" s="39" t="s">
+      <c r="E265" s="38"/>
+    </row>
+    <row r="266" ht="22.5" customHeight="1">
+      <c r="A266" s="39" t="s">
         <v>535</v>
       </c>
-      <c r="B265" s="40"/>
-      <c r="C265" s="41"/>
-      <c r="D265" s="41">
+      <c r="B266" s="40"/>
+      <c r="C266" s="41"/>
+      <c r="D266" s="41">
         <v>4.0</v>
       </c>
-      <c r="E265" s="41"/>
-    </row>
-    <row r="266" ht="22.5" customHeight="1">
-      <c r="A266" s="37" t="s">
-        <v>925</v>
-      </c>
-      <c r="B266" s="45" t="s">
-        <v>535</v>
-      </c>
-      <c r="C266" s="38"/>
-      <c r="D266" s="38">
-        <v>12.0</v>
-      </c>
-      <c r="E266" s="38"/>
+      <c r="E266" s="41"/>
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B267" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C267" s="38"/>
       <c r="D267" s="38">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E267" s="38"/>
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="37" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B268" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C268" s="38"/>
       <c r="D268" s="38">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E268" s="38"/>
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="37" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B269" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C269" s="38"/>
       <c r="D269" s="38">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E269" s="38"/>
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="37" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B270" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C270" s="38"/>
       <c r="D270" s="38">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="E270" s="38"/>
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="37" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B271" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C271" s="38"/>
       <c r="D271" s="38">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="E271" s="38"/>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="37" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B272" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C272" s="38"/>
       <c r="D272" s="38">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="E272" s="38"/>
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="37" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B273" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C273" s="38"/>
       <c r="D273" s="38">
-        <v>4.0</v>
+        <v>36.0</v>
       </c>
       <c r="E273" s="38"/>
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="37" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B274" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C274" s="38"/>
       <c r="D274" s="38">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="E274" s="38"/>
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="37" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B275" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C275" s="38"/>
       <c r="D275" s="38">
-        <v>44.0</v>
+        <v>40.0</v>
       </c>
       <c r="E275" s="38"/>
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="37" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B276" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C276" s="38"/>
       <c r="D276" s="38">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="E276" s="38"/>
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="37" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B277" s="45" t="s">
         <v>535</v>
       </c>
       <c r="C277" s="38"/>
       <c r="D277" s="38">
+        <v>48.0</v>
+      </c>
+      <c r="E277" s="38"/>
+    </row>
+    <row r="278" ht="22.5" customHeight="1">
+      <c r="A278" s="37" t="s">
+        <v>936</v>
+      </c>
+      <c r="B278" s="45" t="s">
+        <v>535</v>
+      </c>
+      <c r="C278" s="38"/>
+      <c r="D278" s="38">
         <v>8.0</v>
       </c>
-      <c r="E277" s="38"/>
-    </row>
-    <row r="278" ht="22.5" customHeight="1">
-      <c r="A278" s="39" t="s">
+      <c r="E278" s="38"/>
+    </row>
+    <row r="279" ht="22.5" customHeight="1">
+      <c r="A279" s="39" t="s">
         <v>537</v>
       </c>
-      <c r="B278" s="40"/>
-      <c r="C278" s="41"/>
-      <c r="D278" s="41">
+      <c r="B279" s="40"/>
+      <c r="C279" s="41"/>
+      <c r="D279" s="41">
         <v>4.0</v>
       </c>
-      <c r="E278" s="41"/>
-    </row>
-    <row r="279" ht="22.5" customHeight="1">
-      <c r="A279" s="37" t="s">
-        <v>937</v>
-      </c>
-      <c r="B279" s="45" t="s">
-        <v>537</v>
-      </c>
-      <c r="C279" s="38"/>
-      <c r="D279" s="38">
-        <v>12.0</v>
-      </c>
-      <c r="E279" s="38"/>
+      <c r="E279" s="41"/>
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="37" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B280" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C280" s="38"/>
       <c r="D280" s="38">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E280" s="38"/>
     </row>
     <row r="281" ht="22.5" customHeight="1">
       <c r="A281" s="37" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B281" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C281" s="38"/>
       <c r="D281" s="38">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E281" s="38"/>
     </row>
     <row r="282" ht="22.5" customHeight="1">
       <c r="A282" s="37" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B282" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C282" s="38"/>
       <c r="D282" s="38">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E282" s="38"/>
     </row>
     <row r="283" ht="22.5" customHeight="1">
       <c r="A283" s="37" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B283" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C283" s="38"/>
       <c r="D283" s="38">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="E283" s="38"/>
     </row>
     <row r="284" ht="22.5" customHeight="1">
       <c r="A284" s="37" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B284" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C284" s="38"/>
       <c r="D284" s="38">
-        <v>36.0</v>
+        <v>28.0</v>
       </c>
       <c r="E284" s="38"/>
     </row>
     <row r="285" ht="22.5" customHeight="1">
       <c r="A285" s="37" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B285" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C285" s="38"/>
       <c r="D285" s="38">
-        <v>4.0</v>
+        <v>36.0</v>
       </c>
       <c r="E285" s="38"/>
     </row>
     <row r="286" ht="22.5" customHeight="1">
       <c r="A286" s="37" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B286" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C286" s="38"/>
       <c r="D286" s="38">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="E286" s="38"/>
     </row>
     <row r="287" ht="22.5" customHeight="1">
       <c r="A287" s="37" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B287" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C287" s="38"/>
       <c r="D287" s="38">
-        <v>32.0</v>
+        <v>40.0</v>
       </c>
       <c r="E287" s="38"/>
     </row>
     <row r="288" ht="22.5" customHeight="1">
       <c r="A288" s="37" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B288" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C288" s="38"/>
       <c r="D288" s="38">
-        <v>44.0</v>
+        <v>32.0</v>
       </c>
       <c r="E288" s="38"/>
     </row>
     <row r="289" ht="22.5" customHeight="1">
       <c r="A289" s="37" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B289" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C289" s="38"/>
       <c r="D289" s="38">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="E289" s="38"/>
     </row>
     <row r="290" ht="22.5" customHeight="1">
       <c r="A290" s="37" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B290" s="45" t="s">
         <v>537</v>
       </c>
       <c r="C290" s="38"/>
       <c r="D290" s="38">
+        <v>48.0</v>
+      </c>
+      <c r="E290" s="38"/>
+    </row>
+    <row r="291" ht="22.5" customHeight="1">
+      <c r="A291" s="37" t="s">
+        <v>948</v>
+      </c>
+      <c r="B291" s="45" t="s">
+        <v>537</v>
+      </c>
+      <c r="C291" s="38"/>
+      <c r="D291" s="38">
         <v>8.0</v>
       </c>
-      <c r="E290" s="38"/>
-    </row>
-    <row r="291" ht="22.5" customHeight="1">
-      <c r="A291" s="39" t="s">
+      <c r="E291" s="38"/>
+    </row>
+    <row r="292" ht="22.5" customHeight="1">
+      <c r="A292" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="B291" s="40"/>
-      <c r="C291" s="41"/>
-      <c r="D291" s="41">
+      <c r="B292" s="40"/>
+      <c r="C292" s="41"/>
+      <c r="D292" s="41">
         <v>4.0</v>
       </c>
-      <c r="E291" s="41"/>
-    </row>
-    <row r="292" ht="22.5" customHeight="1">
-      <c r="A292" s="37" t="s">
-        <v>949</v>
-      </c>
-      <c r="B292" s="45" t="s">
-        <v>539</v>
-      </c>
-      <c r="C292" s="38"/>
-      <c r="D292" s="38">
-        <v>12.0</v>
-      </c>
-      <c r="E292" s="38"/>
+      <c r="E292" s="41"/>
     </row>
     <row r="293" ht="22.5" customHeight="1">
       <c r="A293" s="37" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B293" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C293" s="38"/>
       <c r="D293" s="38">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E293" s="38"/>
     </row>
     <row r="294" ht="22.5" customHeight="1">
       <c r="A294" s="37" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B294" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C294" s="38"/>
       <c r="D294" s="38">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E294" s="38"/>
     </row>
     <row r="295" ht="22.5" customHeight="1">
       <c r="A295" s="37" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B295" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C295" s="38"/>
       <c r="D295" s="38">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E295" s="38"/>
     </row>
     <row r="296" ht="22.5" customHeight="1">
       <c r="A296" s="37" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B296" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C296" s="38"/>
       <c r="D296" s="38">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="E296" s="38"/>
     </row>
     <row r="297" ht="22.5" customHeight="1">
       <c r="A297" s="37" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B297" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C297" s="38"/>
       <c r="D297" s="38">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="E297" s="38"/>
     </row>
     <row r="298" ht="22.5" customHeight="1">
       <c r="A298" s="37" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B298" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C298" s="38"/>
       <c r="D298" s="38">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="E298" s="38"/>
     </row>
     <row r="299" ht="22.5" customHeight="1">
       <c r="A299" s="37" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B299" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C299" s="38"/>
       <c r="D299" s="38">
-        <v>4.0</v>
+        <v>36.0</v>
       </c>
       <c r="E299" s="38"/>
     </row>
     <row r="300" ht="22.5" customHeight="1">
       <c r="A300" s="37" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B300" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C300" s="38"/>
       <c r="D300" s="38">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="E300" s="38"/>
     </row>
     <row r="301" ht="22.5" customHeight="1">
       <c r="A301" s="37" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B301" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C301" s="38"/>
       <c r="D301" s="38">
-        <v>44.0</v>
+        <v>40.0</v>
       </c>
       <c r="E301" s="38"/>
     </row>
     <row r="302" ht="22.5" customHeight="1">
       <c r="A302" s="37" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B302" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C302" s="38"/>
       <c r="D302" s="38">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="E302" s="38"/>
     </row>
     <row r="303" ht="22.5" customHeight="1">
       <c r="A303" s="37" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B303" s="45" t="s">
         <v>539</v>
       </c>
       <c r="C303" s="38"/>
       <c r="D303" s="38">
+        <v>48.0</v>
+      </c>
+      <c r="E303" s="38"/>
+    </row>
+    <row r="304" ht="22.5" customHeight="1">
+      <c r="A304" s="37" t="s">
+        <v>960</v>
+      </c>
+      <c r="B304" s="45" t="s">
+        <v>539</v>
+      </c>
+      <c r="C304" s="38"/>
+      <c r="D304" s="38">
         <v>8.0</v>
       </c>
-      <c r="E303" s="38"/>
-    </row>
-    <row r="304" ht="22.5" customHeight="1">
-      <c r="A304" s="39" t="s">
+      <c r="E304" s="38"/>
+    </row>
+    <row r="305" ht="22.5" customHeight="1">
+      <c r="A305" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="B304" s="40"/>
-      <c r="C304" s="41"/>
-      <c r="D304" s="41">
+      <c r="B305" s="40"/>
+      <c r="C305" s="41"/>
+      <c r="D305" s="41">
         <v>4.0</v>
       </c>
-      <c r="E304" s="41"/>
-    </row>
-    <row r="305" ht="22.5" customHeight="1">
-      <c r="A305" s="37" t="s">
-        <v>961</v>
-      </c>
-      <c r="B305" s="45" t="s">
-        <v>541</v>
-      </c>
-      <c r="C305" s="38"/>
-      <c r="D305" s="38">
-        <v>12.0</v>
-      </c>
-      <c r="E305" s="38"/>
+      <c r="E305" s="41"/>
     </row>
     <row r="306" ht="22.5" customHeight="1">
       <c r="A306" s="37" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B306" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C306" s="38"/>
       <c r="D306" s="38">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E306" s="38"/>
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="37" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B307" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C307" s="38"/>
       <c r="D307" s="38">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E307" s="38"/>
     </row>
     <row r="308" ht="22.5" customHeight="1">
       <c r="A308" s="37" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B308" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C308" s="38"/>
       <c r="D308" s="38">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E308" s="38"/>
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="37" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B309" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C309" s="38"/>
       <c r="D309" s="38">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="E309" s="38"/>
     </row>
     <row r="310" ht="22.5" customHeight="1">
       <c r="A310" s="37" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B310" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C310" s="38"/>
       <c r="D310" s="38">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="E310" s="38"/>
     </row>
     <row r="311" ht="22.5" customHeight="1">
       <c r="A311" s="37" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B311" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C311" s="38"/>
       <c r="D311" s="38">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="E311" s="38"/>
     </row>
     <row r="312" ht="22.5" customHeight="1">
       <c r="A312" s="37" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B312" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C312" s="38"/>
       <c r="D312" s="38">
-        <v>4.0</v>
+        <v>36.0</v>
       </c>
       <c r="E312" s="38"/>
     </row>
     <row r="313" ht="22.5" customHeight="1">
       <c r="A313" s="37" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B313" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C313" s="38"/>
       <c r="D313" s="38">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="E313" s="38"/>
     </row>
     <row r="314" ht="22.5" customHeight="1">
       <c r="A314" s="37" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B314" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C314" s="38"/>
       <c r="D314" s="38">
-        <v>44.0</v>
+        <v>40.0</v>
       </c>
       <c r="E314" s="38"/>
     </row>
     <row r="315" ht="22.5" customHeight="1">
       <c r="A315" s="37" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B315" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C315" s="38"/>
       <c r="D315" s="38">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="E315" s="38"/>
     </row>
     <row r="316" ht="22.5" customHeight="1">
       <c r="A316" s="37" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B316" s="45" t="s">
         <v>541</v>
       </c>
       <c r="C316" s="38"/>
       <c r="D316" s="38">
+        <v>48.0</v>
+      </c>
+      <c r="E316" s="38"/>
+    </row>
+    <row r="317" ht="22.5" customHeight="1">
+      <c r="A317" s="37" t="s">
+        <v>972</v>
+      </c>
+      <c r="B317" s="45" t="s">
+        <v>541</v>
+      </c>
+      <c r="C317" s="38"/>
+      <c r="D317" s="38">
         <v>8.0</v>
       </c>
-      <c r="E316" s="38"/>
-    </row>
-    <row r="317" ht="22.5" customHeight="1">
-      <c r="A317" s="39" t="s">
+      <c r="E317" s="38"/>
+    </row>
+    <row r="318" ht="22.5" customHeight="1">
+      <c r="A318" s="39" t="s">
         <v>543</v>
       </c>
-      <c r="B317" s="40"/>
-      <c r="C317" s="41"/>
-      <c r="D317" s="41">
+      <c r="B318" s="40"/>
+      <c r="C318" s="41"/>
+      <c r="D318" s="41">
         <v>4.0</v>
       </c>
-      <c r="E317" s="41"/>
-    </row>
-    <row r="318" ht="22.5" customHeight="1">
-      <c r="A318" s="37" t="s">
-        <v>973</v>
-      </c>
-      <c r="B318" s="45" t="s">
-        <v>543</v>
-      </c>
-      <c r="C318" s="38"/>
-      <c r="D318" s="38">
-        <v>12.0</v>
-      </c>
-      <c r="E318" s="38"/>
+      <c r="E318" s="41"/>
     </row>
     <row r="319" ht="22.5" customHeight="1">
       <c r="A319" s="37" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B319" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C319" s="38"/>
       <c r="D319" s="38">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E319" s="38"/>
     </row>
     <row r="320" ht="22.5" customHeight="1">
       <c r="A320" s="37" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B320" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C320" s="38"/>
       <c r="D320" s="38">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E320" s="38"/>
     </row>
     <row r="321" ht="22.5" customHeight="1">
       <c r="A321" s="37" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B321" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C321" s="38"/>
       <c r="D321" s="38">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E321" s="38"/>
     </row>
     <row r="322" ht="22.5" customHeight="1">
       <c r="A322" s="37" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B322" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C322" s="38"/>
       <c r="D322" s="38">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="E322" s="38"/>
     </row>
     <row r="323" ht="22.5" customHeight="1">
       <c r="A323" s="37" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B323" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C323" s="38"/>
       <c r="D323" s="38">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="E323" s="38"/>
     </row>
     <row r="324" ht="22.5" customHeight="1">
       <c r="A324" s="37" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B324" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C324" s="38"/>
       <c r="D324" s="38">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="E324" s="38"/>
     </row>
     <row r="325" ht="22.5" customHeight="1">
       <c r="A325" s="37" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B325" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C325" s="38"/>
       <c r="D325" s="38">
-        <v>4.0</v>
+        <v>36.0</v>
       </c>
       <c r="E325" s="38"/>
     </row>
     <row r="326" ht="22.5" customHeight="1">
       <c r="A326" s="37" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B326" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C326" s="38"/>
       <c r="D326" s="38">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="E326" s="38"/>
     </row>
     <row r="327" ht="22.5" customHeight="1">
       <c r="A327" s="37" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B327" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C327" s="38"/>
       <c r="D327" s="38">
-        <v>44.0</v>
+        <v>40.0</v>
       </c>
       <c r="E327" s="38"/>
     </row>
     <row r="328" ht="22.5" customHeight="1">
       <c r="A328" s="37" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B328" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C328" s="38"/>
       <c r="D328" s="38">
-        <v>48.0</v>
+        <v>44.0</v>
       </c>
       <c r="E328" s="38"/>
     </row>
     <row r="329" ht="22.5" customHeight="1">
       <c r="A329" s="37" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B329" s="45" t="s">
         <v>543</v>
       </c>
       <c r="C329" s="38"/>
       <c r="D329" s="38">
+        <v>48.0</v>
+      </c>
+      <c r="E329" s="38"/>
+    </row>
+    <row r="330" ht="22.5" customHeight="1">
+      <c r="A330" s="37" t="s">
+        <v>984</v>
+      </c>
+      <c r="B330" s="45" t="s">
+        <v>543</v>
+      </c>
+      <c r="C330" s="38"/>
+      <c r="D330" s="38">
         <v>8.0</v>
       </c>
-      <c r="E329" s="38"/>
-    </row>
-    <row r="330" ht="22.5" customHeight="1">
-      <c r="A330" s="28" t="s">
-        <v>985</v>
-      </c>
-      <c r="B330" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C330" s="29"/>
-      <c r="D330" s="29"/>
-      <c r="E330" s="29"/>
+      <c r="E330" s="38"/>
     </row>
     <row r="331" ht="22.5" customHeight="1">
       <c r="A331" s="28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B331" s="28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C331" s="29"/>
       <c r="D331" s="29"/>
@@ -13652,10 +13661,10 @@
     </row>
     <row r="332" ht="22.5" customHeight="1">
       <c r="A332" s="28" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B332" s="28" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C332" s="29"/>
       <c r="D332" s="29"/>
@@ -13663,75 +13672,83 @@
     </row>
     <row r="333" ht="22.5" customHeight="1">
       <c r="A333" s="28" t="s">
-        <v>988</v>
-      </c>
-      <c r="B333" s="28"/>
-      <c r="C333" s="47" t="s">
-        <v>100</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="B333" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C333" s="29"/>
       <c r="D333" s="29"/>
       <c r="E333" s="29"/>
     </row>
     <row r="334" ht="22.5" customHeight="1">
       <c r="A334" s="28" t="s">
-        <v>989</v>
-      </c>
-      <c r="B334" s="28"/>
+        <v>988</v>
+      </c>
+      <c r="B334" s="28" t="s">
+        <v>100</v>
+      </c>
       <c r="C334" s="47" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D334" s="29"/>
       <c r="E334" s="29"/>
     </row>
     <row r="335" ht="22.5" customHeight="1">
       <c r="A335" s="28" t="s">
-        <v>990</v>
-      </c>
-      <c r="B335" s="28"/>
+        <v>989</v>
+      </c>
+      <c r="B335" s="28" t="s">
+        <v>106</v>
+      </c>
       <c r="C335" s="47" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D335" s="29"/>
       <c r="E335" s="29"/>
     </row>
     <row r="336" ht="22.5" customHeight="1">
       <c r="A336" s="28" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B336" s="28"/>
       <c r="C336" s="47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D336" s="29"/>
       <c r="E336" s="29"/>
     </row>
     <row r="337" ht="22.5" customHeight="1">
       <c r="A337" s="28" t="s">
-        <v>992</v>
-      </c>
-      <c r="B337" s="28"/>
+        <v>991</v>
+      </c>
+      <c r="B337" s="28" t="s">
+        <v>102</v>
+      </c>
       <c r="C337" s="47" t="s">
-        <v>993</v>
+        <v>102</v>
       </c>
       <c r="D337" s="29"/>
       <c r="E337" s="29"/>
     </row>
     <row r="338" ht="22.5" customHeight="1">
       <c r="A338" s="28" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B338" s="28"/>
       <c r="C338" s="47" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D338" s="29"/>
       <c r="E338" s="29"/>
     </row>
     <row r="339" ht="22.5" customHeight="1">
       <c r="A339" s="28" t="s">
-        <v>996</v>
-      </c>
-      <c r="B339" s="28"/>
+        <v>994</v>
+      </c>
+      <c r="B339" s="28" t="s">
+        <v>995</v>
+      </c>
       <c r="C339" s="47" t="s">
         <v>995</v>
       </c>
@@ -13740,133 +13757,139 @@
     </row>
     <row r="340" ht="22.5" customHeight="1">
       <c r="A340" s="28" t="s">
-        <v>997</v>
-      </c>
-      <c r="B340" s="28"/>
+        <v>996</v>
+      </c>
+      <c r="B340" s="28" t="s">
+        <v>995</v>
+      </c>
       <c r="C340" s="47" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="D340" s="29"/>
       <c r="E340" s="29"/>
     </row>
     <row r="341" ht="22.5" customHeight="1">
       <c r="A341" s="28" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B341" s="28"/>
       <c r="C341" s="47" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D341" s="29"/>
       <c r="E341" s="29"/>
     </row>
     <row r="342" ht="22.5" customHeight="1">
       <c r="A342" s="28" t="s">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="B342" s="28"/>
       <c r="C342" s="47" t="s">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D342" s="29"/>
       <c r="E342" s="29"/>
     </row>
     <row r="343" ht="22.5" customHeight="1">
       <c r="A343" s="28" t="s">
-        <v>989</v>
-      </c>
-      <c r="B343" s="28"/>
+        <v>988</v>
+      </c>
+      <c r="B343" s="28" t="s">
+        <v>100</v>
+      </c>
       <c r="C343" s="47" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D343" s="29"/>
       <c r="E343" s="29"/>
     </row>
     <row r="344" ht="22.5" customHeight="1">
       <c r="A344" s="28" t="s">
-        <v>990</v>
-      </c>
-      <c r="B344" s="28"/>
+        <v>989</v>
+      </c>
+      <c r="B344" s="28" t="s">
+        <v>106</v>
+      </c>
       <c r="C344" s="47" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D344" s="29"/>
       <c r="E344" s="29"/>
     </row>
     <row r="345" ht="22.5" customHeight="1">
-      <c r="A345" s="46" t="s">
-        <v>991</v>
+      <c r="A345" s="28" t="s">
+        <v>990</v>
       </c>
       <c r="B345" s="28"/>
       <c r="C345" s="47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D345" s="29"/>
       <c r="E345" s="29"/>
     </row>
     <row r="346" ht="22.5" customHeight="1">
-      <c r="A346" s="28" t="s">
+      <c r="A346" s="46" t="s">
+        <v>991</v>
+      </c>
+      <c r="B346" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C346" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D346" s="29"/>
+      <c r="E346" s="29"/>
+    </row>
+    <row r="347" ht="22.5" customHeight="1">
+      <c r="A347" s="28" t="s">
         <v>1001</v>
-      </c>
-      <c r="B346" s="48"/>
-      <c r="C346" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D346" s="50"/>
-      <c r="E346" s="50"/>
-    </row>
-    <row r="347" ht="22.5" customHeight="1">
-      <c r="A347" s="48" t="s">
-        <v>1002</v>
       </c>
       <c r="B347" s="48"/>
       <c r="C347" s="49" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D347" s="50"/>
       <c r="E347" s="50"/>
     </row>
     <row r="348" ht="22.5" customHeight="1">
       <c r="A348" s="48" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B348" s="48"/>
       <c r="C348" s="49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D348" s="50"/>
       <c r="E348" s="50"/>
     </row>
     <row r="349" ht="22.5" customHeight="1">
       <c r="A349" s="48" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B349" s="48"/>
       <c r="C349" s="49" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D349" s="50"/>
       <c r="E349" s="50"/>
     </row>
     <row r="350" ht="22.5" customHeight="1">
       <c r="A350" s="48" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B350" s="48" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C350" s="49"/>
+        <v>1004</v>
+      </c>
+      <c r="B350" s="48"/>
+      <c r="C350" s="49" t="s">
+        <v>100</v>
+      </c>
       <c r="D350" s="50"/>
-      <c r="E350" s="49" t="s">
-        <v>1007</v>
-      </c>
+      <c r="E350" s="50"/>
     </row>
     <row r="351" ht="22.5" customHeight="1">
       <c r="A351" s="48" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B351" s="48" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C351" s="49"/>
       <c r="D351" s="50"/>
@@ -13875,36 +13898,58 @@
       </c>
     </row>
     <row r="352" ht="22.5" customHeight="1">
-      <c r="A352" s="48"/>
-      <c r="B352" s="48"/>
+      <c r="A352" s="48" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B352" s="48" t="s">
+        <v>1009</v>
+      </c>
       <c r="C352" s="49"/>
       <c r="D352" s="50"/>
-      <c r="E352" s="50"/>
+      <c r="E352" s="49" t="s">
+        <v>1007</v>
+      </c>
     </row>
     <row r="353" ht="22.5" customHeight="1">
-      <c r="A353" s="48"/>
-      <c r="B353" s="48"/>
+      <c r="A353" s="48">
+        <v>6.15402845588E11</v>
+      </c>
+      <c r="B353" s="48" t="s">
+        <v>100</v>
+      </c>
       <c r="C353" s="49"/>
       <c r="D353" s="50"/>
       <c r="E353" s="50"/>
     </row>
     <row r="354" ht="22.5" customHeight="1">
-      <c r="A354" s="48"/>
-      <c r="B354" s="48"/>
+      <c r="A354" s="48" t="s">
+        <v>430</v>
+      </c>
+      <c r="B354" s="48" t="s">
+        <v>1010</v>
+      </c>
       <c r="C354" s="49"/>
       <c r="D354" s="50"/>
       <c r="E354" s="50"/>
     </row>
     <row r="355" ht="22.5" customHeight="1">
-      <c r="A355" s="48"/>
-      <c r="B355" s="48"/>
+      <c r="A355" s="48" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B355" s="48" t="s">
+        <v>16</v>
+      </c>
       <c r="C355" s="49"/>
       <c r="D355" s="50"/>
       <c r="E355" s="50"/>
     </row>
     <row r="356" ht="22.5" customHeight="1">
-      <c r="A356" s="48"/>
-      <c r="B356" s="48"/>
+      <c r="A356" s="48" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B356" s="48" t="s">
+        <v>36</v>
+      </c>
       <c r="C356" s="49"/>
       <c r="D356" s="50"/>
       <c r="E356" s="50"/>
@@ -14245,26 +14290,26 @@
       <c r="D404" s="50"/>
       <c r="E404" s="50"/>
     </row>
-    <row r="405">
-      <c r="A405" s="51"/>
-      <c r="B405" s="52"/>
-      <c r="C405" s="53"/>
-      <c r="D405" s="53"/>
-      <c r="E405" s="53"/>
+    <row r="405" ht="22.5" customHeight="1">
+      <c r="A405" s="48"/>
+      <c r="B405" s="48"/>
+      <c r="C405" s="49"/>
+      <c r="D405" s="50"/>
+      <c r="E405" s="50"/>
     </row>
     <row r="406">
       <c r="A406" s="51"/>
       <c r="B406" s="52"/>
-      <c r="C406" s="54" t="s">
-        <v>1010</v>
-      </c>
+      <c r="C406" s="53"/>
       <c r="D406" s="53"/>
       <c r="E406" s="53"/>
     </row>
     <row r="407">
       <c r="A407" s="51"/>
       <c r="B407" s="52"/>
-      <c r="C407" s="53"/>
+      <c r="C407" s="54" t="s">
+        <v>1013</v>
+      </c>
       <c r="D407" s="53"/>
       <c r="E407" s="53"/>
     </row>
@@ -18383,6 +18428,13 @@
       <c r="C995" s="53"/>
       <c r="D995" s="53"/>
       <c r="E995" s="53"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="51"/>
+      <c r="B996" s="52"/>
+      <c r="C996" s="53"/>
+      <c r="D996" s="53"/>
+      <c r="E996" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -18432,24 +18484,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="55" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="56" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B2" s="56" t="s">
         <v>762</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D2" s="57"/>
       <c r="E2" s="57"/>
@@ -18477,13 +18529,13 @@
     </row>
     <row r="3">
       <c r="A3" s="56" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>758</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D3" s="57"/>
       <c r="E3" s="57"/>
@@ -18511,275 +18563,275 @@
     </row>
     <row r="4">
       <c r="A4" s="58" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>737</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="58" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="58" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>740</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="58" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B7" s="58" t="s">
         <v>50</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="58" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>766</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="58" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B9" s="58" t="s">
         <v>772</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="58" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>770</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="58" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B11" s="58" t="s">
         <v>767</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="58" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>774</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="58" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B13" s="58" t="s">
         <v>777</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="58" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B14" s="58" t="s">
         <v>784</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="58" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>781</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B16" s="58" t="s">
         <v>791</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B17" s="58" t="s">
         <v>794</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B18" s="58" t="s">
         <v>788</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B19" s="58" t="s">
         <v>790</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B20" s="58" t="s">
         <v>792</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B21" s="58" t="s">
         <v>789</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="58" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B22" s="58" t="s">
         <v>793</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="58" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="58" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B24" s="58" t="s">
         <v>706</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="58" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="58" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B26" s="58" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C26" s="58" t="s">
         <v>1047</v>
-      </c>
-      <c r="B26" s="58" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="58" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B27" s="58" t="s">
         <v>707</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="59" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B28" s="60"/>
       <c r="C28" s="59" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D28" s="61"/>
       <c r="E28" s="61"/>
@@ -18807,11 +18859,11 @@
     </row>
     <row r="29">
       <c r="A29" s="62" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B29" s="63"/>
       <c r="C29" s="62" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D29" s="64"/>
       <c r="E29" s="64"/>
@@ -18839,11 +18891,11 @@
     </row>
     <row r="30">
       <c r="A30" s="62" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B30" s="63"/>
       <c r="C30" s="62" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D30" s="64"/>
       <c r="E30" s="64"/>
@@ -18871,11 +18923,11 @@
     </row>
     <row r="31">
       <c r="A31" s="62" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B31" s="63"/>
       <c r="C31" s="62" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D31" s="64"/>
       <c r="E31" s="64"/>
@@ -18903,11 +18955,11 @@
     </row>
     <row r="32">
       <c r="A32" s="62" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B32" s="63"/>
       <c r="C32" s="62" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -18935,11 +18987,11 @@
     </row>
     <row r="33">
       <c r="A33" s="59" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B33" s="60"/>
       <c r="C33" s="59" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D33" s="61"/>
       <c r="E33" s="61"/>
@@ -18967,102 +19019,102 @@
     </row>
     <row r="34">
       <c r="A34" s="58" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B34" s="58" t="s">
         <v>811</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="58" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B35" s="58" t="s">
         <v>813</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="58" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B36" s="58" t="s">
         <v>815</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="58" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B37" s="58" t="s">
         <v>814</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="58" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B38" s="58" t="s">
         <v>812</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="58" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B39" s="65"/>
       <c r="C39" s="58" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="58" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B40" s="65"/>
       <c r="C40" s="58" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="58" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B41" s="65"/>
       <c r="C41" s="58" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="58" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B42" s="65"/>
       <c r="C42" s="58" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B43" s="60"/>
       <c r="C43" s="59" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D43" s="61"/>
       <c r="E43" s="61"/>
@@ -19090,11 +19142,11 @@
     </row>
     <row r="44">
       <c r="A44" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B44" s="60"/>
       <c r="C44" s="59" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D44" s="61"/>
       <c r="E44" s="61"/>
@@ -19122,11 +19174,11 @@
     </row>
     <row r="45">
       <c r="A45" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B45" s="60"/>
       <c r="C45" s="59" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D45" s="61"/>
       <c r="E45" s="61"/>
@@ -19154,11 +19206,11 @@
     </row>
     <row r="46">
       <c r="A46" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B46" s="60"/>
       <c r="C46" s="59" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D46" s="61"/>
       <c r="E46" s="61"/>
@@ -19186,11 +19238,11 @@
     </row>
     <row r="47">
       <c r="A47" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B47" s="60"/>
       <c r="C47" s="59" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D47" s="61"/>
       <c r="E47" s="61"/>
@@ -19218,11 +19270,11 @@
     </row>
     <row r="48">
       <c r="A48" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B48" s="60"/>
       <c r="C48" s="59" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="D48" s="61"/>
       <c r="E48" s="61"/>
@@ -19250,11 +19302,11 @@
     </row>
     <row r="49">
       <c r="A49" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B49" s="60"/>
       <c r="C49" s="59" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D49" s="61"/>
       <c r="E49" s="61"/>
@@ -19306,12 +19358,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="67" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D1" s="68"/>
       <c r="E1" s="69"/>
       <c r="F1" s="67" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="G1" s="68"/>
       <c r="H1" s="69"/>
@@ -19320,22 +19372,22 @@
       <c r="A2" s="70"/>
       <c r="B2" s="70"/>
       <c r="C2" s="71" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D2" s="71" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="E2" s="71" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F2" s="71" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="G2" s="71" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="H2" s="71" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="3">
@@ -19542,7 +19594,7 @@
     </row>
     <row r="13">
       <c r="A13" s="72" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B13" s="72" t="s">
         <v>39</v>
@@ -19563,7 +19615,7 @@
     </row>
     <row r="14">
       <c r="A14" s="72" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B14" s="72" t="s">
         <v>41</v>
@@ -20475,7 +20527,7 @@
         <v>785</v>
       </c>
       <c r="B63" s="72" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="C63" s="74"/>
       <c r="D63" s="74"/>
@@ -22204,7 +22256,7 @@
     </row>
     <row r="163">
       <c r="A163" s="72" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B163" s="72" t="s">
         <v>534</v>
@@ -22224,7 +22276,7 @@
         <v>603</v>
       </c>
       <c r="B164" s="72" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="C164" s="74"/>
       <c r="D164" s="74"/>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="1079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="1086">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -2986,6 +2986,9 @@
     <t>BY-FBT05GNC</t>
   </si>
   <si>
+    <t>BY-FBT05VC</t>
+  </si>
+  <si>
     <t>BY-FBT05PC</t>
   </si>
   <si>
@@ -3053,6 +3056,24 @@
   </si>
   <si>
     <t>BY-BHC01H</t>
+  </si>
+  <si>
+    <t>BY-FBT05BCC</t>
+  </si>
+  <si>
+    <t>BY-FBT05GCC</t>
+  </si>
+  <si>
+    <t>BY-FBT05C</t>
+  </si>
+  <si>
+    <t>BY-FBT05VCC</t>
+  </si>
+  <si>
+    <t>BY-FBT05PCC</t>
+  </si>
+  <si>
+    <t>BY-FBT01BC</t>
   </si>
   <si>
     <t xml:space="preserve">  </t>
@@ -13685,9 +13706,7 @@
       <c r="A334" s="28" t="s">
         <v>988</v>
       </c>
-      <c r="B334" s="28" t="s">
-        <v>100</v>
-      </c>
+      <c r="B334" s="28"/>
       <c r="C334" s="47" t="s">
         <v>100</v>
       </c>
@@ -13699,7 +13718,7 @@
         <v>989</v>
       </c>
       <c r="B335" s="28" t="s">
-        <v>106</v>
+        <v>990</v>
       </c>
       <c r="C335" s="47" t="s">
         <v>106</v>
@@ -13709,7 +13728,7 @@
     </row>
     <row r="336" ht="22.5" customHeight="1">
       <c r="A336" s="28" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B336" s="28"/>
       <c r="C336" s="47" t="s">
@@ -13720,11 +13739,9 @@
     </row>
     <row r="337" ht="22.5" customHeight="1">
       <c r="A337" s="28" t="s">
-        <v>991</v>
-      </c>
-      <c r="B337" s="28" t="s">
-        <v>102</v>
-      </c>
+        <v>992</v>
+      </c>
+      <c r="B337" s="28"/>
       <c r="C337" s="47" t="s">
         <v>102</v>
       </c>
@@ -13733,59 +13750,59 @@
     </row>
     <row r="338" ht="22.5" customHeight="1">
       <c r="A338" s="28" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B338" s="28"/>
       <c r="C338" s="47" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D338" s="29"/>
       <c r="E338" s="29"/>
     </row>
     <row r="339" ht="22.5" customHeight="1">
       <c r="A339" s="28" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B339" s="28" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C339" s="47" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D339" s="29"/>
       <c r="E339" s="29"/>
     </row>
     <row r="340" ht="22.5" customHeight="1">
       <c r="A340" s="28" t="s">
+        <v>997</v>
+      </c>
+      <c r="B340" s="28" t="s">
         <v>996</v>
       </c>
-      <c r="B340" s="28" t="s">
-        <v>995</v>
-      </c>
       <c r="C340" s="47" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D340" s="29"/>
       <c r="E340" s="29"/>
     </row>
     <row r="341" ht="22.5" customHeight="1">
       <c r="A341" s="28" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B341" s="28"/>
       <c r="C341" s="47" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D341" s="29"/>
       <c r="E341" s="29"/>
     </row>
     <row r="342" ht="22.5" customHeight="1">
       <c r="A342" s="28" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B342" s="28"/>
       <c r="C342" s="47" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D342" s="29"/>
       <c r="E342" s="29"/>
@@ -13794,9 +13811,7 @@
       <c r="A343" s="28" t="s">
         <v>988</v>
       </c>
-      <c r="B343" s="28" t="s">
-        <v>100</v>
-      </c>
+      <c r="B343" s="28"/>
       <c r="C343" s="47" t="s">
         <v>100</v>
       </c>
@@ -13807,9 +13822,7 @@
       <c r="A344" s="28" t="s">
         <v>989</v>
       </c>
-      <c r="B344" s="28" t="s">
-        <v>106</v>
-      </c>
+      <c r="B344" s="28"/>
       <c r="C344" s="47" t="s">
         <v>106</v>
       </c>
@@ -13818,7 +13831,7 @@
     </row>
     <row r="345" ht="22.5" customHeight="1">
       <c r="A345" s="28" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B345" s="28"/>
       <c r="C345" s="47" t="s">
@@ -13829,11 +13842,9 @@
     </row>
     <row r="346" ht="22.5" customHeight="1">
       <c r="A346" s="46" t="s">
-        <v>991</v>
-      </c>
-      <c r="B346" s="28" t="s">
-        <v>102</v>
-      </c>
+        <v>992</v>
+      </c>
+      <c r="B346" s="28"/>
       <c r="C346" s="47" t="s">
         <v>102</v>
       </c>
@@ -13842,7 +13853,7 @@
     </row>
     <row r="347" ht="22.5" customHeight="1">
       <c r="A347" s="28" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B347" s="48"/>
       <c r="C347" s="49" t="s">
@@ -13853,7 +13864,7 @@
     </row>
     <row r="348" ht="22.5" customHeight="1">
       <c r="A348" s="48" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B348" s="48"/>
       <c r="C348" s="49" t="s">
@@ -13864,7 +13875,7 @@
     </row>
     <row r="349" ht="22.5" customHeight="1">
       <c r="A349" s="48" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B349" s="48"/>
       <c r="C349" s="49" t="s">
@@ -13875,7 +13886,7 @@
     </row>
     <row r="350" ht="22.5" customHeight="1">
       <c r="A350" s="48" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B350" s="48"/>
       <c r="C350" s="49" t="s">
@@ -13886,28 +13897,28 @@
     </row>
     <row r="351" ht="22.5" customHeight="1">
       <c r="A351" s="48" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B351" s="48" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C351" s="49"/>
       <c r="D351" s="50"/>
       <c r="E351" s="49" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="352" ht="22.5" customHeight="1">
       <c r="A352" s="48" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B352" s="48" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C352" s="49"/>
       <c r="D352" s="50"/>
       <c r="E352" s="49" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="353" ht="22.5" customHeight="1">
@@ -13926,7 +13937,7 @@
         <v>430</v>
       </c>
       <c r="B354" s="48" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C354" s="49"/>
       <c r="D354" s="50"/>
@@ -13934,7 +13945,7 @@
     </row>
     <row r="355" ht="22.5" customHeight="1">
       <c r="A355" s="48" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B355" s="48" t="s">
         <v>16</v>
@@ -13945,7 +13956,7 @@
     </row>
     <row r="356" ht="22.5" customHeight="1">
       <c r="A356" s="48" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B356" s="48" t="s">
         <v>36</v>
@@ -13955,37 +13966,57 @@
       <c r="E356" s="50"/>
     </row>
     <row r="357" ht="22.5" customHeight="1">
-      <c r="A357" s="48"/>
+      <c r="A357" s="48" t="s">
+        <v>1014</v>
+      </c>
       <c r="B357" s="48"/>
-      <c r="C357" s="49"/>
+      <c r="C357" s="49" t="s">
+        <v>100</v>
+      </c>
       <c r="D357" s="50"/>
       <c r="E357" s="50"/>
     </row>
     <row r="358" ht="22.5" customHeight="1">
-      <c r="A358" s="48"/>
+      <c r="A358" s="48" t="s">
+        <v>1015</v>
+      </c>
       <c r="B358" s="48"/>
-      <c r="C358" s="49"/>
+      <c r="C358" s="49" t="s">
+        <v>1016</v>
+      </c>
       <c r="D358" s="50"/>
       <c r="E358" s="50"/>
     </row>
     <row r="359" ht="22.5" customHeight="1">
-      <c r="A359" s="48"/>
+      <c r="A359" s="48" t="s">
+        <v>1017</v>
+      </c>
       <c r="B359" s="48"/>
-      <c r="C359" s="49"/>
+      <c r="C359" s="49" t="s">
+        <v>106</v>
+      </c>
       <c r="D359" s="50"/>
       <c r="E359" s="50"/>
     </row>
     <row r="360" ht="22.5" customHeight="1">
-      <c r="A360" s="48"/>
+      <c r="A360" s="48" t="s">
+        <v>1018</v>
+      </c>
       <c r="B360" s="48"/>
-      <c r="C360" s="49"/>
+      <c r="C360" s="49" t="s">
+        <v>104</v>
+      </c>
       <c r="D360" s="50"/>
       <c r="E360" s="50"/>
     </row>
     <row r="361" ht="22.5" customHeight="1">
-      <c r="A361" s="48"/>
+      <c r="A361" s="48" t="s">
+        <v>1019</v>
+      </c>
       <c r="B361" s="48"/>
-      <c r="C361" s="49"/>
+      <c r="C361" s="49" t="s">
+        <v>78</v>
+      </c>
       <c r="D361" s="50"/>
       <c r="E361" s="50"/>
     </row>
@@ -14308,7 +14339,7 @@
       <c r="A407" s="51"/>
       <c r="B407" s="52"/>
       <c r="C407" s="54" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="D407" s="53"/>
       <c r="E407" s="53"/>
@@ -18484,24 +18515,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="55" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="B1" s="55" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="56" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="B2" s="56" t="s">
         <v>762</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="D2" s="57"/>
       <c r="E2" s="57"/>
@@ -18529,13 +18560,13 @@
     </row>
     <row r="3">
       <c r="A3" s="56" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="B3" s="56" t="s">
         <v>758</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="D3" s="57"/>
       <c r="E3" s="57"/>
@@ -18563,275 +18594,275 @@
     </row>
     <row r="4">
       <c r="A4" s="58" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="B4" s="58" t="s">
         <v>737</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="58" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="58" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="58" t="s">
         <v>740</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="58" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="B7" s="58" t="s">
         <v>50</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="58" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="B8" s="58" t="s">
         <v>766</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="58" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="B9" s="58" t="s">
         <v>772</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="58" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="B10" s="58" t="s">
         <v>770</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="58" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="B11" s="58" t="s">
         <v>767</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="58" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>774</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="58" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="B13" s="58" t="s">
         <v>777</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="58" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="B14" s="58" t="s">
         <v>784</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="58" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="B15" s="58" t="s">
         <v>781</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B16" s="58" t="s">
         <v>791</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B17" s="58" t="s">
         <v>794</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B18" s="58" t="s">
         <v>788</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B19" s="58" t="s">
         <v>790</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B20" s="58" t="s">
         <v>792</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B21" s="58" t="s">
         <v>789</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="58" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="B22" s="58" t="s">
         <v>793</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="58" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="58" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="B24" s="58" t="s">
         <v>706</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="58" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="58" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="58" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="B27" s="58" t="s">
         <v>707</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="59" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="B28" s="60"/>
       <c r="C28" s="59" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="D28" s="61"/>
       <c r="E28" s="61"/>
@@ -18859,11 +18890,11 @@
     </row>
     <row r="29">
       <c r="A29" s="62" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="B29" s="63"/>
       <c r="C29" s="62" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="D29" s="64"/>
       <c r="E29" s="64"/>
@@ -18891,11 +18922,11 @@
     </row>
     <row r="30">
       <c r="A30" s="62" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="B30" s="63"/>
       <c r="C30" s="62" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="D30" s="64"/>
       <c r="E30" s="64"/>
@@ -18923,11 +18954,11 @@
     </row>
     <row r="31">
       <c r="A31" s="62" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="B31" s="63"/>
       <c r="C31" s="62" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="D31" s="64"/>
       <c r="E31" s="64"/>
@@ -18955,11 +18986,11 @@
     </row>
     <row r="32">
       <c r="A32" s="62" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="B32" s="63"/>
       <c r="C32" s="62" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -18987,11 +19018,11 @@
     </row>
     <row r="33">
       <c r="A33" s="59" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="B33" s="60"/>
       <c r="C33" s="59" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="D33" s="61"/>
       <c r="E33" s="61"/>
@@ -19019,102 +19050,102 @@
     </row>
     <row r="34">
       <c r="A34" s="58" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B34" s="58" t="s">
         <v>811</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="58" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B35" s="58" t="s">
         <v>813</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="58" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B36" s="58" t="s">
         <v>815</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="58" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B37" s="58" t="s">
         <v>814</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="58" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B38" s="58" t="s">
         <v>812</v>
       </c>
       <c r="C38" s="58" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="58" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="B39" s="65"/>
       <c r="C39" s="58" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="58" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="B40" s="65"/>
       <c r="C40" s="58" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="58" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="B41" s="65"/>
       <c r="C41" s="58" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="58" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="B42" s="65"/>
       <c r="C42" s="58" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B43" s="60"/>
       <c r="C43" s="59" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="D43" s="61"/>
       <c r="E43" s="61"/>
@@ -19142,11 +19173,11 @@
     </row>
     <row r="44">
       <c r="A44" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B44" s="60"/>
       <c r="C44" s="59" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="D44" s="61"/>
       <c r="E44" s="61"/>
@@ -19174,11 +19205,11 @@
     </row>
     <row r="45">
       <c r="A45" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B45" s="60"/>
       <c r="C45" s="59" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="D45" s="61"/>
       <c r="E45" s="61"/>
@@ -19206,11 +19237,11 @@
     </row>
     <row r="46">
       <c r="A46" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B46" s="60"/>
       <c r="C46" s="59" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="D46" s="61"/>
       <c r="E46" s="61"/>
@@ -19238,11 +19269,11 @@
     </row>
     <row r="47">
       <c r="A47" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B47" s="60"/>
       <c r="C47" s="59" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="D47" s="61"/>
       <c r="E47" s="61"/>
@@ -19270,11 +19301,11 @@
     </row>
     <row r="48">
       <c r="A48" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B48" s="60"/>
       <c r="C48" s="59" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="D48" s="61"/>
       <c r="E48" s="61"/>
@@ -19302,11 +19333,11 @@
     </row>
     <row r="49">
       <c r="A49" s="59" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B49" s="60"/>
       <c r="C49" s="59" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="D49" s="61"/>
       <c r="E49" s="61"/>
@@ -19358,12 +19389,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="67" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="D1" s="68"/>
       <c r="E1" s="69"/>
       <c r="F1" s="67" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="G1" s="68"/>
       <c r="H1" s="69"/>
@@ -19372,22 +19403,22 @@
       <c r="A2" s="70"/>
       <c r="B2" s="70"/>
       <c r="C2" s="71" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="D2" s="71" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="E2" s="71" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="F2" s="71" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="G2" s="71" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="H2" s="71" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="3">
@@ -19594,7 +19625,7 @@
     </row>
     <row r="13">
       <c r="A13" s="72" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="B13" s="72" t="s">
         <v>39</v>
@@ -19615,7 +19646,7 @@
     </row>
     <row r="14">
       <c r="A14" s="72" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="B14" s="72" t="s">
         <v>41</v>
@@ -20527,7 +20558,7 @@
         <v>785</v>
       </c>
       <c r="B63" s="72" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="C63" s="74"/>
       <c r="D63" s="74"/>
@@ -22256,7 +22287,7 @@
     </row>
     <row r="163">
       <c r="A163" s="72" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="B163" s="72" t="s">
         <v>534</v>
@@ -22276,7 +22307,7 @@
         <v>603</v>
       </c>
       <c r="B164" s="72" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="C164" s="74"/>
       <c r="D164" s="74"/>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -5,8 +5,9 @@
   <sheets>
     <sheet state="visible" name="PRODUCTOS" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="SKU MAP" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Hoja 3" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="PRECIOS" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="MENSAJES" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Hoja 3" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="PRECIOS" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="1104">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -3086,6 +3087,71 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>example message</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>AD24</t>
+  </si>
+  <si>
+    <t>Buenos días 😊
+Queríamos informarte de que hemos tenido un retraso en la llegada de las mancuernas ajustables debido a incidencias en el transporte marítimo y cambios en las rutas logísticas
+Tras permanecer varios días retenida en Valencia, la mercancía ha sufrido una incidencia en puerto. Según la última información recibida, no llegará a Barcelona hasta el día 19/06, por lo que prevemos recibirla en nuestro almacén en esa fecha
+En cuanto recibamos las mancuernas, prepararemos y enviaremos tu pedido lo antes posible
+Lamentamos sinceramente las molestias ocasionadas y agradecemos tu comprensión</t>
+  </si>
+  <si>
+    <t>out_of_stock</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">type </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>es para filtrar, podéis usar los tipos que necesitéis sin requerir cambios. Añadid aquí los que vayáis usando para que os ponga un icono y color en la tabla.</t>
+    </r>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>another test</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>test 2</t>
+  </si>
+  <si>
+    <t>refund</t>
   </si>
   <si>
     <t>Nombre del producto</t>
@@ -3290,7 +3356,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -3337,13 +3403,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color theme="1"/>
       <name val="宋体"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3382,6 +3453,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9900FF"/>
+        <bgColor rgb="FF9900FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
@@ -3399,7 +3494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border/>
     <border>
       <left style="medium">
@@ -3446,6 +3541,20 @@
         <color rgb="FF000000"/>
       </right>
       <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -3519,7 +3628,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="83">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3666,23 +3775,44 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="7" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="11" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -3693,25 +3823,25 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3781,7 +3911,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="2">
+  <tableStyles count="3">
     <tableStyle count="4" pivot="0" name="PRODUCTOS-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -3789,6 +3919,12 @@
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
     <tableStyle count="4" pivot="0" name="SKU MAP-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="MENSAJES-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -3811,6 +3947,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -3844,6 +3984,17 @@
     <tableColumn name="price_distr" id="5"/>
   </tableColumns>
   <tableStyleInfo name="SKU MAP-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C5" displayName="messages" name="messages" id="3">
+  <tableColumns count="3">
+    <tableColumn name="title" id="1"/>
+    <tableColumn name="message" id="2"/>
+    <tableColumn name="type" id="3"/>
+  </tableColumns>
+  <tableStyleInfo name="MENSAJES-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -18562,6 +18713,3080 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="142.38"/>
+    <col customWidth="1" min="5" max="5" width="46.88"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="60"/>
+      <c r="E6" s="61" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="60"/>
+      <c r="E7" s="62" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="60"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="60"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="60"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="60"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="60"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="60"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="60"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="60"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="60"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="60"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="60"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="60"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="60"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="60"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="60"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="60"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="60"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="60"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="60"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="60"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="60"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="60"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="60"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="60"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="60"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="60"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="60"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="60"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="60"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="60"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="60"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="60"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="60"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="60"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="60"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="60"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="60"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="60"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="60"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="60"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="60"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="60"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="60"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="60"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="60"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="60"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="60"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="60"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="60"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="60"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="60"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="60"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="60"/>
+    </row>
+    <row r="61">
+      <c r="C61" s="60"/>
+    </row>
+    <row r="62">
+      <c r="C62" s="60"/>
+    </row>
+    <row r="63">
+      <c r="C63" s="60"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="60"/>
+    </row>
+    <row r="65">
+      <c r="C65" s="60"/>
+    </row>
+    <row r="66">
+      <c r="C66" s="60"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="60"/>
+    </row>
+    <row r="68">
+      <c r="C68" s="60"/>
+    </row>
+    <row r="69">
+      <c r="C69" s="60"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="60"/>
+    </row>
+    <row r="71">
+      <c r="C71" s="60"/>
+    </row>
+    <row r="72">
+      <c r="C72" s="60"/>
+    </row>
+    <row r="73">
+      <c r="C73" s="60"/>
+    </row>
+    <row r="74">
+      <c r="C74" s="60"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="60"/>
+    </row>
+    <row r="76">
+      <c r="C76" s="60"/>
+    </row>
+    <row r="77">
+      <c r="C77" s="60"/>
+    </row>
+    <row r="78">
+      <c r="C78" s="60"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="60"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="60"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="60"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="60"/>
+    </row>
+    <row r="83">
+      <c r="C83" s="60"/>
+    </row>
+    <row r="84">
+      <c r="C84" s="60"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="60"/>
+    </row>
+    <row r="86">
+      <c r="C86" s="60"/>
+    </row>
+    <row r="87">
+      <c r="C87" s="60"/>
+    </row>
+    <row r="88">
+      <c r="C88" s="60"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="60"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="60"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="60"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="60"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="60"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="60"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="60"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="60"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="60"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="60"/>
+    </row>
+    <row r="99">
+      <c r="C99" s="60"/>
+    </row>
+    <row r="100">
+      <c r="C100" s="60"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="60"/>
+    </row>
+    <row r="102">
+      <c r="C102" s="60"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="60"/>
+    </row>
+    <row r="104">
+      <c r="C104" s="60"/>
+    </row>
+    <row r="105">
+      <c r="C105" s="60"/>
+    </row>
+    <row r="106">
+      <c r="C106" s="60"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="60"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="60"/>
+    </row>
+    <row r="109">
+      <c r="C109" s="60"/>
+    </row>
+    <row r="110">
+      <c r="C110" s="60"/>
+    </row>
+    <row r="111">
+      <c r="C111" s="60"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="60"/>
+    </row>
+    <row r="113">
+      <c r="C113" s="60"/>
+    </row>
+    <row r="114">
+      <c r="C114" s="60"/>
+    </row>
+    <row r="115">
+      <c r="C115" s="60"/>
+    </row>
+    <row r="116">
+      <c r="C116" s="60"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="60"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="60"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="60"/>
+    </row>
+    <row r="120">
+      <c r="C120" s="60"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="60"/>
+    </row>
+    <row r="122">
+      <c r="C122" s="60"/>
+    </row>
+    <row r="123">
+      <c r="C123" s="60"/>
+    </row>
+    <row r="124">
+      <c r="C124" s="60"/>
+    </row>
+    <row r="125">
+      <c r="C125" s="60"/>
+    </row>
+    <row r="126">
+      <c r="C126" s="60"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="60"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="60"/>
+    </row>
+    <row r="129">
+      <c r="C129" s="60"/>
+    </row>
+    <row r="130">
+      <c r="C130" s="60"/>
+    </row>
+    <row r="131">
+      <c r="C131" s="60"/>
+    </row>
+    <row r="132">
+      <c r="C132" s="60"/>
+    </row>
+    <row r="133">
+      <c r="C133" s="60"/>
+    </row>
+    <row r="134">
+      <c r="C134" s="60"/>
+    </row>
+    <row r="135">
+      <c r="C135" s="60"/>
+    </row>
+    <row r="136">
+      <c r="C136" s="60"/>
+    </row>
+    <row r="137">
+      <c r="C137" s="60"/>
+    </row>
+    <row r="138">
+      <c r="C138" s="60"/>
+    </row>
+    <row r="139">
+      <c r="C139" s="60"/>
+    </row>
+    <row r="140">
+      <c r="C140" s="60"/>
+    </row>
+    <row r="141">
+      <c r="C141" s="60"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="60"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="60"/>
+    </row>
+    <row r="144">
+      <c r="C144" s="60"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="60"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="60"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="60"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="60"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="60"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="60"/>
+    </row>
+    <row r="151">
+      <c r="C151" s="60"/>
+    </row>
+    <row r="152">
+      <c r="C152" s="60"/>
+    </row>
+    <row r="153">
+      <c r="C153" s="60"/>
+    </row>
+    <row r="154">
+      <c r="C154" s="60"/>
+    </row>
+    <row r="155">
+      <c r="C155" s="60"/>
+    </row>
+    <row r="156">
+      <c r="C156" s="60"/>
+    </row>
+    <row r="157">
+      <c r="C157" s="60"/>
+    </row>
+    <row r="158">
+      <c r="C158" s="60"/>
+    </row>
+    <row r="159">
+      <c r="C159" s="60"/>
+    </row>
+    <row r="160">
+      <c r="C160" s="60"/>
+    </row>
+    <row r="161">
+      <c r="C161" s="60"/>
+    </row>
+    <row r="162">
+      <c r="C162" s="60"/>
+    </row>
+    <row r="163">
+      <c r="C163" s="60"/>
+    </row>
+    <row r="164">
+      <c r="C164" s="60"/>
+    </row>
+    <row r="165">
+      <c r="C165" s="60"/>
+    </row>
+    <row r="166">
+      <c r="C166" s="60"/>
+    </row>
+    <row r="167">
+      <c r="C167" s="60"/>
+    </row>
+    <row r="168">
+      <c r="C168" s="60"/>
+    </row>
+    <row r="169">
+      <c r="C169" s="60"/>
+    </row>
+    <row r="170">
+      <c r="C170" s="60"/>
+    </row>
+    <row r="171">
+      <c r="C171" s="60"/>
+    </row>
+    <row r="172">
+      <c r="C172" s="60"/>
+    </row>
+    <row r="173">
+      <c r="C173" s="60"/>
+    </row>
+    <row r="174">
+      <c r="C174" s="60"/>
+    </row>
+    <row r="175">
+      <c r="C175" s="60"/>
+    </row>
+    <row r="176">
+      <c r="C176" s="60"/>
+    </row>
+    <row r="177">
+      <c r="C177" s="60"/>
+    </row>
+    <row r="178">
+      <c r="C178" s="60"/>
+    </row>
+    <row r="179">
+      <c r="C179" s="60"/>
+    </row>
+    <row r="180">
+      <c r="C180" s="60"/>
+    </row>
+    <row r="181">
+      <c r="C181" s="60"/>
+    </row>
+    <row r="182">
+      <c r="C182" s="60"/>
+    </row>
+    <row r="183">
+      <c r="C183" s="60"/>
+    </row>
+    <row r="184">
+      <c r="C184" s="60"/>
+    </row>
+    <row r="185">
+      <c r="C185" s="60"/>
+    </row>
+    <row r="186">
+      <c r="C186" s="60"/>
+    </row>
+    <row r="187">
+      <c r="C187" s="60"/>
+    </row>
+    <row r="188">
+      <c r="C188" s="60"/>
+    </row>
+    <row r="189">
+      <c r="C189" s="60"/>
+    </row>
+    <row r="190">
+      <c r="C190" s="60"/>
+    </row>
+    <row r="191">
+      <c r="C191" s="60"/>
+    </row>
+    <row r="192">
+      <c r="C192" s="60"/>
+    </row>
+    <row r="193">
+      <c r="C193" s="60"/>
+    </row>
+    <row r="194">
+      <c r="C194" s="60"/>
+    </row>
+    <row r="195">
+      <c r="C195" s="60"/>
+    </row>
+    <row r="196">
+      <c r="C196" s="60"/>
+    </row>
+    <row r="197">
+      <c r="C197" s="60"/>
+    </row>
+    <row r="198">
+      <c r="C198" s="60"/>
+    </row>
+    <row r="199">
+      <c r="C199" s="60"/>
+    </row>
+    <row r="200">
+      <c r="C200" s="60"/>
+    </row>
+    <row r="201">
+      <c r="C201" s="60"/>
+    </row>
+    <row r="202">
+      <c r="C202" s="60"/>
+    </row>
+    <row r="203">
+      <c r="C203" s="60"/>
+    </row>
+    <row r="204">
+      <c r="C204" s="60"/>
+    </row>
+    <row r="205">
+      <c r="C205" s="60"/>
+    </row>
+    <row r="206">
+      <c r="C206" s="60"/>
+    </row>
+    <row r="207">
+      <c r="C207" s="60"/>
+    </row>
+    <row r="208">
+      <c r="C208" s="60"/>
+    </row>
+    <row r="209">
+      <c r="C209" s="60"/>
+    </row>
+    <row r="210">
+      <c r="C210" s="60"/>
+    </row>
+    <row r="211">
+      <c r="C211" s="60"/>
+    </row>
+    <row r="212">
+      <c r="C212" s="60"/>
+    </row>
+    <row r="213">
+      <c r="C213" s="60"/>
+    </row>
+    <row r="214">
+      <c r="C214" s="60"/>
+    </row>
+    <row r="215">
+      <c r="C215" s="60"/>
+    </row>
+    <row r="216">
+      <c r="C216" s="60"/>
+    </row>
+    <row r="217">
+      <c r="C217" s="60"/>
+    </row>
+    <row r="218">
+      <c r="C218" s="60"/>
+    </row>
+    <row r="219">
+      <c r="C219" s="60"/>
+    </row>
+    <row r="220">
+      <c r="C220" s="60"/>
+    </row>
+    <row r="221">
+      <c r="C221" s="60"/>
+    </row>
+    <row r="222">
+      <c r="C222" s="60"/>
+    </row>
+    <row r="223">
+      <c r="C223" s="60"/>
+    </row>
+    <row r="224">
+      <c r="C224" s="60"/>
+    </row>
+    <row r="225">
+      <c r="C225" s="60"/>
+    </row>
+    <row r="226">
+      <c r="C226" s="60"/>
+    </row>
+    <row r="227">
+      <c r="C227" s="60"/>
+    </row>
+    <row r="228">
+      <c r="C228" s="60"/>
+    </row>
+    <row r="229">
+      <c r="C229" s="60"/>
+    </row>
+    <row r="230">
+      <c r="C230" s="60"/>
+    </row>
+    <row r="231">
+      <c r="C231" s="60"/>
+    </row>
+    <row r="232">
+      <c r="C232" s="60"/>
+    </row>
+    <row r="233">
+      <c r="C233" s="60"/>
+    </row>
+    <row r="234">
+      <c r="C234" s="60"/>
+    </row>
+    <row r="235">
+      <c r="C235" s="60"/>
+    </row>
+    <row r="236">
+      <c r="C236" s="60"/>
+    </row>
+    <row r="237">
+      <c r="C237" s="60"/>
+    </row>
+    <row r="238">
+      <c r="C238" s="60"/>
+    </row>
+    <row r="239">
+      <c r="C239" s="60"/>
+    </row>
+    <row r="240">
+      <c r="C240" s="60"/>
+    </row>
+    <row r="241">
+      <c r="C241" s="60"/>
+    </row>
+    <row r="242">
+      <c r="C242" s="60"/>
+    </row>
+    <row r="243">
+      <c r="C243" s="60"/>
+    </row>
+    <row r="244">
+      <c r="C244" s="60"/>
+    </row>
+    <row r="245">
+      <c r="C245" s="60"/>
+    </row>
+    <row r="246">
+      <c r="C246" s="60"/>
+    </row>
+    <row r="247">
+      <c r="C247" s="60"/>
+    </row>
+    <row r="248">
+      <c r="C248" s="60"/>
+    </row>
+    <row r="249">
+      <c r="C249" s="60"/>
+    </row>
+    <row r="250">
+      <c r="C250" s="60"/>
+    </row>
+    <row r="251">
+      <c r="C251" s="60"/>
+    </row>
+    <row r="252">
+      <c r="C252" s="60"/>
+    </row>
+    <row r="253">
+      <c r="C253" s="60"/>
+    </row>
+    <row r="254">
+      <c r="C254" s="60"/>
+    </row>
+    <row r="255">
+      <c r="C255" s="60"/>
+    </row>
+    <row r="256">
+      <c r="C256" s="60"/>
+    </row>
+    <row r="257">
+      <c r="C257" s="60"/>
+    </row>
+    <row r="258">
+      <c r="C258" s="60"/>
+    </row>
+    <row r="259">
+      <c r="C259" s="60"/>
+    </row>
+    <row r="260">
+      <c r="C260" s="60"/>
+    </row>
+    <row r="261">
+      <c r="C261" s="60"/>
+    </row>
+    <row r="262">
+      <c r="C262" s="60"/>
+    </row>
+    <row r="263">
+      <c r="C263" s="60"/>
+    </row>
+    <row r="264">
+      <c r="C264" s="60"/>
+    </row>
+    <row r="265">
+      <c r="C265" s="60"/>
+    </row>
+    <row r="266">
+      <c r="C266" s="60"/>
+    </row>
+    <row r="267">
+      <c r="C267" s="60"/>
+    </row>
+    <row r="268">
+      <c r="C268" s="60"/>
+    </row>
+    <row r="269">
+      <c r="C269" s="60"/>
+    </row>
+    <row r="270">
+      <c r="C270" s="60"/>
+    </row>
+    <row r="271">
+      <c r="C271" s="60"/>
+    </row>
+    <row r="272">
+      <c r="C272" s="60"/>
+    </row>
+    <row r="273">
+      <c r="C273" s="60"/>
+    </row>
+    <row r="274">
+      <c r="C274" s="60"/>
+    </row>
+    <row r="275">
+      <c r="C275" s="60"/>
+    </row>
+    <row r="276">
+      <c r="C276" s="60"/>
+    </row>
+    <row r="277">
+      <c r="C277" s="60"/>
+    </row>
+    <row r="278">
+      <c r="C278" s="60"/>
+    </row>
+    <row r="279">
+      <c r="C279" s="60"/>
+    </row>
+    <row r="280">
+      <c r="C280" s="60"/>
+    </row>
+    <row r="281">
+      <c r="C281" s="60"/>
+    </row>
+    <row r="282">
+      <c r="C282" s="60"/>
+    </row>
+    <row r="283">
+      <c r="C283" s="60"/>
+    </row>
+    <row r="284">
+      <c r="C284" s="60"/>
+    </row>
+    <row r="285">
+      <c r="C285" s="60"/>
+    </row>
+    <row r="286">
+      <c r="C286" s="60"/>
+    </row>
+    <row r="287">
+      <c r="C287" s="60"/>
+    </row>
+    <row r="288">
+      <c r="C288" s="60"/>
+    </row>
+    <row r="289">
+      <c r="C289" s="60"/>
+    </row>
+    <row r="290">
+      <c r="C290" s="60"/>
+    </row>
+    <row r="291">
+      <c r="C291" s="60"/>
+    </row>
+    <row r="292">
+      <c r="C292" s="60"/>
+    </row>
+    <row r="293">
+      <c r="C293" s="60"/>
+    </row>
+    <row r="294">
+      <c r="C294" s="60"/>
+    </row>
+    <row r="295">
+      <c r="C295" s="60"/>
+    </row>
+    <row r="296">
+      <c r="C296" s="60"/>
+    </row>
+    <row r="297">
+      <c r="C297" s="60"/>
+    </row>
+    <row r="298">
+      <c r="C298" s="60"/>
+    </row>
+    <row r="299">
+      <c r="C299" s="60"/>
+    </row>
+    <row r="300">
+      <c r="C300" s="60"/>
+    </row>
+    <row r="301">
+      <c r="C301" s="60"/>
+    </row>
+    <row r="302">
+      <c r="C302" s="60"/>
+    </row>
+    <row r="303">
+      <c r="C303" s="60"/>
+    </row>
+    <row r="304">
+      <c r="C304" s="60"/>
+    </row>
+    <row r="305">
+      <c r="C305" s="60"/>
+    </row>
+    <row r="306">
+      <c r="C306" s="60"/>
+    </row>
+    <row r="307">
+      <c r="C307" s="60"/>
+    </row>
+    <row r="308">
+      <c r="C308" s="60"/>
+    </row>
+    <row r="309">
+      <c r="C309" s="60"/>
+    </row>
+    <row r="310">
+      <c r="C310" s="60"/>
+    </row>
+    <row r="311">
+      <c r="C311" s="60"/>
+    </row>
+    <row r="312">
+      <c r="C312" s="60"/>
+    </row>
+    <row r="313">
+      <c r="C313" s="60"/>
+    </row>
+    <row r="314">
+      <c r="C314" s="60"/>
+    </row>
+    <row r="315">
+      <c r="C315" s="60"/>
+    </row>
+    <row r="316">
+      <c r="C316" s="60"/>
+    </row>
+    <row r="317">
+      <c r="C317" s="60"/>
+    </row>
+    <row r="318">
+      <c r="C318" s="60"/>
+    </row>
+    <row r="319">
+      <c r="C319" s="60"/>
+    </row>
+    <row r="320">
+      <c r="C320" s="60"/>
+    </row>
+    <row r="321">
+      <c r="C321" s="60"/>
+    </row>
+    <row r="322">
+      <c r="C322" s="60"/>
+    </row>
+    <row r="323">
+      <c r="C323" s="60"/>
+    </row>
+    <row r="324">
+      <c r="C324" s="60"/>
+    </row>
+    <row r="325">
+      <c r="C325" s="60"/>
+    </row>
+    <row r="326">
+      <c r="C326" s="60"/>
+    </row>
+    <row r="327">
+      <c r="C327" s="60"/>
+    </row>
+    <row r="328">
+      <c r="C328" s="60"/>
+    </row>
+    <row r="329">
+      <c r="C329" s="60"/>
+    </row>
+    <row r="330">
+      <c r="C330" s="60"/>
+    </row>
+    <row r="331">
+      <c r="C331" s="60"/>
+    </row>
+    <row r="332">
+      <c r="C332" s="60"/>
+    </row>
+    <row r="333">
+      <c r="C333" s="60"/>
+    </row>
+    <row r="334">
+      <c r="C334" s="60"/>
+    </row>
+    <row r="335">
+      <c r="C335" s="60"/>
+    </row>
+    <row r="336">
+      <c r="C336" s="60"/>
+    </row>
+    <row r="337">
+      <c r="C337" s="60"/>
+    </row>
+    <row r="338">
+      <c r="C338" s="60"/>
+    </row>
+    <row r="339">
+      <c r="C339" s="60"/>
+    </row>
+    <row r="340">
+      <c r="C340" s="60"/>
+    </row>
+    <row r="341">
+      <c r="C341" s="60"/>
+    </row>
+    <row r="342">
+      <c r="C342" s="60"/>
+    </row>
+    <row r="343">
+      <c r="C343" s="60"/>
+    </row>
+    <row r="344">
+      <c r="C344" s="60"/>
+    </row>
+    <row r="345">
+      <c r="C345" s="60"/>
+    </row>
+    <row r="346">
+      <c r="C346" s="60"/>
+    </row>
+    <row r="347">
+      <c r="C347" s="60"/>
+    </row>
+    <row r="348">
+      <c r="C348" s="60"/>
+    </row>
+    <row r="349">
+      <c r="C349" s="60"/>
+    </row>
+    <row r="350">
+      <c r="C350" s="60"/>
+    </row>
+    <row r="351">
+      <c r="C351" s="60"/>
+    </row>
+    <row r="352">
+      <c r="C352" s="60"/>
+    </row>
+    <row r="353">
+      <c r="C353" s="60"/>
+    </row>
+    <row r="354">
+      <c r="C354" s="60"/>
+    </row>
+    <row r="355">
+      <c r="C355" s="60"/>
+    </row>
+    <row r="356">
+      <c r="C356" s="60"/>
+    </row>
+    <row r="357">
+      <c r="C357" s="60"/>
+    </row>
+    <row r="358">
+      <c r="C358" s="60"/>
+    </row>
+    <row r="359">
+      <c r="C359" s="60"/>
+    </row>
+    <row r="360">
+      <c r="C360" s="60"/>
+    </row>
+    <row r="361">
+      <c r="C361" s="60"/>
+    </row>
+    <row r="362">
+      <c r="C362" s="60"/>
+    </row>
+    <row r="363">
+      <c r="C363" s="60"/>
+    </row>
+    <row r="364">
+      <c r="C364" s="60"/>
+    </row>
+    <row r="365">
+      <c r="C365" s="60"/>
+    </row>
+    <row r="366">
+      <c r="C366" s="60"/>
+    </row>
+    <row r="367">
+      <c r="C367" s="60"/>
+    </row>
+    <row r="368">
+      <c r="C368" s="60"/>
+    </row>
+    <row r="369">
+      <c r="C369" s="60"/>
+    </row>
+    <row r="370">
+      <c r="C370" s="60"/>
+    </row>
+    <row r="371">
+      <c r="C371" s="60"/>
+    </row>
+    <row r="372">
+      <c r="C372" s="60"/>
+    </row>
+    <row r="373">
+      <c r="C373" s="60"/>
+    </row>
+    <row r="374">
+      <c r="C374" s="60"/>
+    </row>
+    <row r="375">
+      <c r="C375" s="60"/>
+    </row>
+    <row r="376">
+      <c r="C376" s="60"/>
+    </row>
+    <row r="377">
+      <c r="C377" s="60"/>
+    </row>
+    <row r="378">
+      <c r="C378" s="60"/>
+    </row>
+    <row r="379">
+      <c r="C379" s="60"/>
+    </row>
+    <row r="380">
+      <c r="C380" s="60"/>
+    </row>
+    <row r="381">
+      <c r="C381" s="60"/>
+    </row>
+    <row r="382">
+      <c r="C382" s="60"/>
+    </row>
+    <row r="383">
+      <c r="C383" s="60"/>
+    </row>
+    <row r="384">
+      <c r="C384" s="60"/>
+    </row>
+    <row r="385">
+      <c r="C385" s="60"/>
+    </row>
+    <row r="386">
+      <c r="C386" s="60"/>
+    </row>
+    <row r="387">
+      <c r="C387" s="60"/>
+    </row>
+    <row r="388">
+      <c r="C388" s="60"/>
+    </row>
+    <row r="389">
+      <c r="C389" s="60"/>
+    </row>
+    <row r="390">
+      <c r="C390" s="60"/>
+    </row>
+    <row r="391">
+      <c r="C391" s="60"/>
+    </row>
+    <row r="392">
+      <c r="C392" s="60"/>
+    </row>
+    <row r="393">
+      <c r="C393" s="60"/>
+    </row>
+    <row r="394">
+      <c r="C394" s="60"/>
+    </row>
+    <row r="395">
+      <c r="C395" s="60"/>
+    </row>
+    <row r="396">
+      <c r="C396" s="60"/>
+    </row>
+    <row r="397">
+      <c r="C397" s="60"/>
+    </row>
+    <row r="398">
+      <c r="C398" s="60"/>
+    </row>
+    <row r="399">
+      <c r="C399" s="60"/>
+    </row>
+    <row r="400">
+      <c r="C400" s="60"/>
+    </row>
+    <row r="401">
+      <c r="C401" s="60"/>
+    </row>
+    <row r="402">
+      <c r="C402" s="60"/>
+    </row>
+    <row r="403">
+      <c r="C403" s="60"/>
+    </row>
+    <row r="404">
+      <c r="C404" s="60"/>
+    </row>
+    <row r="405">
+      <c r="C405" s="60"/>
+    </row>
+    <row r="406">
+      <c r="C406" s="60"/>
+    </row>
+    <row r="407">
+      <c r="C407" s="60"/>
+    </row>
+    <row r="408">
+      <c r="C408" s="60"/>
+    </row>
+    <row r="409">
+      <c r="C409" s="60"/>
+    </row>
+    <row r="410">
+      <c r="C410" s="60"/>
+    </row>
+    <row r="411">
+      <c r="C411" s="60"/>
+    </row>
+    <row r="412">
+      <c r="C412" s="60"/>
+    </row>
+    <row r="413">
+      <c r="C413" s="60"/>
+    </row>
+    <row r="414">
+      <c r="C414" s="60"/>
+    </row>
+    <row r="415">
+      <c r="C415" s="60"/>
+    </row>
+    <row r="416">
+      <c r="C416" s="60"/>
+    </row>
+    <row r="417">
+      <c r="C417" s="60"/>
+    </row>
+    <row r="418">
+      <c r="C418" s="60"/>
+    </row>
+    <row r="419">
+      <c r="C419" s="60"/>
+    </row>
+    <row r="420">
+      <c r="C420" s="60"/>
+    </row>
+    <row r="421">
+      <c r="C421" s="60"/>
+    </row>
+    <row r="422">
+      <c r="C422" s="60"/>
+    </row>
+    <row r="423">
+      <c r="C423" s="60"/>
+    </row>
+    <row r="424">
+      <c r="C424" s="60"/>
+    </row>
+    <row r="425">
+      <c r="C425" s="60"/>
+    </row>
+    <row r="426">
+      <c r="C426" s="60"/>
+    </row>
+    <row r="427">
+      <c r="C427" s="60"/>
+    </row>
+    <row r="428">
+      <c r="C428" s="60"/>
+    </row>
+    <row r="429">
+      <c r="C429" s="60"/>
+    </row>
+    <row r="430">
+      <c r="C430" s="60"/>
+    </row>
+    <row r="431">
+      <c r="C431" s="60"/>
+    </row>
+    <row r="432">
+      <c r="C432" s="60"/>
+    </row>
+    <row r="433">
+      <c r="C433" s="60"/>
+    </row>
+    <row r="434">
+      <c r="C434" s="60"/>
+    </row>
+    <row r="435">
+      <c r="C435" s="60"/>
+    </row>
+    <row r="436">
+      <c r="C436" s="60"/>
+    </row>
+    <row r="437">
+      <c r="C437" s="60"/>
+    </row>
+    <row r="438">
+      <c r="C438" s="60"/>
+    </row>
+    <row r="439">
+      <c r="C439" s="60"/>
+    </row>
+    <row r="440">
+      <c r="C440" s="60"/>
+    </row>
+    <row r="441">
+      <c r="C441" s="60"/>
+    </row>
+    <row r="442">
+      <c r="C442" s="60"/>
+    </row>
+    <row r="443">
+      <c r="C443" s="60"/>
+    </row>
+    <row r="444">
+      <c r="C444" s="60"/>
+    </row>
+    <row r="445">
+      <c r="C445" s="60"/>
+    </row>
+    <row r="446">
+      <c r="C446" s="60"/>
+    </row>
+    <row r="447">
+      <c r="C447" s="60"/>
+    </row>
+    <row r="448">
+      <c r="C448" s="60"/>
+    </row>
+    <row r="449">
+      <c r="C449" s="60"/>
+    </row>
+    <row r="450">
+      <c r="C450" s="60"/>
+    </row>
+    <row r="451">
+      <c r="C451" s="60"/>
+    </row>
+    <row r="452">
+      <c r="C452" s="60"/>
+    </row>
+    <row r="453">
+      <c r="C453" s="60"/>
+    </row>
+    <row r="454">
+      <c r="C454" s="60"/>
+    </row>
+    <row r="455">
+      <c r="C455" s="60"/>
+    </row>
+    <row r="456">
+      <c r="C456" s="60"/>
+    </row>
+    <row r="457">
+      <c r="C457" s="60"/>
+    </row>
+    <row r="458">
+      <c r="C458" s="60"/>
+    </row>
+    <row r="459">
+      <c r="C459" s="60"/>
+    </row>
+    <row r="460">
+      <c r="C460" s="60"/>
+    </row>
+    <row r="461">
+      <c r="C461" s="60"/>
+    </row>
+    <row r="462">
+      <c r="C462" s="60"/>
+    </row>
+    <row r="463">
+      <c r="C463" s="60"/>
+    </row>
+    <row r="464">
+      <c r="C464" s="60"/>
+    </row>
+    <row r="465">
+      <c r="C465" s="60"/>
+    </row>
+    <row r="466">
+      <c r="C466" s="60"/>
+    </row>
+    <row r="467">
+      <c r="C467" s="60"/>
+    </row>
+    <row r="468">
+      <c r="C468" s="60"/>
+    </row>
+    <row r="469">
+      <c r="C469" s="60"/>
+    </row>
+    <row r="470">
+      <c r="C470" s="60"/>
+    </row>
+    <row r="471">
+      <c r="C471" s="60"/>
+    </row>
+    <row r="472">
+      <c r="C472" s="60"/>
+    </row>
+    <row r="473">
+      <c r="C473" s="60"/>
+    </row>
+    <row r="474">
+      <c r="C474" s="60"/>
+    </row>
+    <row r="475">
+      <c r="C475" s="60"/>
+    </row>
+    <row r="476">
+      <c r="C476" s="60"/>
+    </row>
+    <row r="477">
+      <c r="C477" s="60"/>
+    </row>
+    <row r="478">
+      <c r="C478" s="60"/>
+    </row>
+    <row r="479">
+      <c r="C479" s="60"/>
+    </row>
+    <row r="480">
+      <c r="C480" s="60"/>
+    </row>
+    <row r="481">
+      <c r="C481" s="60"/>
+    </row>
+    <row r="482">
+      <c r="C482" s="60"/>
+    </row>
+    <row r="483">
+      <c r="C483" s="60"/>
+    </row>
+    <row r="484">
+      <c r="C484" s="60"/>
+    </row>
+    <row r="485">
+      <c r="C485" s="60"/>
+    </row>
+    <row r="486">
+      <c r="C486" s="60"/>
+    </row>
+    <row r="487">
+      <c r="C487" s="60"/>
+    </row>
+    <row r="488">
+      <c r="C488" s="60"/>
+    </row>
+    <row r="489">
+      <c r="C489" s="60"/>
+    </row>
+    <row r="490">
+      <c r="C490" s="60"/>
+    </row>
+    <row r="491">
+      <c r="C491" s="60"/>
+    </row>
+    <row r="492">
+      <c r="C492" s="60"/>
+    </row>
+    <row r="493">
+      <c r="C493" s="60"/>
+    </row>
+    <row r="494">
+      <c r="C494" s="60"/>
+    </row>
+    <row r="495">
+      <c r="C495" s="60"/>
+    </row>
+    <row r="496">
+      <c r="C496" s="60"/>
+    </row>
+    <row r="497">
+      <c r="C497" s="60"/>
+    </row>
+    <row r="498">
+      <c r="C498" s="60"/>
+    </row>
+    <row r="499">
+      <c r="C499" s="60"/>
+    </row>
+    <row r="500">
+      <c r="C500" s="60"/>
+    </row>
+    <row r="501">
+      <c r="C501" s="60"/>
+    </row>
+    <row r="502">
+      <c r="C502" s="60"/>
+    </row>
+    <row r="503">
+      <c r="C503" s="60"/>
+    </row>
+    <row r="504">
+      <c r="C504" s="60"/>
+    </row>
+    <row r="505">
+      <c r="C505" s="60"/>
+    </row>
+    <row r="506">
+      <c r="C506" s="60"/>
+    </row>
+    <row r="507">
+      <c r="C507" s="60"/>
+    </row>
+    <row r="508">
+      <c r="C508" s="60"/>
+    </row>
+    <row r="509">
+      <c r="C509" s="60"/>
+    </row>
+    <row r="510">
+      <c r="C510" s="60"/>
+    </row>
+    <row r="511">
+      <c r="C511" s="60"/>
+    </row>
+    <row r="512">
+      <c r="C512" s="60"/>
+    </row>
+    <row r="513">
+      <c r="C513" s="60"/>
+    </row>
+    <row r="514">
+      <c r="C514" s="60"/>
+    </row>
+    <row r="515">
+      <c r="C515" s="60"/>
+    </row>
+    <row r="516">
+      <c r="C516" s="60"/>
+    </row>
+    <row r="517">
+      <c r="C517" s="60"/>
+    </row>
+    <row r="518">
+      <c r="C518" s="60"/>
+    </row>
+    <row r="519">
+      <c r="C519" s="60"/>
+    </row>
+    <row r="520">
+      <c r="C520" s="60"/>
+    </row>
+    <row r="521">
+      <c r="C521" s="60"/>
+    </row>
+    <row r="522">
+      <c r="C522" s="60"/>
+    </row>
+    <row r="523">
+      <c r="C523" s="60"/>
+    </row>
+    <row r="524">
+      <c r="C524" s="60"/>
+    </row>
+    <row r="525">
+      <c r="C525" s="60"/>
+    </row>
+    <row r="526">
+      <c r="C526" s="60"/>
+    </row>
+    <row r="527">
+      <c r="C527" s="60"/>
+    </row>
+    <row r="528">
+      <c r="C528" s="60"/>
+    </row>
+    <row r="529">
+      <c r="C529" s="60"/>
+    </row>
+    <row r="530">
+      <c r="C530" s="60"/>
+    </row>
+    <row r="531">
+      <c r="C531" s="60"/>
+    </row>
+    <row r="532">
+      <c r="C532" s="60"/>
+    </row>
+    <row r="533">
+      <c r="C533" s="60"/>
+    </row>
+    <row r="534">
+      <c r="C534" s="60"/>
+    </row>
+    <row r="535">
+      <c r="C535" s="60"/>
+    </row>
+    <row r="536">
+      <c r="C536" s="60"/>
+    </row>
+    <row r="537">
+      <c r="C537" s="60"/>
+    </row>
+    <row r="538">
+      <c r="C538" s="60"/>
+    </row>
+    <row r="539">
+      <c r="C539" s="60"/>
+    </row>
+    <row r="540">
+      <c r="C540" s="60"/>
+    </row>
+    <row r="541">
+      <c r="C541" s="60"/>
+    </row>
+    <row r="542">
+      <c r="C542" s="60"/>
+    </row>
+    <row r="543">
+      <c r="C543" s="60"/>
+    </row>
+    <row r="544">
+      <c r="C544" s="60"/>
+    </row>
+    <row r="545">
+      <c r="C545" s="60"/>
+    </row>
+    <row r="546">
+      <c r="C546" s="60"/>
+    </row>
+    <row r="547">
+      <c r="C547" s="60"/>
+    </row>
+    <row r="548">
+      <c r="C548" s="60"/>
+    </row>
+    <row r="549">
+      <c r="C549" s="60"/>
+    </row>
+    <row r="550">
+      <c r="C550" s="60"/>
+    </row>
+    <row r="551">
+      <c r="C551" s="60"/>
+    </row>
+    <row r="552">
+      <c r="C552" s="60"/>
+    </row>
+    <row r="553">
+      <c r="C553" s="60"/>
+    </row>
+    <row r="554">
+      <c r="C554" s="60"/>
+    </row>
+    <row r="555">
+      <c r="C555" s="60"/>
+    </row>
+    <row r="556">
+      <c r="C556" s="60"/>
+    </row>
+    <row r="557">
+      <c r="C557" s="60"/>
+    </row>
+    <row r="558">
+      <c r="C558" s="60"/>
+    </row>
+    <row r="559">
+      <c r="C559" s="60"/>
+    </row>
+    <row r="560">
+      <c r="C560" s="60"/>
+    </row>
+    <row r="561">
+      <c r="C561" s="60"/>
+    </row>
+    <row r="562">
+      <c r="C562" s="60"/>
+    </row>
+    <row r="563">
+      <c r="C563" s="60"/>
+    </row>
+    <row r="564">
+      <c r="C564" s="60"/>
+    </row>
+    <row r="565">
+      <c r="C565" s="60"/>
+    </row>
+    <row r="566">
+      <c r="C566" s="60"/>
+    </row>
+    <row r="567">
+      <c r="C567" s="60"/>
+    </row>
+    <row r="568">
+      <c r="C568" s="60"/>
+    </row>
+    <row r="569">
+      <c r="C569" s="60"/>
+    </row>
+    <row r="570">
+      <c r="C570" s="60"/>
+    </row>
+    <row r="571">
+      <c r="C571" s="60"/>
+    </row>
+    <row r="572">
+      <c r="C572" s="60"/>
+    </row>
+    <row r="573">
+      <c r="C573" s="60"/>
+    </row>
+    <row r="574">
+      <c r="C574" s="60"/>
+    </row>
+    <row r="575">
+      <c r="C575" s="60"/>
+    </row>
+    <row r="576">
+      <c r="C576" s="60"/>
+    </row>
+    <row r="577">
+      <c r="C577" s="60"/>
+    </row>
+    <row r="578">
+      <c r="C578" s="60"/>
+    </row>
+    <row r="579">
+      <c r="C579" s="60"/>
+    </row>
+    <row r="580">
+      <c r="C580" s="60"/>
+    </row>
+    <row r="581">
+      <c r="C581" s="60"/>
+    </row>
+    <row r="582">
+      <c r="C582" s="60"/>
+    </row>
+    <row r="583">
+      <c r="C583" s="60"/>
+    </row>
+    <row r="584">
+      <c r="C584" s="60"/>
+    </row>
+    <row r="585">
+      <c r="C585" s="60"/>
+    </row>
+    <row r="586">
+      <c r="C586" s="60"/>
+    </row>
+    <row r="587">
+      <c r="C587" s="60"/>
+    </row>
+    <row r="588">
+      <c r="C588" s="60"/>
+    </row>
+    <row r="589">
+      <c r="C589" s="60"/>
+    </row>
+    <row r="590">
+      <c r="C590" s="60"/>
+    </row>
+    <row r="591">
+      <c r="C591" s="60"/>
+    </row>
+    <row r="592">
+      <c r="C592" s="60"/>
+    </row>
+    <row r="593">
+      <c r="C593" s="60"/>
+    </row>
+    <row r="594">
+      <c r="C594" s="60"/>
+    </row>
+    <row r="595">
+      <c r="C595" s="60"/>
+    </row>
+    <row r="596">
+      <c r="C596" s="60"/>
+    </row>
+    <row r="597">
+      <c r="C597" s="60"/>
+    </row>
+    <row r="598">
+      <c r="C598" s="60"/>
+    </row>
+    <row r="599">
+      <c r="C599" s="60"/>
+    </row>
+    <row r="600">
+      <c r="C600" s="60"/>
+    </row>
+    <row r="601">
+      <c r="C601" s="60"/>
+    </row>
+    <row r="602">
+      <c r="C602" s="60"/>
+    </row>
+    <row r="603">
+      <c r="C603" s="60"/>
+    </row>
+    <row r="604">
+      <c r="C604" s="60"/>
+    </row>
+    <row r="605">
+      <c r="C605" s="60"/>
+    </row>
+    <row r="606">
+      <c r="C606" s="60"/>
+    </row>
+    <row r="607">
+      <c r="C607" s="60"/>
+    </row>
+    <row r="608">
+      <c r="C608" s="60"/>
+    </row>
+    <row r="609">
+      <c r="C609" s="60"/>
+    </row>
+    <row r="610">
+      <c r="C610" s="60"/>
+    </row>
+    <row r="611">
+      <c r="C611" s="60"/>
+    </row>
+    <row r="612">
+      <c r="C612" s="60"/>
+    </row>
+    <row r="613">
+      <c r="C613" s="60"/>
+    </row>
+    <row r="614">
+      <c r="C614" s="60"/>
+    </row>
+    <row r="615">
+      <c r="C615" s="60"/>
+    </row>
+    <row r="616">
+      <c r="C616" s="60"/>
+    </row>
+    <row r="617">
+      <c r="C617" s="60"/>
+    </row>
+    <row r="618">
+      <c r="C618" s="60"/>
+    </row>
+    <row r="619">
+      <c r="C619" s="60"/>
+    </row>
+    <row r="620">
+      <c r="C620" s="60"/>
+    </row>
+    <row r="621">
+      <c r="C621" s="60"/>
+    </row>
+    <row r="622">
+      <c r="C622" s="60"/>
+    </row>
+    <row r="623">
+      <c r="C623" s="60"/>
+    </row>
+    <row r="624">
+      <c r="C624" s="60"/>
+    </row>
+    <row r="625">
+      <c r="C625" s="60"/>
+    </row>
+    <row r="626">
+      <c r="C626" s="60"/>
+    </row>
+    <row r="627">
+      <c r="C627" s="60"/>
+    </row>
+    <row r="628">
+      <c r="C628" s="60"/>
+    </row>
+    <row r="629">
+      <c r="C629" s="60"/>
+    </row>
+    <row r="630">
+      <c r="C630" s="60"/>
+    </row>
+    <row r="631">
+      <c r="C631" s="60"/>
+    </row>
+    <row r="632">
+      <c r="C632" s="60"/>
+    </row>
+    <row r="633">
+      <c r="C633" s="60"/>
+    </row>
+    <row r="634">
+      <c r="C634" s="60"/>
+    </row>
+    <row r="635">
+      <c r="C635" s="60"/>
+    </row>
+    <row r="636">
+      <c r="C636" s="60"/>
+    </row>
+    <row r="637">
+      <c r="C637" s="60"/>
+    </row>
+    <row r="638">
+      <c r="C638" s="60"/>
+    </row>
+    <row r="639">
+      <c r="C639" s="60"/>
+    </row>
+    <row r="640">
+      <c r="C640" s="60"/>
+    </row>
+    <row r="641">
+      <c r="C641" s="60"/>
+    </row>
+    <row r="642">
+      <c r="C642" s="60"/>
+    </row>
+    <row r="643">
+      <c r="C643" s="60"/>
+    </row>
+    <row r="644">
+      <c r="C644" s="60"/>
+    </row>
+    <row r="645">
+      <c r="C645" s="60"/>
+    </row>
+    <row r="646">
+      <c r="C646" s="60"/>
+    </row>
+    <row r="647">
+      <c r="C647" s="60"/>
+    </row>
+    <row r="648">
+      <c r="C648" s="60"/>
+    </row>
+    <row r="649">
+      <c r="C649" s="60"/>
+    </row>
+    <row r="650">
+      <c r="C650" s="60"/>
+    </row>
+    <row r="651">
+      <c r="C651" s="60"/>
+    </row>
+    <row r="652">
+      <c r="C652" s="60"/>
+    </row>
+    <row r="653">
+      <c r="C653" s="60"/>
+    </row>
+    <row r="654">
+      <c r="C654" s="60"/>
+    </row>
+    <row r="655">
+      <c r="C655" s="60"/>
+    </row>
+    <row r="656">
+      <c r="C656" s="60"/>
+    </row>
+    <row r="657">
+      <c r="C657" s="60"/>
+    </row>
+    <row r="658">
+      <c r="C658" s="60"/>
+    </row>
+    <row r="659">
+      <c r="C659" s="60"/>
+    </row>
+    <row r="660">
+      <c r="C660" s="60"/>
+    </row>
+    <row r="661">
+      <c r="C661" s="60"/>
+    </row>
+    <row r="662">
+      <c r="C662" s="60"/>
+    </row>
+    <row r="663">
+      <c r="C663" s="60"/>
+    </row>
+    <row r="664">
+      <c r="C664" s="60"/>
+    </row>
+    <row r="665">
+      <c r="C665" s="60"/>
+    </row>
+    <row r="666">
+      <c r="C666" s="60"/>
+    </row>
+    <row r="667">
+      <c r="C667" s="60"/>
+    </row>
+    <row r="668">
+      <c r="C668" s="60"/>
+    </row>
+    <row r="669">
+      <c r="C669" s="60"/>
+    </row>
+    <row r="670">
+      <c r="C670" s="60"/>
+    </row>
+    <row r="671">
+      <c r="C671" s="60"/>
+    </row>
+    <row r="672">
+      <c r="C672" s="60"/>
+    </row>
+    <row r="673">
+      <c r="C673" s="60"/>
+    </row>
+    <row r="674">
+      <c r="C674" s="60"/>
+    </row>
+    <row r="675">
+      <c r="C675" s="60"/>
+    </row>
+    <row r="676">
+      <c r="C676" s="60"/>
+    </row>
+    <row r="677">
+      <c r="C677" s="60"/>
+    </row>
+    <row r="678">
+      <c r="C678" s="60"/>
+    </row>
+    <row r="679">
+      <c r="C679" s="60"/>
+    </row>
+    <row r="680">
+      <c r="C680" s="60"/>
+    </row>
+    <row r="681">
+      <c r="C681" s="60"/>
+    </row>
+    <row r="682">
+      <c r="C682" s="60"/>
+    </row>
+    <row r="683">
+      <c r="C683" s="60"/>
+    </row>
+    <row r="684">
+      <c r="C684" s="60"/>
+    </row>
+    <row r="685">
+      <c r="C685" s="60"/>
+    </row>
+    <row r="686">
+      <c r="C686" s="60"/>
+    </row>
+    <row r="687">
+      <c r="C687" s="60"/>
+    </row>
+    <row r="688">
+      <c r="C688" s="60"/>
+    </row>
+    <row r="689">
+      <c r="C689" s="60"/>
+    </row>
+    <row r="690">
+      <c r="C690" s="60"/>
+    </row>
+    <row r="691">
+      <c r="C691" s="60"/>
+    </row>
+    <row r="692">
+      <c r="C692" s="60"/>
+    </row>
+    <row r="693">
+      <c r="C693" s="60"/>
+    </row>
+    <row r="694">
+      <c r="C694" s="60"/>
+    </row>
+    <row r="695">
+      <c r="C695" s="60"/>
+    </row>
+    <row r="696">
+      <c r="C696" s="60"/>
+    </row>
+    <row r="697">
+      <c r="C697" s="60"/>
+    </row>
+    <row r="698">
+      <c r="C698" s="60"/>
+    </row>
+    <row r="699">
+      <c r="C699" s="60"/>
+    </row>
+    <row r="700">
+      <c r="C700" s="60"/>
+    </row>
+    <row r="701">
+      <c r="C701" s="60"/>
+    </row>
+    <row r="702">
+      <c r="C702" s="60"/>
+    </row>
+    <row r="703">
+      <c r="C703" s="60"/>
+    </row>
+    <row r="704">
+      <c r="C704" s="60"/>
+    </row>
+    <row r="705">
+      <c r="C705" s="60"/>
+    </row>
+    <row r="706">
+      <c r="C706" s="60"/>
+    </row>
+    <row r="707">
+      <c r="C707" s="60"/>
+    </row>
+    <row r="708">
+      <c r="C708" s="60"/>
+    </row>
+    <row r="709">
+      <c r="C709" s="60"/>
+    </row>
+    <row r="710">
+      <c r="C710" s="60"/>
+    </row>
+    <row r="711">
+      <c r="C711" s="60"/>
+    </row>
+    <row r="712">
+      <c r="C712" s="60"/>
+    </row>
+    <row r="713">
+      <c r="C713" s="60"/>
+    </row>
+    <row r="714">
+      <c r="C714" s="60"/>
+    </row>
+    <row r="715">
+      <c r="C715" s="60"/>
+    </row>
+    <row r="716">
+      <c r="C716" s="60"/>
+    </row>
+    <row r="717">
+      <c r="C717" s="60"/>
+    </row>
+    <row r="718">
+      <c r="C718" s="60"/>
+    </row>
+    <row r="719">
+      <c r="C719" s="60"/>
+    </row>
+    <row r="720">
+      <c r="C720" s="60"/>
+    </row>
+    <row r="721">
+      <c r="C721" s="60"/>
+    </row>
+    <row r="722">
+      <c r="C722" s="60"/>
+    </row>
+    <row r="723">
+      <c r="C723" s="60"/>
+    </row>
+    <row r="724">
+      <c r="C724" s="60"/>
+    </row>
+    <row r="725">
+      <c r="C725" s="60"/>
+    </row>
+    <row r="726">
+      <c r="C726" s="60"/>
+    </row>
+    <row r="727">
+      <c r="C727" s="60"/>
+    </row>
+    <row r="728">
+      <c r="C728" s="60"/>
+    </row>
+    <row r="729">
+      <c r="C729" s="60"/>
+    </row>
+    <row r="730">
+      <c r="C730" s="60"/>
+    </row>
+    <row r="731">
+      <c r="C731" s="60"/>
+    </row>
+    <row r="732">
+      <c r="C732" s="60"/>
+    </row>
+    <row r="733">
+      <c r="C733" s="60"/>
+    </row>
+    <row r="734">
+      <c r="C734" s="60"/>
+    </row>
+    <row r="735">
+      <c r="C735" s="60"/>
+    </row>
+    <row r="736">
+      <c r="C736" s="60"/>
+    </row>
+    <row r="737">
+      <c r="C737" s="60"/>
+    </row>
+    <row r="738">
+      <c r="C738" s="60"/>
+    </row>
+    <row r="739">
+      <c r="C739" s="60"/>
+    </row>
+    <row r="740">
+      <c r="C740" s="60"/>
+    </row>
+    <row r="741">
+      <c r="C741" s="60"/>
+    </row>
+    <row r="742">
+      <c r="C742" s="60"/>
+    </row>
+    <row r="743">
+      <c r="C743" s="60"/>
+    </row>
+    <row r="744">
+      <c r="C744" s="60"/>
+    </row>
+    <row r="745">
+      <c r="C745" s="60"/>
+    </row>
+    <row r="746">
+      <c r="C746" s="60"/>
+    </row>
+    <row r="747">
+      <c r="C747" s="60"/>
+    </row>
+    <row r="748">
+      <c r="C748" s="60"/>
+    </row>
+    <row r="749">
+      <c r="C749" s="60"/>
+    </row>
+    <row r="750">
+      <c r="C750" s="60"/>
+    </row>
+    <row r="751">
+      <c r="C751" s="60"/>
+    </row>
+    <row r="752">
+      <c r="C752" s="60"/>
+    </row>
+    <row r="753">
+      <c r="C753" s="60"/>
+    </row>
+    <row r="754">
+      <c r="C754" s="60"/>
+    </row>
+    <row r="755">
+      <c r="C755" s="60"/>
+    </row>
+    <row r="756">
+      <c r="C756" s="60"/>
+    </row>
+    <row r="757">
+      <c r="C757" s="60"/>
+    </row>
+    <row r="758">
+      <c r="C758" s="60"/>
+    </row>
+    <row r="759">
+      <c r="C759" s="60"/>
+    </row>
+    <row r="760">
+      <c r="C760" s="60"/>
+    </row>
+    <row r="761">
+      <c r="C761" s="60"/>
+    </row>
+    <row r="762">
+      <c r="C762" s="60"/>
+    </row>
+    <row r="763">
+      <c r="C763" s="60"/>
+    </row>
+    <row r="764">
+      <c r="C764" s="60"/>
+    </row>
+    <row r="765">
+      <c r="C765" s="60"/>
+    </row>
+    <row r="766">
+      <c r="C766" s="60"/>
+    </row>
+    <row r="767">
+      <c r="C767" s="60"/>
+    </row>
+    <row r="768">
+      <c r="C768" s="60"/>
+    </row>
+    <row r="769">
+      <c r="C769" s="60"/>
+    </row>
+    <row r="770">
+      <c r="C770" s="60"/>
+    </row>
+    <row r="771">
+      <c r="C771" s="60"/>
+    </row>
+    <row r="772">
+      <c r="C772" s="60"/>
+    </row>
+    <row r="773">
+      <c r="C773" s="60"/>
+    </row>
+    <row r="774">
+      <c r="C774" s="60"/>
+    </row>
+    <row r="775">
+      <c r="C775" s="60"/>
+    </row>
+    <row r="776">
+      <c r="C776" s="60"/>
+    </row>
+    <row r="777">
+      <c r="C777" s="60"/>
+    </row>
+    <row r="778">
+      <c r="C778" s="60"/>
+    </row>
+    <row r="779">
+      <c r="C779" s="60"/>
+    </row>
+    <row r="780">
+      <c r="C780" s="60"/>
+    </row>
+    <row r="781">
+      <c r="C781" s="60"/>
+    </row>
+    <row r="782">
+      <c r="C782" s="60"/>
+    </row>
+    <row r="783">
+      <c r="C783" s="60"/>
+    </row>
+    <row r="784">
+      <c r="C784" s="60"/>
+    </row>
+    <row r="785">
+      <c r="C785" s="60"/>
+    </row>
+    <row r="786">
+      <c r="C786" s="60"/>
+    </row>
+    <row r="787">
+      <c r="C787" s="60"/>
+    </row>
+    <row r="788">
+      <c r="C788" s="60"/>
+    </row>
+    <row r="789">
+      <c r="C789" s="60"/>
+    </row>
+    <row r="790">
+      <c r="C790" s="60"/>
+    </row>
+    <row r="791">
+      <c r="C791" s="60"/>
+    </row>
+    <row r="792">
+      <c r="C792" s="60"/>
+    </row>
+    <row r="793">
+      <c r="C793" s="60"/>
+    </row>
+    <row r="794">
+      <c r="C794" s="60"/>
+    </row>
+    <row r="795">
+      <c r="C795" s="60"/>
+    </row>
+    <row r="796">
+      <c r="C796" s="60"/>
+    </row>
+    <row r="797">
+      <c r="C797" s="60"/>
+    </row>
+    <row r="798">
+      <c r="C798" s="60"/>
+    </row>
+    <row r="799">
+      <c r="C799" s="60"/>
+    </row>
+    <row r="800">
+      <c r="C800" s="60"/>
+    </row>
+    <row r="801">
+      <c r="C801" s="60"/>
+    </row>
+    <row r="802">
+      <c r="C802" s="60"/>
+    </row>
+    <row r="803">
+      <c r="C803" s="60"/>
+    </row>
+    <row r="804">
+      <c r="C804" s="60"/>
+    </row>
+    <row r="805">
+      <c r="C805" s="60"/>
+    </row>
+    <row r="806">
+      <c r="C806" s="60"/>
+    </row>
+    <row r="807">
+      <c r="C807" s="60"/>
+    </row>
+    <row r="808">
+      <c r="C808" s="60"/>
+    </row>
+    <row r="809">
+      <c r="C809" s="60"/>
+    </row>
+    <row r="810">
+      <c r="C810" s="60"/>
+    </row>
+    <row r="811">
+      <c r="C811" s="60"/>
+    </row>
+    <row r="812">
+      <c r="C812" s="60"/>
+    </row>
+    <row r="813">
+      <c r="C813" s="60"/>
+    </row>
+    <row r="814">
+      <c r="C814" s="60"/>
+    </row>
+    <row r="815">
+      <c r="C815" s="60"/>
+    </row>
+    <row r="816">
+      <c r="C816" s="60"/>
+    </row>
+    <row r="817">
+      <c r="C817" s="60"/>
+    </row>
+    <row r="818">
+      <c r="C818" s="60"/>
+    </row>
+    <row r="819">
+      <c r="C819" s="60"/>
+    </row>
+    <row r="820">
+      <c r="C820" s="60"/>
+    </row>
+    <row r="821">
+      <c r="C821" s="60"/>
+    </row>
+    <row r="822">
+      <c r="C822" s="60"/>
+    </row>
+    <row r="823">
+      <c r="C823" s="60"/>
+    </row>
+    <row r="824">
+      <c r="C824" s="60"/>
+    </row>
+    <row r="825">
+      <c r="C825" s="60"/>
+    </row>
+    <row r="826">
+      <c r="C826" s="60"/>
+    </row>
+    <row r="827">
+      <c r="C827" s="60"/>
+    </row>
+    <row r="828">
+      <c r="C828" s="60"/>
+    </row>
+    <row r="829">
+      <c r="C829" s="60"/>
+    </row>
+    <row r="830">
+      <c r="C830" s="60"/>
+    </row>
+    <row r="831">
+      <c r="C831" s="60"/>
+    </row>
+    <row r="832">
+      <c r="C832" s="60"/>
+    </row>
+    <row r="833">
+      <c r="C833" s="60"/>
+    </row>
+    <row r="834">
+      <c r="C834" s="60"/>
+    </row>
+    <row r="835">
+      <c r="C835" s="60"/>
+    </row>
+    <row r="836">
+      <c r="C836" s="60"/>
+    </row>
+    <row r="837">
+      <c r="C837" s="60"/>
+    </row>
+    <row r="838">
+      <c r="C838" s="60"/>
+    </row>
+    <row r="839">
+      <c r="C839" s="60"/>
+    </row>
+    <row r="840">
+      <c r="C840" s="60"/>
+    </row>
+    <row r="841">
+      <c r="C841" s="60"/>
+    </row>
+    <row r="842">
+      <c r="C842" s="60"/>
+    </row>
+    <row r="843">
+      <c r="C843" s="60"/>
+    </row>
+    <row r="844">
+      <c r="C844" s="60"/>
+    </row>
+    <row r="845">
+      <c r="C845" s="60"/>
+    </row>
+    <row r="846">
+      <c r="C846" s="60"/>
+    </row>
+    <row r="847">
+      <c r="C847" s="60"/>
+    </row>
+    <row r="848">
+      <c r="C848" s="60"/>
+    </row>
+    <row r="849">
+      <c r="C849" s="60"/>
+    </row>
+    <row r="850">
+      <c r="C850" s="60"/>
+    </row>
+    <row r="851">
+      <c r="C851" s="60"/>
+    </row>
+    <row r="852">
+      <c r="C852" s="60"/>
+    </row>
+    <row r="853">
+      <c r="C853" s="60"/>
+    </row>
+    <row r="854">
+      <c r="C854" s="60"/>
+    </row>
+    <row r="855">
+      <c r="C855" s="60"/>
+    </row>
+    <row r="856">
+      <c r="C856" s="60"/>
+    </row>
+    <row r="857">
+      <c r="C857" s="60"/>
+    </row>
+    <row r="858">
+      <c r="C858" s="60"/>
+    </row>
+    <row r="859">
+      <c r="C859" s="60"/>
+    </row>
+    <row r="860">
+      <c r="C860" s="60"/>
+    </row>
+    <row r="861">
+      <c r="C861" s="60"/>
+    </row>
+    <row r="862">
+      <c r="C862" s="60"/>
+    </row>
+    <row r="863">
+      <c r="C863" s="60"/>
+    </row>
+    <row r="864">
+      <c r="C864" s="60"/>
+    </row>
+    <row r="865">
+      <c r="C865" s="60"/>
+    </row>
+    <row r="866">
+      <c r="C866" s="60"/>
+    </row>
+    <row r="867">
+      <c r="C867" s="60"/>
+    </row>
+    <row r="868">
+      <c r="C868" s="60"/>
+    </row>
+    <row r="869">
+      <c r="C869" s="60"/>
+    </row>
+    <row r="870">
+      <c r="C870" s="60"/>
+    </row>
+    <row r="871">
+      <c r="C871" s="60"/>
+    </row>
+    <row r="872">
+      <c r="C872" s="60"/>
+    </row>
+    <row r="873">
+      <c r="C873" s="60"/>
+    </row>
+    <row r="874">
+      <c r="C874" s="60"/>
+    </row>
+    <row r="875">
+      <c r="C875" s="60"/>
+    </row>
+    <row r="876">
+      <c r="C876" s="60"/>
+    </row>
+    <row r="877">
+      <c r="C877" s="60"/>
+    </row>
+    <row r="878">
+      <c r="C878" s="60"/>
+    </row>
+    <row r="879">
+      <c r="C879" s="60"/>
+    </row>
+    <row r="880">
+      <c r="C880" s="60"/>
+    </row>
+    <row r="881">
+      <c r="C881" s="60"/>
+    </row>
+    <row r="882">
+      <c r="C882" s="60"/>
+    </row>
+    <row r="883">
+      <c r="C883" s="60"/>
+    </row>
+    <row r="884">
+      <c r="C884" s="60"/>
+    </row>
+    <row r="885">
+      <c r="C885" s="60"/>
+    </row>
+    <row r="886">
+      <c r="C886" s="60"/>
+    </row>
+    <row r="887">
+      <c r="C887" s="60"/>
+    </row>
+    <row r="888">
+      <c r="C888" s="60"/>
+    </row>
+    <row r="889">
+      <c r="C889" s="60"/>
+    </row>
+    <row r="890">
+      <c r="C890" s="60"/>
+    </row>
+    <row r="891">
+      <c r="C891" s="60"/>
+    </row>
+    <row r="892">
+      <c r="C892" s="60"/>
+    </row>
+    <row r="893">
+      <c r="C893" s="60"/>
+    </row>
+    <row r="894">
+      <c r="C894" s="60"/>
+    </row>
+    <row r="895">
+      <c r="C895" s="60"/>
+    </row>
+    <row r="896">
+      <c r="C896" s="60"/>
+    </row>
+    <row r="897">
+      <c r="C897" s="60"/>
+    </row>
+    <row r="898">
+      <c r="C898" s="60"/>
+    </row>
+    <row r="899">
+      <c r="C899" s="60"/>
+    </row>
+    <row r="900">
+      <c r="C900" s="60"/>
+    </row>
+    <row r="901">
+      <c r="C901" s="60"/>
+    </row>
+    <row r="902">
+      <c r="C902" s="60"/>
+    </row>
+    <row r="903">
+      <c r="C903" s="60"/>
+    </row>
+    <row r="904">
+      <c r="C904" s="60"/>
+    </row>
+    <row r="905">
+      <c r="C905" s="60"/>
+    </row>
+    <row r="906">
+      <c r="C906" s="60"/>
+    </row>
+    <row r="907">
+      <c r="C907" s="60"/>
+    </row>
+    <row r="908">
+      <c r="C908" s="60"/>
+    </row>
+    <row r="909">
+      <c r="C909" s="60"/>
+    </row>
+    <row r="910">
+      <c r="C910" s="60"/>
+    </row>
+    <row r="911">
+      <c r="C911" s="60"/>
+    </row>
+    <row r="912">
+      <c r="C912" s="60"/>
+    </row>
+    <row r="913">
+      <c r="C913" s="60"/>
+    </row>
+    <row r="914">
+      <c r="C914" s="60"/>
+    </row>
+    <row r="915">
+      <c r="C915" s="60"/>
+    </row>
+    <row r="916">
+      <c r="C916" s="60"/>
+    </row>
+    <row r="917">
+      <c r="C917" s="60"/>
+    </row>
+    <row r="918">
+      <c r="C918" s="60"/>
+    </row>
+    <row r="919">
+      <c r="C919" s="60"/>
+    </row>
+    <row r="920">
+      <c r="C920" s="60"/>
+    </row>
+    <row r="921">
+      <c r="C921" s="60"/>
+    </row>
+    <row r="922">
+      <c r="C922" s="60"/>
+    </row>
+    <row r="923">
+      <c r="C923" s="60"/>
+    </row>
+    <row r="924">
+      <c r="C924" s="60"/>
+    </row>
+    <row r="925">
+      <c r="C925" s="60"/>
+    </row>
+    <row r="926">
+      <c r="C926" s="60"/>
+    </row>
+    <row r="927">
+      <c r="C927" s="60"/>
+    </row>
+    <row r="928">
+      <c r="C928" s="60"/>
+    </row>
+    <row r="929">
+      <c r="C929" s="60"/>
+    </row>
+    <row r="930">
+      <c r="C930" s="60"/>
+    </row>
+    <row r="931">
+      <c r="C931" s="60"/>
+    </row>
+    <row r="932">
+      <c r="C932" s="60"/>
+    </row>
+    <row r="933">
+      <c r="C933" s="60"/>
+    </row>
+    <row r="934">
+      <c r="C934" s="60"/>
+    </row>
+    <row r="935">
+      <c r="C935" s="60"/>
+    </row>
+    <row r="936">
+      <c r="C936" s="60"/>
+    </row>
+    <row r="937">
+      <c r="C937" s="60"/>
+    </row>
+    <row r="938">
+      <c r="C938" s="60"/>
+    </row>
+    <row r="939">
+      <c r="C939" s="60"/>
+    </row>
+    <row r="940">
+      <c r="C940" s="60"/>
+    </row>
+    <row r="941">
+      <c r="C941" s="60"/>
+    </row>
+    <row r="942">
+      <c r="C942" s="60"/>
+    </row>
+    <row r="943">
+      <c r="C943" s="60"/>
+    </row>
+    <row r="944">
+      <c r="C944" s="60"/>
+    </row>
+    <row r="945">
+      <c r="C945" s="60"/>
+    </row>
+    <row r="946">
+      <c r="C946" s="60"/>
+    </row>
+    <row r="947">
+      <c r="C947" s="60"/>
+    </row>
+    <row r="948">
+      <c r="C948" s="60"/>
+    </row>
+    <row r="949">
+      <c r="C949" s="60"/>
+    </row>
+    <row r="950">
+      <c r="C950" s="60"/>
+    </row>
+    <row r="951">
+      <c r="C951" s="60"/>
+    </row>
+    <row r="952">
+      <c r="C952" s="60"/>
+    </row>
+    <row r="953">
+      <c r="C953" s="60"/>
+    </row>
+    <row r="954">
+      <c r="C954" s="60"/>
+    </row>
+    <row r="955">
+      <c r="C955" s="60"/>
+    </row>
+    <row r="956">
+      <c r="C956" s="60"/>
+    </row>
+    <row r="957">
+      <c r="C957" s="60"/>
+    </row>
+    <row r="958">
+      <c r="C958" s="60"/>
+    </row>
+    <row r="959">
+      <c r="C959" s="60"/>
+    </row>
+    <row r="960">
+      <c r="C960" s="60"/>
+    </row>
+    <row r="961">
+      <c r="C961" s="60"/>
+    </row>
+    <row r="962">
+      <c r="C962" s="60"/>
+    </row>
+    <row r="963">
+      <c r="C963" s="60"/>
+    </row>
+    <row r="964">
+      <c r="C964" s="60"/>
+    </row>
+    <row r="965">
+      <c r="C965" s="60"/>
+    </row>
+    <row r="966">
+      <c r="C966" s="60"/>
+    </row>
+    <row r="967">
+      <c r="C967" s="60"/>
+    </row>
+    <row r="968">
+      <c r="C968" s="60"/>
+    </row>
+    <row r="969">
+      <c r="C969" s="60"/>
+    </row>
+    <row r="970">
+      <c r="C970" s="60"/>
+    </row>
+    <row r="971">
+      <c r="C971" s="60"/>
+    </row>
+    <row r="972">
+      <c r="C972" s="60"/>
+    </row>
+    <row r="973">
+      <c r="C973" s="60"/>
+    </row>
+    <row r="974">
+      <c r="C974" s="60"/>
+    </row>
+    <row r="975">
+      <c r="C975" s="60"/>
+    </row>
+    <row r="976">
+      <c r="C976" s="60"/>
+    </row>
+    <row r="977">
+      <c r="C977" s="60"/>
+    </row>
+    <row r="978">
+      <c r="C978" s="60"/>
+    </row>
+    <row r="979">
+      <c r="C979" s="60"/>
+    </row>
+    <row r="980">
+      <c r="C980" s="60"/>
+    </row>
+    <row r="981">
+      <c r="C981" s="60"/>
+    </row>
+    <row r="982">
+      <c r="C982" s="60"/>
+    </row>
+    <row r="983">
+      <c r="C983" s="60"/>
+    </row>
+    <row r="984">
+      <c r="C984" s="60"/>
+    </row>
+    <row r="985">
+      <c r="C985" s="60"/>
+    </row>
+    <row r="986">
+      <c r="C986" s="60"/>
+    </row>
+    <row r="987">
+      <c r="C987" s="60"/>
+    </row>
+    <row r="988">
+      <c r="C988" s="60"/>
+    </row>
+    <row r="989">
+      <c r="C989" s="60"/>
+    </row>
+    <row r="990">
+      <c r="C990" s="60"/>
+    </row>
+    <row r="991">
+      <c r="C991" s="60"/>
+    </row>
+    <row r="992">
+      <c r="C992" s="60"/>
+    </row>
+    <row r="993">
+      <c r="C993" s="60"/>
+    </row>
+    <row r="994">
+      <c r="C994" s="60"/>
+    </row>
+    <row r="995">
+      <c r="C995" s="60"/>
+    </row>
+    <row r="996">
+      <c r="C996" s="60"/>
+    </row>
+    <row r="997">
+      <c r="C997" s="60"/>
+    </row>
+    <row r="998">
+      <c r="C998" s="60"/>
+    </row>
+    <row r="999">
+      <c r="C999" s="60"/>
+    </row>
+    <row r="1000">
+      <c r="C1000" s="60"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
@@ -18572,854 +21797,854 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="56" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C1" s="56" t="s">
-        <v>1026</v>
+      <c r="A1" s="63" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1" s="63" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="64" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B2" s="64" t="s">
         <v>762</v>
       </c>
-      <c r="C2" s="57" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
+      <c r="C2" s="64" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
     </row>
     <row r="3">
-      <c r="A3" s="57" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B3" s="57" t="s">
+      <c r="A3" s="64" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B3" s="64" t="s">
         <v>758</v>
       </c>
-      <c r="C3" s="57" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="58"/>
+      <c r="C3" s="64" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B4" s="59" t="s">
+      <c r="A4" s="66" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B4" s="66" t="s">
         <v>737</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>1031</v>
+      <c r="C4" s="66" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B5" s="59" t="s">
+      <c r="A5" s="66" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B5" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="59" t="s">
-        <v>1032</v>
+      <c r="C5" s="66" t="s">
+        <v>1047</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B6" s="59" t="s">
+      <c r="A6" s="66" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B6" s="66" t="s">
         <v>740</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>1033</v>
+      <c r="C6" s="66" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B7" s="59" t="s">
+      <c r="A7" s="66" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="59" t="s">
-        <v>1034</v>
+      <c r="C7" s="66" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B8" s="59" t="s">
+      <c r="A8" s="66" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B8" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="C8" s="59" t="s">
-        <v>1028</v>
+      <c r="C8" s="66" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B9" s="59" t="s">
+      <c r="A9" s="66" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B9" s="66" t="s">
         <v>772</v>
       </c>
-      <c r="C9" s="59" t="s">
-        <v>1037</v>
+      <c r="C9" s="66" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B10" s="59" t="s">
+      <c r="A10" s="66" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B10" s="66" t="s">
         <v>770</v>
       </c>
-      <c r="C10" s="59" t="s">
-        <v>1038</v>
+      <c r="C10" s="66" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B11" s="59" t="s">
+      <c r="A11" s="66" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B11" s="66" t="s">
         <v>767</v>
       </c>
-      <c r="C11" s="59" t="s">
-        <v>1039</v>
+      <c r="C11" s="66" t="s">
+        <v>1054</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B12" s="59" t="s">
+      <c r="A12" s="66" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B12" s="66" t="s">
         <v>774</v>
       </c>
-      <c r="C12" s="59" t="s">
-        <v>1041</v>
+      <c r="C12" s="66" t="s">
+        <v>1056</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B13" s="59" t="s">
+      <c r="A13" s="66" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B13" s="66" t="s">
         <v>777</v>
       </c>
-      <c r="C13" s="59" t="s">
-        <v>1042</v>
+      <c r="C13" s="66" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="59" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B14" s="59" t="s">
+      <c r="A14" s="66" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B14" s="66" t="s">
         <v>784</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="66" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="66" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B15" s="66" t="s">
+        <v>781</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>791</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>794</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>788</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>790</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B20" s="66" t="s">
+        <v>792</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>789</v>
+      </c>
+      <c r="C21" s="66" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B22" s="66" t="s">
+        <v>793</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B23" s="66" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B24" s="66" t="s">
+        <v>706</v>
+      </c>
+      <c r="C24" s="66" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="66" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B25" s="66" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="66" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B26" s="66" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="66" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B27" s="66" t="s">
+        <v>707</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="67" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B28" s="68"/>
+      <c r="C28" s="67" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="69"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="69"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="69"/>
+      <c r="W28" s="69"/>
+      <c r="X28" s="69"/>
+      <c r="Y28" s="69"/>
+      <c r="Z28" s="69"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="70" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B29" s="71"/>
+      <c r="C29" s="70" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="59" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B15" s="59" t="s">
-        <v>781</v>
-      </c>
-      <c r="C15" s="59" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>791</v>
-      </c>
-      <c r="C16" s="59" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>794</v>
-      </c>
-      <c r="C17" s="59" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>788</v>
-      </c>
-      <c r="C18" s="59" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B19" s="59" t="s">
-        <v>790</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B20" s="59" t="s">
-        <v>792</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B21" s="59" t="s">
-        <v>789</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="59" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B22" s="59" t="s">
-        <v>793</v>
-      </c>
-      <c r="C22" s="59" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="59" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B23" s="59" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C23" s="59" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="59" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B24" s="59" t="s">
-        <v>706</v>
-      </c>
-      <c r="C24" s="59" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="59" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C25" s="59" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="59" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B26" s="59" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="59" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B27" s="59" t="s">
-        <v>707</v>
-      </c>
-      <c r="C27" s="59" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="60" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B28" s="61"/>
-      <c r="C28" s="60" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="62"/>
-      <c r="P28" s="62"/>
-      <c r="Q28" s="62"/>
-      <c r="R28" s="62"/>
-      <c r="S28" s="62"/>
-      <c r="T28" s="62"/>
-      <c r="U28" s="62"/>
-      <c r="V28" s="62"/>
-      <c r="W28" s="62"/>
-      <c r="X28" s="62"/>
-      <c r="Y28" s="62"/>
-      <c r="Z28" s="62"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="63" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B29" s="64"/>
-      <c r="C29" s="63" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="65"/>
-      <c r="V29" s="65"/>
-      <c r="W29" s="65"/>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="65"/>
-      <c r="Z29" s="65"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="72"/>
+      <c r="V29" s="72"/>
+      <c r="W29" s="72"/>
+      <c r="X29" s="72"/>
+      <c r="Y29" s="72"/>
+      <c r="Z29" s="72"/>
     </row>
     <row r="30">
-      <c r="A30" s="63" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="63" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="65"/>
-      <c r="V30" s="65"/>
-      <c r="W30" s="65"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="65"/>
-      <c r="Z30" s="65"/>
+      <c r="A30" s="70" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B30" s="71"/>
+      <c r="C30" s="70" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
+      <c r="X30" s="72"/>
+      <c r="Y30" s="72"/>
+      <c r="Z30" s="72"/>
     </row>
     <row r="31">
-      <c r="A31" s="63" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="63" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="65"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-      <c r="Z31" s="65"/>
+      <c r="A31" s="70" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B31" s="71"/>
+      <c r="C31" s="70" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="72"/>
+      <c r="W31" s="72"/>
+      <c r="X31" s="72"/>
+      <c r="Y31" s="72"/>
+      <c r="Z31" s="72"/>
     </row>
     <row r="32">
-      <c r="A32" s="63" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="63" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
-      <c r="W32" s="65"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
-      <c r="Z32" s="65"/>
+      <c r="A32" s="70" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B32" s="71"/>
+      <c r="C32" s="70" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="72"/>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B33" s="61"/>
-      <c r="C33" s="60" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
-      <c r="M33" s="62"/>
-      <c r="N33" s="62"/>
-      <c r="O33" s="62"/>
-      <c r="P33" s="62"/>
-      <c r="Q33" s="62"/>
-      <c r="R33" s="62"/>
-      <c r="S33" s="62"/>
-      <c r="T33" s="62"/>
-      <c r="U33" s="62"/>
-      <c r="V33" s="62"/>
-      <c r="W33" s="62"/>
-      <c r="X33" s="62"/>
-      <c r="Y33" s="62"/>
-      <c r="Z33" s="62"/>
+      <c r="A33" s="67" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B33" s="68"/>
+      <c r="C33" s="67" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="69"/>
+      <c r="M33" s="69"/>
+      <c r="N33" s="69"/>
+      <c r="O33" s="69"/>
+      <c r="P33" s="69"/>
+      <c r="Q33" s="69"/>
+      <c r="R33" s="69"/>
+      <c r="S33" s="69"/>
+      <c r="T33" s="69"/>
+      <c r="U33" s="69"/>
+      <c r="V33" s="69"/>
+      <c r="W33" s="69"/>
+      <c r="X33" s="69"/>
+      <c r="Y33" s="69"/>
+      <c r="Z33" s="69"/>
     </row>
     <row r="34">
-      <c r="A34" s="59" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B34" s="59" t="s">
+      <c r="A34" s="66" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B34" s="66" t="s">
         <v>811</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>1065</v>
+      <c r="C34" s="66" t="s">
+        <v>1080</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="59" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B35" s="59" t="s">
+      <c r="A35" s="66" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B35" s="66" t="s">
         <v>813</v>
       </c>
-      <c r="C35" s="59" t="s">
-        <v>1069</v>
+      <c r="C35" s="66" t="s">
+        <v>1084</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="59" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B36" s="59" t="s">
+      <c r="A36" s="66" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B36" s="66" t="s">
         <v>815</v>
       </c>
-      <c r="C36" s="59" t="s">
-        <v>1066</v>
+      <c r="C36" s="66" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="59" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B37" s="59" t="s">
+      <c r="A37" s="66" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B37" s="66" t="s">
         <v>814</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>1057</v>
+      <c r="C37" s="66" t="s">
+        <v>1072</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="59" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B38" s="59" t="s">
+      <c r="A38" s="66" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B38" s="66" t="s">
         <v>812</v>
       </c>
-      <c r="C38" s="59" t="s">
-        <v>1055</v>
+      <c r="C38" s="66" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="66" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B39" s="73"/>
+      <c r="C39" s="66" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="66" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B40" s="73"/>
+      <c r="C40" s="66" t="s">
         <v>1070</v>
       </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="59" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="59" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="59" t="s">
-        <v>1055</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="59" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="59" t="s">
-        <v>1066</v>
+      <c r="A41" s="66" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B41" s="73"/>
+      <c r="C41" s="66" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="59" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B42" s="66"/>
-      <c r="C42" s="59" t="s">
-        <v>1057</v>
+      <c r="A42" s="66" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B42" s="73"/>
+      <c r="C42" s="66" t="s">
+        <v>1072</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B43" s="61"/>
-      <c r="C43" s="60" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="62"/>
-      <c r="J43" s="62"/>
-      <c r="K43" s="62"/>
-      <c r="L43" s="62"/>
-      <c r="M43" s="62"/>
-      <c r="N43" s="62"/>
-      <c r="O43" s="62"/>
-      <c r="P43" s="62"/>
-      <c r="Q43" s="62"/>
-      <c r="R43" s="62"/>
-      <c r="S43" s="62"/>
-      <c r="T43" s="62"/>
-      <c r="U43" s="62"/>
-      <c r="V43" s="62"/>
-      <c r="W43" s="62"/>
-      <c r="X43" s="62"/>
-      <c r="Y43" s="62"/>
-      <c r="Z43" s="62"/>
+      <c r="A43" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B43" s="68"/>
+      <c r="C43" s="67" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="69"/>
+      <c r="L43" s="69"/>
+      <c r="M43" s="69"/>
+      <c r="N43" s="69"/>
+      <c r="O43" s="69"/>
+      <c r="P43" s="69"/>
+      <c r="Q43" s="69"/>
+      <c r="R43" s="69"/>
+      <c r="S43" s="69"/>
+      <c r="T43" s="69"/>
+      <c r="U43" s="69"/>
+      <c r="V43" s="69"/>
+      <c r="W43" s="69"/>
+      <c r="X43" s="69"/>
+      <c r="Y43" s="69"/>
+      <c r="Z43" s="69"/>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B44" s="61"/>
-      <c r="C44" s="60" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D44" s="62"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="62"/>
-      <c r="H44" s="62"/>
-      <c r="I44" s="62"/>
-      <c r="J44" s="62"/>
-      <c r="K44" s="62"/>
-      <c r="L44" s="62"/>
-      <c r="M44" s="62"/>
-      <c r="N44" s="62"/>
-      <c r="O44" s="62"/>
-      <c r="P44" s="62"/>
-      <c r="Q44" s="62"/>
-      <c r="R44" s="62"/>
-      <c r="S44" s="62"/>
-      <c r="T44" s="62"/>
-      <c r="U44" s="62"/>
-      <c r="V44" s="62"/>
-      <c r="W44" s="62"/>
-      <c r="X44" s="62"/>
-      <c r="Y44" s="62"/>
-      <c r="Z44" s="62"/>
+      <c r="A44" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B44" s="68"/>
+      <c r="C44" s="67" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="69"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="69"/>
+      <c r="O44" s="69"/>
+      <c r="P44" s="69"/>
+      <c r="Q44" s="69"/>
+      <c r="R44" s="69"/>
+      <c r="S44" s="69"/>
+      <c r="T44" s="69"/>
+      <c r="U44" s="69"/>
+      <c r="V44" s="69"/>
+      <c r="W44" s="69"/>
+      <c r="X44" s="69"/>
+      <c r="Y44" s="69"/>
+      <c r="Z44" s="69"/>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B45" s="61"/>
-      <c r="C45" s="60" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D45" s="62"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="62"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="62"/>
-      <c r="I45" s="62"/>
-      <c r="J45" s="62"/>
-      <c r="K45" s="62"/>
-      <c r="L45" s="62"/>
-      <c r="M45" s="62"/>
-      <c r="N45" s="62"/>
-      <c r="O45" s="62"/>
-      <c r="P45" s="62"/>
-      <c r="Q45" s="62"/>
-      <c r="R45" s="62"/>
-      <c r="S45" s="62"/>
-      <c r="T45" s="62"/>
-      <c r="U45" s="62"/>
-      <c r="V45" s="62"/>
-      <c r="W45" s="62"/>
-      <c r="X45" s="62"/>
-      <c r="Y45" s="62"/>
-      <c r="Z45" s="62"/>
+      <c r="A45" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B45" s="68"/>
+      <c r="C45" s="67" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="69"/>
+      <c r="M45" s="69"/>
+      <c r="N45" s="69"/>
+      <c r="O45" s="69"/>
+      <c r="P45" s="69"/>
+      <c r="Q45" s="69"/>
+      <c r="R45" s="69"/>
+      <c r="S45" s="69"/>
+      <c r="T45" s="69"/>
+      <c r="U45" s="69"/>
+      <c r="V45" s="69"/>
+      <c r="W45" s="69"/>
+      <c r="X45" s="69"/>
+      <c r="Y45" s="69"/>
+      <c r="Z45" s="69"/>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B46" s="61"/>
-      <c r="C46" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="62"/>
-      <c r="H46" s="62"/>
-      <c r="I46" s="62"/>
-      <c r="J46" s="62"/>
-      <c r="K46" s="62"/>
-      <c r="L46" s="62"/>
-      <c r="M46" s="62"/>
-      <c r="N46" s="62"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="62"/>
-      <c r="T46" s="62"/>
-      <c r="U46" s="62"/>
-      <c r="V46" s="62"/>
-      <c r="W46" s="62"/>
-      <c r="X46" s="62"/>
-      <c r="Y46" s="62"/>
-      <c r="Z46" s="62"/>
+      <c r="A46" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B46" s="68"/>
+      <c r="C46" s="67" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="69"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="69"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="69"/>
+      <c r="S46" s="69"/>
+      <c r="T46" s="69"/>
+      <c r="U46" s="69"/>
+      <c r="V46" s="69"/>
+      <c r="W46" s="69"/>
+      <c r="X46" s="69"/>
+      <c r="Y46" s="69"/>
+      <c r="Z46" s="69"/>
     </row>
     <row r="47">
-      <c r="A47" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B47" s="61"/>
-      <c r="C47" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="62"/>
-      <c r="J47" s="62"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="62"/>
-      <c r="M47" s="62"/>
-      <c r="N47" s="62"/>
-      <c r="O47" s="62"/>
-      <c r="P47" s="62"/>
-      <c r="Q47" s="62"/>
-      <c r="R47" s="62"/>
-      <c r="S47" s="62"/>
-      <c r="T47" s="62"/>
-      <c r="U47" s="62"/>
-      <c r="V47" s="62"/>
-      <c r="W47" s="62"/>
-      <c r="X47" s="62"/>
-      <c r="Y47" s="62"/>
-      <c r="Z47" s="62"/>
+      <c r="A47" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B47" s="68"/>
+      <c r="C47" s="67" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="69"/>
+      <c r="M47" s="69"/>
+      <c r="N47" s="69"/>
+      <c r="O47" s="69"/>
+      <c r="P47" s="69"/>
+      <c r="Q47" s="69"/>
+      <c r="R47" s="69"/>
+      <c r="S47" s="69"/>
+      <c r="T47" s="69"/>
+      <c r="U47" s="69"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="69"/>
+      <c r="X47" s="69"/>
+      <c r="Y47" s="69"/>
+      <c r="Z47" s="69"/>
     </row>
     <row r="48">
-      <c r="A48" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B48" s="61"/>
-      <c r="C48" s="60" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="62"/>
-      <c r="H48" s="62"/>
-      <c r="I48" s="62"/>
-      <c r="J48" s="62"/>
-      <c r="K48" s="62"/>
-      <c r="L48" s="62"/>
-      <c r="M48" s="62"/>
-      <c r="N48" s="62"/>
-      <c r="O48" s="62"/>
-      <c r="P48" s="62"/>
-      <c r="Q48" s="62"/>
-      <c r="R48" s="62"/>
-      <c r="S48" s="62"/>
-      <c r="T48" s="62"/>
-      <c r="U48" s="62"/>
-      <c r="V48" s="62"/>
-      <c r="W48" s="62"/>
-      <c r="X48" s="62"/>
-      <c r="Y48" s="62"/>
-      <c r="Z48" s="62"/>
+      <c r="A48" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B48" s="68"/>
+      <c r="C48" s="67" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="69"/>
+      <c r="M48" s="69"/>
+      <c r="N48" s="69"/>
+      <c r="O48" s="69"/>
+      <c r="P48" s="69"/>
+      <c r="Q48" s="69"/>
+      <c r="R48" s="69"/>
+      <c r="S48" s="69"/>
+      <c r="T48" s="69"/>
+      <c r="U48" s="69"/>
+      <c r="V48" s="69"/>
+      <c r="W48" s="69"/>
+      <c r="X48" s="69"/>
+      <c r="Y48" s="69"/>
+      <c r="Z48" s="69"/>
     </row>
     <row r="49">
-      <c r="A49" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B49" s="61"/>
-      <c r="C49" s="60" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="62"/>
-      <c r="K49" s="62"/>
-      <c r="L49" s="62"/>
-      <c r="M49" s="62"/>
-      <c r="N49" s="62"/>
-      <c r="O49" s="62"/>
-      <c r="P49" s="62"/>
-      <c r="Q49" s="62"/>
-      <c r="R49" s="62"/>
-      <c r="S49" s="62"/>
-      <c r="T49" s="62"/>
-      <c r="U49" s="62"/>
-      <c r="V49" s="62"/>
-      <c r="W49" s="62"/>
-      <c r="X49" s="62"/>
-      <c r="Y49" s="62"/>
-      <c r="Z49" s="62"/>
+      <c r="A49" s="67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B49" s="68"/>
+      <c r="C49" s="67" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="69"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="69"/>
+      <c r="T49" s="69"/>
+      <c r="U49" s="69"/>
+      <c r="V49" s="69"/>
+      <c r="W49" s="69"/>
+      <c r="X49" s="69"/>
+      <c r="Y49" s="69"/>
+      <c r="Z49" s="69"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -19429,7 +22654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -19440,2942 +22665,2942 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="68" t="s">
-        <v>1080</v>
-      </c>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
+      <c r="C1" s="75" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D1" s="76"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="75" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1" s="76"/>
+      <c r="H1" s="77"/>
     </row>
     <row r="2">
-      <c r="A2" s="71"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="72" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D2" s="72" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E2" s="72" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F2" s="72" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G2" s="72" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H2" s="72" t="s">
-        <v>1083</v>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="79" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H2" s="79" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="81">
         <v>4.24</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="81">
         <v>4.72</v>
       </c>
-      <c r="E3" s="75">
+      <c r="E3" s="82">
         <f t="shared" ref="E3:E164" si="1">AVERAGE(C3:D3)</f>
         <v>4.48</v>
       </c>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="81">
         <v>4.24</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="81">
         <v>4.72</v>
       </c>
-      <c r="E4" s="75">
+      <c r="E4" s="82">
         <f t="shared" si="1"/>
         <v>4.48</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
     </row>
     <row r="5">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="74">
+      <c r="C5" s="81">
         <v>4.24</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="81">
         <v>4.72</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="82">
         <f t="shared" si="1"/>
         <v>4.48</v>
       </c>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="81">
         <v>3.74</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="81">
         <v>4.16</v>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="82">
         <f t="shared" si="1"/>
         <v>3.95</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
     </row>
     <row r="7">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="81">
         <v>3.74</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="81">
         <v>4.16</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="82">
         <f t="shared" si="1"/>
         <v>3.95</v>
       </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="81">
         <v>3.74</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="81">
         <v>4.16</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="82">
         <f t="shared" si="1"/>
         <v>3.95</v>
       </c>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="74">
+      <c r="C9" s="81">
         <v>3.74</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="81">
         <v>4.16</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="82">
         <f t="shared" si="1"/>
         <v>3.95</v>
       </c>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75" t="str">
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75" t="str">
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="80" t="s">
         <v>733</v>
       </c>
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="81">
         <v>7.59</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="81">
         <v>10.05</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="82">
         <f t="shared" si="1"/>
         <v>8.82</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
     </row>
     <row r="13">
-      <c r="A13" s="73" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B13" s="73" t="s">
+      <c r="A13" s="80" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B13" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="81">
         <v>7.59</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="81">
         <v>10.05</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="82">
         <f t="shared" si="1"/>
         <v>8.82</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
     </row>
     <row r="14">
-      <c r="A14" s="73" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B14" s="73" t="s">
+      <c r="A14" s="80" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B14" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="74">
+      <c r="C14" s="81">
         <v>7.59</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="81">
         <v>10.05</v>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="82">
         <f t="shared" si="1"/>
         <v>8.82</v>
       </c>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
     </row>
     <row r="15">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75" t="str">
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
     </row>
     <row r="16">
-      <c r="A16" s="73" t="s">
+      <c r="A16" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="75" t="str">
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
     </row>
     <row r="17">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="74">
+      <c r="C17" s="81">
         <v>9.37</v>
       </c>
-      <c r="D17" s="74">
+      <c r="D17" s="81">
         <v>12.85</v>
       </c>
-      <c r="E17" s="75">
+      <c r="E17" s="82">
         <f t="shared" si="1"/>
         <v>11.11</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
     </row>
     <row r="18">
-      <c r="A18" s="73" t="s">
+      <c r="A18" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="73" t="s">
+      <c r="B18" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="74">
+      <c r="C18" s="81">
         <v>9.37</v>
       </c>
-      <c r="D18" s="74">
+      <c r="D18" s="81">
         <v>12.85</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="82">
         <f t="shared" si="1"/>
         <v>11.11</v>
       </c>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
     </row>
     <row r="19">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="80" t="s">
         <v>741</v>
       </c>
-      <c r="B19" s="73" t="s">
+      <c r="B19" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="75" t="str">
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="82"/>
     </row>
     <row r="20">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="80" t="s">
         <v>743</v>
       </c>
-      <c r="B20" s="73" t="s">
+      <c r="B20" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75" t="str">
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
     </row>
     <row r="21">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="73" t="s">
+      <c r="B21" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75" t="str">
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
     </row>
     <row r="22">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75" t="str">
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
     </row>
     <row r="23">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="80" t="s">
         <v>751</v>
       </c>
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75" t="str">
+      <c r="C23" s="82"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
     </row>
     <row r="24">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="80" t="s">
         <v>752</v>
       </c>
-      <c r="B24" s="73" t="s">
+      <c r="B24" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75" t="str">
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
     </row>
     <row r="25">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="80" t="s">
         <v>753</v>
       </c>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75" t="str">
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
     </row>
     <row r="26">
-      <c r="A26" s="73" t="s">
+      <c r="A26" s="80" t="s">
         <v>754</v>
       </c>
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75" t="str">
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
     </row>
     <row r="27">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="80" t="s">
         <v>755</v>
       </c>
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="75"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75" t="str">
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
     </row>
     <row r="28">
-      <c r="A28" s="73" t="s">
+      <c r="A28" s="80" t="s">
         <v>756</v>
       </c>
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="75"/>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75" t="str">
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
     </row>
     <row r="29">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="74">
+      <c r="C29" s="81">
         <v>4.49</v>
       </c>
-      <c r="D29" s="74">
+      <c r="D29" s="81">
         <v>4.99</v>
       </c>
-      <c r="E29" s="75">
+      <c r="E29" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F29" s="75"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
     </row>
     <row r="30">
-      <c r="A30" s="73" t="s">
+      <c r="A30" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="74">
+      <c r="C30" s="81">
         <v>4.49</v>
       </c>
-      <c r="D30" s="74">
+      <c r="D30" s="81">
         <v>4.99</v>
       </c>
-      <c r="E30" s="75">
+      <c r="E30" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
     </row>
     <row r="31">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="74">
+      <c r="C31" s="81">
         <v>4.49</v>
       </c>
-      <c r="D31" s="74">
+      <c r="D31" s="81">
         <v>4.99</v>
       </c>
-      <c r="E31" s="75">
+      <c r="E31" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
     </row>
     <row r="32">
-      <c r="A32" s="73" t="s">
+      <c r="A32" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="73" t="s">
+      <c r="B32" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="74">
+      <c r="C32" s="81">
         <v>4.49</v>
       </c>
-      <c r="D32" s="74">
+      <c r="D32" s="81">
         <v>4.99</v>
       </c>
-      <c r="E32" s="75">
+      <c r="E32" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
     </row>
     <row r="33">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="74">
+      <c r="C33" s="81">
         <v>4.49</v>
       </c>
-      <c r="D33" s="74">
+      <c r="D33" s="81">
         <v>4.99</v>
       </c>
-      <c r="E33" s="75">
+      <c r="E33" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
     </row>
     <row r="34">
-      <c r="A34" s="73" t="s">
+      <c r="A34" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="73" t="s">
+      <c r="B34" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="74">
+      <c r="C34" s="81">
         <v>4.49</v>
       </c>
-      <c r="D34" s="74">
+      <c r="D34" s="81">
         <v>4.99</v>
       </c>
-      <c r="E34" s="75">
+      <c r="E34" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
     </row>
     <row r="35">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="74">
+      <c r="C35" s="81">
         <v>4.49</v>
       </c>
-      <c r="D35" s="74">
+      <c r="D35" s="81">
         <v>4.99</v>
       </c>
-      <c r="E35" s="75">
+      <c r="E35" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
     </row>
     <row r="36">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="73" t="s">
+      <c r="B36" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="74">
+      <c r="C36" s="81">
         <v>4.49</v>
       </c>
-      <c r="D36" s="74">
+      <c r="D36" s="81">
         <v>4.99</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
     </row>
     <row r="37">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="73" t="s">
+      <c r="B37" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="74">
+      <c r="C37" s="81">
         <v>4.49</v>
       </c>
-      <c r="D37" s="74">
+      <c r="D37" s="81">
         <v>4.99</v>
       </c>
-      <c r="E37" s="75">
+      <c r="E37" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
     </row>
     <row r="38">
-      <c r="A38" s="73" t="s">
+      <c r="A38" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="73" t="s">
+      <c r="B38" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="74">
+      <c r="C38" s="81">
         <v>4.49</v>
       </c>
-      <c r="D38" s="74">
+      <c r="D38" s="81">
         <v>4.99</v>
       </c>
-      <c r="E38" s="75">
+      <c r="E38" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
     </row>
     <row r="39">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="73" t="s">
+      <c r="B39" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="74">
+      <c r="C39" s="81">
         <v>4.49</v>
       </c>
-      <c r="D39" s="74">
+      <c r="D39" s="81">
         <v>4.99</v>
       </c>
-      <c r="E39" s="75">
+      <c r="E39" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
     </row>
     <row r="40">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="73" t="s">
+      <c r="B40" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="74">
+      <c r="C40" s="81">
         <v>5.57</v>
       </c>
-      <c r="D40" s="74">
+      <c r="D40" s="81">
         <v>6.55</v>
       </c>
-      <c r="E40" s="75">
+      <c r="E40" s="82">
         <f t="shared" si="1"/>
         <v>6.06</v>
       </c>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
     </row>
     <row r="41">
-      <c r="A41" s="73" t="s">
+      <c r="A41" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="B41" s="73" t="s">
+      <c r="B41" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="74">
+      <c r="C41" s="81">
         <v>5.57</v>
       </c>
-      <c r="D41" s="74">
+      <c r="D41" s="81">
         <v>6.55</v>
       </c>
-      <c r="E41" s="75">
+      <c r="E41" s="82">
         <f t="shared" si="1"/>
         <v>6.06</v>
       </c>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
     </row>
     <row r="42">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="B42" s="73" t="s">
+      <c r="B42" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="74">
+      <c r="C42" s="81">
         <v>5.57</v>
       </c>
-      <c r="D42" s="74">
+      <c r="D42" s="81">
         <v>6.55</v>
       </c>
-      <c r="E42" s="75">
+      <c r="E42" s="82">
         <f t="shared" si="1"/>
         <v>6.06</v>
       </c>
-      <c r="F42" s="75"/>
-      <c r="G42" s="75"/>
-      <c r="H42" s="75"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
     </row>
     <row r="43">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="B43" s="73" t="s">
+      <c r="B43" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="74">
+      <c r="C43" s="81">
         <v>5.57</v>
       </c>
-      <c r="D43" s="74">
+      <c r="D43" s="81">
         <v>6.55</v>
       </c>
-      <c r="E43" s="75">
+      <c r="E43" s="82">
         <f t="shared" si="1"/>
         <v>6.06</v>
       </c>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="82"/>
     </row>
     <row r="44">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="73" t="s">
+      <c r="B44" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75" t="str">
+      <c r="C44" s="82"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F44" s="75"/>
-      <c r="G44" s="75"/>
-      <c r="H44" s="75"/>
+      <c r="F44" s="82"/>
+      <c r="G44" s="82"/>
+      <c r="H44" s="82"/>
     </row>
     <row r="45">
-      <c r="A45" s="73" t="s">
+      <c r="A45" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="B45" s="73" t="s">
+      <c r="B45" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="C45" s="75"/>
-      <c r="D45" s="75"/>
-      <c r="E45" s="75" t="str">
+      <c r="C45" s="82"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F45" s="75"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="82"/>
     </row>
     <row r="46">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="73" t="s">
+      <c r="B46" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="75"/>
-      <c r="D46" s="75"/>
-      <c r="E46" s="75" t="str">
+      <c r="C46" s="82"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F46" s="75"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="75"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="82"/>
     </row>
     <row r="47">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="B47" s="73" t="s">
+      <c r="B47" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75" t="str">
+      <c r="C47" s="82"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
+      <c r="F47" s="82"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="82"/>
     </row>
     <row r="48">
-      <c r="A48" s="73" t="s">
+      <c r="A48" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="73" t="s">
+      <c r="B48" s="80" t="s">
         <v>119</v>
       </c>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75" t="str">
+      <c r="C48" s="82"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
+      <c r="F48" s="82"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="82"/>
     </row>
     <row r="49">
-      <c r="A49" s="73" t="s">
+      <c r="A49" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="73" t="s">
+      <c r="B49" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="75" t="str">
+      <c r="C49" s="82"/>
+      <c r="D49" s="82"/>
+      <c r="E49" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F49" s="75"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
+      <c r="F49" s="82"/>
+      <c r="G49" s="82"/>
+      <c r="H49" s="82"/>
     </row>
     <row r="50">
-      <c r="A50" s="73" t="s">
+      <c r="A50" s="80" t="s">
         <v>122</v>
       </c>
-      <c r="B50" s="73" t="s">
+      <c r="B50" s="80" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="75"/>
-      <c r="E50" s="75" t="str">
+      <c r="C50" s="82"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F50" s="75"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="75"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="82"/>
+      <c r="H50" s="82"/>
     </row>
     <row r="51">
-      <c r="A51" s="73" t="s">
+      <c r="A51" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="B51" s="73" t="s">
+      <c r="B51" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75" t="str">
+      <c r="C51" s="82"/>
+      <c r="D51" s="82"/>
+      <c r="E51" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
+      <c r="F51" s="82"/>
+      <c r="G51" s="82"/>
+      <c r="H51" s="82"/>
     </row>
     <row r="52">
-      <c r="A52" s="73" t="s">
+      <c r="A52" s="80" t="s">
         <v>763</v>
       </c>
-      <c r="B52" s="73" t="s">
+      <c r="B52" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75" t="str">
+      <c r="C52" s="82"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
+      <c r="H52" s="82"/>
     </row>
     <row r="53">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="80" t="s">
         <v>765</v>
       </c>
-      <c r="B53" s="73" t="s">
+      <c r="B53" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="74">
+      <c r="C53" s="81">
         <v>4.49</v>
       </c>
-      <c r="D53" s="74">
+      <c r="D53" s="81">
         <v>4.99</v>
       </c>
-      <c r="E53" s="75">
+      <c r="E53" s="82">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
-      <c r="F53" s="75"/>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
     </row>
     <row r="54">
-      <c r="A54" s="73" t="s">
+      <c r="A54" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="73" t="s">
+      <c r="B54" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="C54" s="75"/>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75" t="str">
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F54" s="75"/>
-      <c r="G54" s="75"/>
-      <c r="H54" s="75"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
     </row>
     <row r="55">
-      <c r="A55" s="73" t="s">
+      <c r="A55" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="73" t="s">
+      <c r="B55" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75" t="str">
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F55" s="75"/>
-      <c r="G55" s="75"/>
-      <c r="H55" s="75"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="82"/>
     </row>
     <row r="56">
-      <c r="A56" s="73" t="s">
+      <c r="A56" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="B56" s="73" t="s">
+      <c r="B56" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75" t="str">
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F56" s="75"/>
-      <c r="G56" s="75"/>
-      <c r="H56" s="75"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="82"/>
     </row>
     <row r="57">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="B57" s="73" t="s">
+      <c r="B57" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75" t="str">
+      <c r="C57" s="82"/>
+      <c r="D57" s="82"/>
+      <c r="E57" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="82"/>
+      <c r="H57" s="82"/>
     </row>
     <row r="58">
-      <c r="A58" s="73" t="s">
+      <c r="A58" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="73" t="s">
+      <c r="B58" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="75"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75" t="str">
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F58" s="75"/>
-      <c r="G58" s="75"/>
-      <c r="H58" s="75"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="82"/>
     </row>
     <row r="59">
-      <c r="A59" s="73" t="s">
+      <c r="A59" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="B59" s="73" t="s">
+      <c r="B59" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75" t="str">
+      <c r="C59" s="82"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F59" s="75"/>
-      <c r="G59" s="75"/>
-      <c r="H59" s="75"/>
+      <c r="F59" s="82"/>
+      <c r="G59" s="82"/>
+      <c r="H59" s="82"/>
     </row>
     <row r="60">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="B60" s="73" t="s">
+      <c r="B60" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="75"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="75" t="str">
+      <c r="C60" s="82"/>
+      <c r="D60" s="82"/>
+      <c r="E60" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F60" s="75"/>
-      <c r="G60" s="75"/>
-      <c r="H60" s="75"/>
+      <c r="F60" s="82"/>
+      <c r="G60" s="82"/>
+      <c r="H60" s="82"/>
     </row>
     <row r="61">
-      <c r="A61" s="73" t="s">
+      <c r="A61" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="73" t="s">
+      <c r="B61" s="80" t="s">
         <v>141</v>
       </c>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75" t="str">
+      <c r="C61" s="82"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
+      <c r="F61" s="82"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="82"/>
     </row>
     <row r="62">
-      <c r="A62" s="73" t="s">
+      <c r="A62" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="B62" s="73" t="s">
+      <c r="B62" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="C62" s="75"/>
-      <c r="D62" s="75"/>
-      <c r="E62" s="75" t="str">
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F62" s="75"/>
-      <c r="G62" s="75"/>
-      <c r="H62" s="75"/>
+      <c r="F62" s="82"/>
+      <c r="G62" s="82"/>
+      <c r="H62" s="82"/>
     </row>
     <row r="63">
-      <c r="A63" s="73" t="s">
+      <c r="A63" s="80" t="s">
         <v>785</v>
       </c>
-      <c r="B63" s="73" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C63" s="75"/>
-      <c r="D63" s="75"/>
-      <c r="E63" s="75" t="str">
+      <c r="B63" s="80" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C63" s="82"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F63" s="75"/>
-      <c r="G63" s="75"/>
-      <c r="H63" s="75"/>
+      <c r="F63" s="82"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="82"/>
     </row>
     <row r="64">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="80" t="s">
         <v>144</v>
       </c>
-      <c r="B64" s="73" t="s">
+      <c r="B64" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="C64" s="75"/>
-      <c r="D64" s="75"/>
-      <c r="E64" s="75" t="str">
+      <c r="C64" s="82"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F64" s="75"/>
-      <c r="G64" s="75"/>
-      <c r="H64" s="75"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
+      <c r="H64" s="82"/>
     </row>
     <row r="65">
-      <c r="A65" s="73" t="s">
+      <c r="A65" s="80" t="s">
         <v>146</v>
       </c>
-      <c r="B65" s="73" t="s">
+      <c r="B65" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="C65" s="75"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="75" t="str">
+      <c r="C65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F65" s="75"/>
-      <c r="G65" s="75"/>
-      <c r="H65" s="75"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="82"/>
+      <c r="H65" s="82"/>
     </row>
     <row r="66">
-      <c r="A66" s="73" t="s">
+      <c r="A66" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="B66" s="73" t="s">
+      <c r="B66" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="C66" s="75"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="75" t="str">
+      <c r="C66" s="82"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F66" s="75"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="75"/>
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
+      <c r="H66" s="82"/>
     </row>
     <row r="67">
-      <c r="A67" s="73" t="s">
+      <c r="A67" s="80" t="s">
         <v>158</v>
       </c>
-      <c r="B67" s="73" t="s">
+      <c r="B67" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="75"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="75" t="str">
+      <c r="C67" s="82"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F67" s="75"/>
-      <c r="G67" s="75"/>
-      <c r="H67" s="75"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
+      <c r="H67" s="82"/>
     </row>
     <row r="68">
-      <c r="A68" s="73" t="s">
+      <c r="A68" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="B68" s="73" t="s">
+      <c r="B68" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="75"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75" t="str">
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F68" s="75"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="82"/>
     </row>
     <row r="69">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="73" t="s">
+      <c r="B69" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="75"/>
-      <c r="D69" s="75"/>
-      <c r="E69" s="75" t="str">
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F69" s="75"/>
-      <c r="G69" s="75"/>
-      <c r="H69" s="75"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
+      <c r="H69" s="82"/>
     </row>
     <row r="70">
-      <c r="A70" s="73" t="s">
+      <c r="A70" s="80" t="s">
         <v>164</v>
       </c>
-      <c r="B70" s="73" t="s">
+      <c r="B70" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75" t="str">
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F70" s="75"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
+      <c r="F70" s="82"/>
+      <c r="G70" s="82"/>
+      <c r="H70" s="82"/>
     </row>
     <row r="71">
-      <c r="A71" s="73" t="s">
+      <c r="A71" s="80" t="s">
         <v>166</v>
       </c>
-      <c r="B71" s="73" t="s">
+      <c r="B71" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="75"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="75" t="str">
+      <c r="C71" s="82"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F71" s="75"/>
-      <c r="G71" s="75"/>
-      <c r="H71" s="75"/>
+      <c r="F71" s="82"/>
+      <c r="G71" s="82"/>
+      <c r="H71" s="82"/>
     </row>
     <row r="72">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="80" t="s">
         <v>264</v>
       </c>
-      <c r="B72" s="73" t="s">
+      <c r="B72" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="C72" s="74">
+      <c r="C72" s="81">
         <v>7.59</v>
       </c>
-      <c r="D72" s="74">
+      <c r="D72" s="81">
         <v>10.05</v>
       </c>
-      <c r="E72" s="75">
+      <c r="E72" s="82">
         <f t="shared" si="1"/>
         <v>8.82</v>
       </c>
-      <c r="F72" s="75"/>
-      <c r="G72" s="75"/>
-      <c r="H72" s="75"/>
+      <c r="F72" s="82"/>
+      <c r="G72" s="82"/>
+      <c r="H72" s="82"/>
     </row>
     <row r="73">
-      <c r="A73" s="73" t="s">
+      <c r="A73" s="80" t="s">
         <v>266</v>
       </c>
-      <c r="B73" s="73" t="s">
+      <c r="B73" s="80" t="s">
         <v>267</v>
       </c>
-      <c r="C73" s="74">
+      <c r="C73" s="81">
         <v>11.45</v>
       </c>
-      <c r="D73" s="74">
+      <c r="D73" s="81">
         <v>16.45</v>
       </c>
-      <c r="E73" s="75">
+      <c r="E73" s="82">
         <f t="shared" si="1"/>
         <v>13.95</v>
       </c>
-      <c r="F73" s="75"/>
-      <c r="G73" s="75"/>
-      <c r="H73" s="75"/>
+      <c r="F73" s="82"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
     </row>
     <row r="74">
-      <c r="A74" s="73" t="s">
+      <c r="A74" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="B74" s="73" t="s">
+      <c r="B74" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="C74" s="74">
+      <c r="C74" s="81">
         <v>11.45</v>
       </c>
-      <c r="D74" s="74">
+      <c r="D74" s="81">
         <v>16.52</v>
       </c>
-      <c r="E74" s="75">
+      <c r="E74" s="82">
         <f t="shared" si="1"/>
         <v>13.985</v>
       </c>
-      <c r="F74" s="75"/>
-      <c r="G74" s="75"/>
-      <c r="H74" s="75"/>
+      <c r="F74" s="82"/>
+      <c r="G74" s="82"/>
+      <c r="H74" s="82"/>
     </row>
     <row r="75">
-      <c r="A75" s="73" t="s">
+      <c r="A75" s="80" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="73" t="s">
+      <c r="B75" s="80" t="s">
         <v>271</v>
       </c>
-      <c r="C75" s="74">
+      <c r="C75" s="81">
         <v>14.22</v>
       </c>
-      <c r="D75" s="74">
+      <c r="D75" s="81">
         <v>21.36</v>
       </c>
-      <c r="E75" s="75">
+      <c r="E75" s="82">
         <f t="shared" si="1"/>
         <v>17.79</v>
       </c>
-      <c r="F75" s="75"/>
-      <c r="G75" s="75"/>
-      <c r="H75" s="75"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="82"/>
     </row>
     <row r="76">
-      <c r="A76" s="73" t="s">
+      <c r="A76" s="80" t="s">
         <v>272</v>
       </c>
-      <c r="B76" s="73" t="s">
+      <c r="B76" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="C76" s="74">
+      <c r="C76" s="81">
         <v>17.1</v>
       </c>
-      <c r="D76" s="74">
+      <c r="D76" s="81">
         <v>25.72</v>
       </c>
-      <c r="E76" s="75">
+      <c r="E76" s="82">
         <f t="shared" si="1"/>
         <v>21.41</v>
       </c>
-      <c r="F76" s="75"/>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
+      <c r="F76" s="82"/>
+      <c r="G76" s="82"/>
+      <c r="H76" s="82"/>
     </row>
     <row r="77">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="80" t="s">
         <v>274</v>
       </c>
-      <c r="B77" s="73" t="s">
+      <c r="B77" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="C77" s="74">
+      <c r="C77" s="81">
         <v>9.37</v>
       </c>
-      <c r="D77" s="74">
+      <c r="D77" s="81">
         <v>12.85</v>
       </c>
-      <c r="E77" s="75">
+      <c r="E77" s="82">
         <f t="shared" si="1"/>
         <v>11.11</v>
       </c>
-      <c r="F77" s="75"/>
-      <c r="G77" s="75"/>
-      <c r="H77" s="75"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="82"/>
     </row>
     <row r="78">
-      <c r="A78" s="73" t="s">
+      <c r="A78" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="B78" s="73" t="s">
+      <c r="B78" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="C78" s="74">
+      <c r="C78" s="81">
         <v>7.59</v>
       </c>
-      <c r="D78" s="74">
+      <c r="D78" s="81">
         <v>10.05</v>
       </c>
-      <c r="E78" s="75">
+      <c r="E78" s="82">
         <f t="shared" si="1"/>
         <v>8.82</v>
       </c>
-      <c r="F78" s="75"/>
-      <c r="G78" s="75"/>
-      <c r="H78" s="75"/>
+      <c r="F78" s="82"/>
+      <c r="G78" s="82"/>
+      <c r="H78" s="82"/>
     </row>
     <row r="79">
-      <c r="A79" s="73" t="s">
+      <c r="A79" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="B79" s="73" t="s">
+      <c r="B79" s="80" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="74">
+      <c r="C79" s="81">
         <v>7.59</v>
       </c>
-      <c r="D79" s="74">
+      <c r="D79" s="81">
         <v>10.05</v>
       </c>
-      <c r="E79" s="75">
+      <c r="E79" s="82">
         <f t="shared" si="1"/>
         <v>8.82</v>
       </c>
-      <c r="F79" s="75"/>
-      <c r="G79" s="75"/>
-      <c r="H79" s="75"/>
+      <c r="F79" s="82"/>
+      <c r="G79" s="82"/>
+      <c r="H79" s="82"/>
     </row>
     <row r="80">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="80" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="73" t="s">
+      <c r="B80" s="80" t="s">
         <v>281</v>
       </c>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75" t="str">
+      <c r="C80" s="82"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
+      <c r="F80" s="82"/>
+      <c r="G80" s="82"/>
+      <c r="H80" s="82"/>
     </row>
     <row r="81">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="80" t="s">
         <v>282</v>
       </c>
-      <c r="B81" s="73" t="s">
+      <c r="B81" s="80" t="s">
         <v>283</v>
       </c>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75"/>
-      <c r="E81" s="75" t="str">
+      <c r="C81" s="82"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F81" s="75"/>
-      <c r="G81" s="75"/>
-      <c r="H81" s="75"/>
+      <c r="F81" s="82"/>
+      <c r="G81" s="82"/>
+      <c r="H81" s="82"/>
     </row>
     <row r="82">
-      <c r="A82" s="73" t="s">
+      <c r="A82" s="80" t="s">
         <v>284</v>
       </c>
-      <c r="B82" s="73" t="s">
+      <c r="B82" s="80" t="s">
         <v>285</v>
       </c>
-      <c r="C82" s="75"/>
-      <c r="D82" s="75"/>
-      <c r="E82" s="75" t="str">
+      <c r="C82" s="82"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F82" s="75"/>
-      <c r="G82" s="75"/>
-      <c r="H82" s="75"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
+      <c r="H82" s="82"/>
     </row>
     <row r="83">
-      <c r="A83" s="73" t="s">
+      <c r="A83" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="B83" s="73" t="s">
+      <c r="B83" s="80" t="s">
         <v>287</v>
       </c>
-      <c r="C83" s="75"/>
-      <c r="D83" s="75"/>
-      <c r="E83" s="75" t="str">
+      <c r="C83" s="82"/>
+      <c r="D83" s="82"/>
+      <c r="E83" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F83" s="75"/>
-      <c r="G83" s="75"/>
-      <c r="H83" s="75"/>
+      <c r="F83" s="82"/>
+      <c r="G83" s="82"/>
+      <c r="H83" s="82"/>
     </row>
     <row r="84">
-      <c r="A84" s="73" t="s">
+      <c r="A84" s="80" t="s">
         <v>288</v>
       </c>
-      <c r="B84" s="73" t="s">
+      <c r="B84" s="80" t="s">
         <v>289</v>
       </c>
-      <c r="C84" s="75"/>
-      <c r="D84" s="75"/>
-      <c r="E84" s="75" t="str">
+      <c r="C84" s="82"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F84" s="75"/>
-      <c r="G84" s="75"/>
-      <c r="H84" s="75"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="82"/>
     </row>
     <row r="85">
-      <c r="A85" s="73" t="s">
+      <c r="A85" s="80" t="s">
         <v>292</v>
       </c>
-      <c r="B85" s="73" t="s">
+      <c r="B85" s="80" t="s">
         <v>293</v>
       </c>
-      <c r="C85" s="75"/>
-      <c r="D85" s="75"/>
-      <c r="E85" s="75" t="str">
+      <c r="C85" s="82"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F85" s="75"/>
-      <c r="G85" s="75"/>
-      <c r="H85" s="75"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="82"/>
+      <c r="H85" s="82"/>
     </row>
     <row r="86">
-      <c r="A86" s="73" t="s">
+      <c r="A86" s="80" t="s">
         <v>294</v>
       </c>
-      <c r="B86" s="73" t="s">
+      <c r="B86" s="80" t="s">
         <v>295</v>
       </c>
-      <c r="C86" s="75"/>
-      <c r="D86" s="75"/>
-      <c r="E86" s="75" t="str">
+      <c r="C86" s="82"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F86" s="75"/>
-      <c r="G86" s="75"/>
-      <c r="H86" s="75"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
     </row>
     <row r="87">
-      <c r="A87" s="73" t="s">
+      <c r="A87" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="B87" s="73" t="s">
+      <c r="B87" s="80" t="s">
         <v>297</v>
       </c>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
-      <c r="E87" s="75" t="str">
+      <c r="C87" s="82"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F87" s="75"/>
-      <c r="G87" s="75"/>
-      <c r="H87" s="75"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="82"/>
+      <c r="H87" s="82"/>
     </row>
     <row r="88">
-      <c r="A88" s="73" t="s">
+      <c r="A88" s="80" t="s">
         <v>298</v>
       </c>
-      <c r="B88" s="73" t="s">
+      <c r="B88" s="80" t="s">
         <v>299</v>
       </c>
-      <c r="C88" s="75"/>
-      <c r="D88" s="75"/>
-      <c r="E88" s="75" t="str">
+      <c r="C88" s="82"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F88" s="75"/>
-      <c r="G88" s="75"/>
-      <c r="H88" s="75"/>
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
     </row>
     <row r="89">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="80" t="s">
         <v>300</v>
       </c>
-      <c r="B89" s="73" t="s">
+      <c r="B89" s="80" t="s">
         <v>301</v>
       </c>
-      <c r="C89" s="75"/>
-      <c r="D89" s="75"/>
-      <c r="E89" s="75" t="str">
+      <c r="C89" s="82"/>
+      <c r="D89" s="82"/>
+      <c r="E89" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F89" s="75"/>
-      <c r="G89" s="75"/>
-      <c r="H89" s="75"/>
+      <c r="F89" s="82"/>
+      <c r="G89" s="82"/>
+      <c r="H89" s="82"/>
     </row>
     <row r="90">
-      <c r="A90" s="73" t="s">
+      <c r="A90" s="80" t="s">
         <v>302</v>
       </c>
-      <c r="B90" s="73" t="s">
+      <c r="B90" s="80" t="s">
         <v>303</v>
       </c>
-      <c r="C90" s="75"/>
-      <c r="D90" s="75"/>
-      <c r="E90" s="75" t="str">
+      <c r="C90" s="82"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F90" s="75"/>
-      <c r="G90" s="75"/>
-      <c r="H90" s="75"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="82"/>
     </row>
     <row r="91">
-      <c r="A91" s="73" t="s">
+      <c r="A91" s="80" t="s">
         <v>304</v>
       </c>
-      <c r="B91" s="73" t="s">
+      <c r="B91" s="80" t="s">
         <v>305</v>
       </c>
-      <c r="C91" s="75"/>
-      <c r="D91" s="75"/>
-      <c r="E91" s="75" t="str">
+      <c r="C91" s="82"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F91" s="75"/>
-      <c r="G91" s="75"/>
-      <c r="H91" s="75"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="82"/>
     </row>
     <row r="92">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="80" t="s">
         <v>306</v>
       </c>
-      <c r="B92" s="73" t="s">
+      <c r="B92" s="80" t="s">
         <v>307</v>
       </c>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
-      <c r="E92" s="75" t="str">
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F92" s="75"/>
-      <c r="G92" s="75"/>
-      <c r="H92" s="75"/>
+      <c r="F92" s="82"/>
+      <c r="G92" s="82"/>
+      <c r="H92" s="82"/>
     </row>
     <row r="93">
-      <c r="A93" s="73" t="s">
+      <c r="A93" s="80" t="s">
         <v>308</v>
       </c>
-      <c r="B93" s="73" t="s">
+      <c r="B93" s="80" t="s">
         <v>309</v>
       </c>
-      <c r="C93" s="75"/>
-      <c r="D93" s="75"/>
-      <c r="E93" s="75" t="str">
+      <c r="C93" s="82"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F93" s="75"/>
-      <c r="G93" s="75"/>
-      <c r="H93" s="75"/>
+      <c r="F93" s="82"/>
+      <c r="G93" s="82"/>
+      <c r="H93" s="82"/>
     </row>
     <row r="94">
-      <c r="A94" s="73" t="s">
+      <c r="A94" s="80" t="s">
         <v>310</v>
       </c>
-      <c r="B94" s="73" t="s">
+      <c r="B94" s="80" t="s">
         <v>311</v>
       </c>
-      <c r="C94" s="75"/>
-      <c r="D94" s="75"/>
-      <c r="E94" s="75" t="str">
+      <c r="C94" s="82"/>
+      <c r="D94" s="82"/>
+      <c r="E94" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
+      <c r="F94" s="82"/>
+      <c r="G94" s="82"/>
+      <c r="H94" s="82"/>
     </row>
     <row r="95">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="80" t="s">
         <v>312</v>
       </c>
-      <c r="B95" s="73" t="s">
+      <c r="B95" s="80" t="s">
         <v>313</v>
       </c>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="75" t="str">
+      <c r="C95" s="82"/>
+      <c r="D95" s="82"/>
+      <c r="E95" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F95" s="75"/>
-      <c r="G95" s="75"/>
-      <c r="H95" s="75"/>
+      <c r="F95" s="82"/>
+      <c r="G95" s="82"/>
+      <c r="H95" s="82"/>
     </row>
     <row r="96">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="80" t="s">
         <v>314</v>
       </c>
-      <c r="B96" s="73" t="s">
+      <c r="B96" s="80" t="s">
         <v>315</v>
       </c>
-      <c r="C96" s="75"/>
-      <c r="D96" s="75"/>
-      <c r="E96" s="75" t="str">
+      <c r="C96" s="82"/>
+      <c r="D96" s="82"/>
+      <c r="E96" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F96" s="75"/>
-      <c r="G96" s="75"/>
-      <c r="H96" s="75"/>
+      <c r="F96" s="82"/>
+      <c r="G96" s="82"/>
+      <c r="H96" s="82"/>
     </row>
     <row r="97">
-      <c r="A97" s="73" t="s">
+      <c r="A97" s="80" t="s">
         <v>316</v>
       </c>
-      <c r="B97" s="73" t="s">
+      <c r="B97" s="80" t="s">
         <v>317</v>
       </c>
-      <c r="C97" s="75"/>
-      <c r="D97" s="75"/>
-      <c r="E97" s="75" t="str">
+      <c r="C97" s="82"/>
+      <c r="D97" s="82"/>
+      <c r="E97" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F97" s="75"/>
-      <c r="G97" s="75"/>
-      <c r="H97" s="75"/>
+      <c r="F97" s="82"/>
+      <c r="G97" s="82"/>
+      <c r="H97" s="82"/>
     </row>
     <row r="98">
-      <c r="A98" s="73" t="s">
+      <c r="A98" s="80" t="s">
         <v>318</v>
       </c>
-      <c r="B98" s="73" t="s">
+      <c r="B98" s="80" t="s">
         <v>319</v>
       </c>
-      <c r="C98" s="75"/>
-      <c r="D98" s="75"/>
-      <c r="E98" s="75" t="str">
+      <c r="C98" s="82"/>
+      <c r="D98" s="82"/>
+      <c r="E98" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F98" s="75"/>
-      <c r="G98" s="75"/>
-      <c r="H98" s="75"/>
+      <c r="F98" s="82"/>
+      <c r="G98" s="82"/>
+      <c r="H98" s="82"/>
     </row>
     <row r="99">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="80" t="s">
         <v>320</v>
       </c>
-      <c r="B99" s="73" t="s">
+      <c r="B99" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75" t="str">
+      <c r="C99" s="82"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="82"/>
+      <c r="H99" s="82"/>
     </row>
     <row r="100">
-      <c r="A100" s="73" t="s">
+      <c r="A100" s="80" t="s">
         <v>322</v>
       </c>
-      <c r="B100" s="73" t="s">
+      <c r="B100" s="80" t="s">
         <v>323</v>
       </c>
-      <c r="C100" s="75"/>
-      <c r="D100" s="75"/>
-      <c r="E100" s="75" t="str">
+      <c r="C100" s="82"/>
+      <c r="D100" s="82"/>
+      <c r="E100" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F100" s="75"/>
-      <c r="G100" s="75"/>
-      <c r="H100" s="75"/>
+      <c r="F100" s="82"/>
+      <c r="G100" s="82"/>
+      <c r="H100" s="82"/>
     </row>
     <row r="101">
-      <c r="A101" s="73" t="s">
+      <c r="A101" s="80" t="s">
         <v>324</v>
       </c>
-      <c r="B101" s="73" t="s">
+      <c r="B101" s="80" t="s">
         <v>325</v>
       </c>
-      <c r="C101" s="75"/>
-      <c r="D101" s="75"/>
-      <c r="E101" s="75" t="str">
+      <c r="C101" s="82"/>
+      <c r="D101" s="82"/>
+      <c r="E101" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F101" s="75"/>
-      <c r="G101" s="75"/>
-      <c r="H101" s="75"/>
+      <c r="F101" s="82"/>
+      <c r="G101" s="82"/>
+      <c r="H101" s="82"/>
     </row>
     <row r="102">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="80" t="s">
         <v>326</v>
       </c>
-      <c r="B102" s="73" t="s">
+      <c r="B102" s="80" t="s">
         <v>327</v>
       </c>
-      <c r="C102" s="75"/>
-      <c r="D102" s="75"/>
-      <c r="E102" s="75" t="str">
+      <c r="C102" s="82"/>
+      <c r="D102" s="82"/>
+      <c r="E102" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F102" s="75"/>
-      <c r="G102" s="75"/>
-      <c r="H102" s="75"/>
+      <c r="F102" s="82"/>
+      <c r="G102" s="82"/>
+      <c r="H102" s="82"/>
     </row>
     <row r="103">
-      <c r="A103" s="73" t="s">
+      <c r="A103" s="80" t="s">
         <v>328</v>
       </c>
-      <c r="B103" s="73" t="s">
+      <c r="B103" s="80" t="s">
         <v>329</v>
       </c>
-      <c r="C103" s="75"/>
-      <c r="D103" s="75"/>
-      <c r="E103" s="75" t="str">
+      <c r="C103" s="82"/>
+      <c r="D103" s="82"/>
+      <c r="E103" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F103" s="75"/>
-      <c r="G103" s="75"/>
-      <c r="H103" s="75"/>
+      <c r="F103" s="82"/>
+      <c r="G103" s="82"/>
+      <c r="H103" s="82"/>
     </row>
     <row r="104">
-      <c r="A104" s="73" t="s">
+      <c r="A104" s="80" t="s">
         <v>330</v>
       </c>
-      <c r="B104" s="73" t="s">
+      <c r="B104" s="80" t="s">
         <v>331</v>
       </c>
-      <c r="C104" s="75"/>
-      <c r="D104" s="75"/>
-      <c r="E104" s="75" t="str">
+      <c r="C104" s="82"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F104" s="75"/>
-      <c r="G104" s="75"/>
-      <c r="H104" s="75"/>
+      <c r="F104" s="82"/>
+      <c r="G104" s="82"/>
+      <c r="H104" s="82"/>
     </row>
     <row r="105">
-      <c r="A105" s="73" t="s">
+      <c r="A105" s="80" t="s">
         <v>332</v>
       </c>
-      <c r="B105" s="73" t="s">
+      <c r="B105" s="80" t="s">
         <v>333</v>
       </c>
-      <c r="C105" s="75"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="75" t="str">
+      <c r="C105" s="82"/>
+      <c r="D105" s="82"/>
+      <c r="E105" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F105" s="75"/>
-      <c r="G105" s="75"/>
-      <c r="H105" s="75"/>
+      <c r="F105" s="82"/>
+      <c r="G105" s="82"/>
+      <c r="H105" s="82"/>
     </row>
     <row r="106">
-      <c r="A106" s="73" t="s">
+      <c r="A106" s="80" t="s">
         <v>334</v>
       </c>
-      <c r="B106" s="73" t="s">
+      <c r="B106" s="80" t="s">
         <v>335</v>
       </c>
-      <c r="C106" s="75"/>
-      <c r="D106" s="75"/>
-      <c r="E106" s="75" t="str">
+      <c r="C106" s="82"/>
+      <c r="D106" s="82"/>
+      <c r="E106" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F106" s="75"/>
-      <c r="G106" s="75"/>
-      <c r="H106" s="75"/>
+      <c r="F106" s="82"/>
+      <c r="G106" s="82"/>
+      <c r="H106" s="82"/>
     </row>
     <row r="107">
-      <c r="A107" s="73" t="s">
+      <c r="A107" s="80" t="s">
         <v>336</v>
       </c>
-      <c r="B107" s="73" t="s">
+      <c r="B107" s="80" t="s">
         <v>337</v>
       </c>
-      <c r="C107" s="75"/>
-      <c r="D107" s="75"/>
-      <c r="E107" s="75" t="str">
+      <c r="C107" s="82"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F107" s="75"/>
-      <c r="G107" s="75"/>
-      <c r="H107" s="75"/>
+      <c r="F107" s="82"/>
+      <c r="G107" s="82"/>
+      <c r="H107" s="82"/>
     </row>
     <row r="108">
-      <c r="A108" s="73" t="s">
+      <c r="A108" s="80" t="s">
         <v>338</v>
       </c>
-      <c r="B108" s="73" t="s">
+      <c r="B108" s="80" t="s">
         <v>339</v>
       </c>
-      <c r="C108" s="75"/>
-      <c r="D108" s="75"/>
-      <c r="E108" s="75" t="str">
+      <c r="C108" s="82"/>
+      <c r="D108" s="82"/>
+      <c r="E108" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F108" s="75"/>
-      <c r="G108" s="75"/>
-      <c r="H108" s="75"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="82"/>
+      <c r="H108" s="82"/>
     </row>
     <row r="109">
-      <c r="A109" s="73" t="s">
+      <c r="A109" s="80" t="s">
         <v>340</v>
       </c>
-      <c r="B109" s="73" t="s">
+      <c r="B109" s="80" t="s">
         <v>341</v>
       </c>
-      <c r="C109" s="75"/>
-      <c r="D109" s="75"/>
-      <c r="E109" s="75" t="str">
+      <c r="C109" s="82"/>
+      <c r="D109" s="82"/>
+      <c r="E109" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F109" s="75"/>
-      <c r="G109" s="75"/>
-      <c r="H109" s="75"/>
+      <c r="F109" s="82"/>
+      <c r="G109" s="82"/>
+      <c r="H109" s="82"/>
     </row>
     <row r="110">
-      <c r="A110" s="73" t="s">
+      <c r="A110" s="80" t="s">
         <v>342</v>
       </c>
-      <c r="B110" s="73" t="s">
+      <c r="B110" s="80" t="s">
         <v>343</v>
       </c>
-      <c r="C110" s="75"/>
-      <c r="D110" s="75"/>
-      <c r="E110" s="75" t="str">
+      <c r="C110" s="82"/>
+      <c r="D110" s="82"/>
+      <c r="E110" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F110" s="75"/>
-      <c r="G110" s="75"/>
-      <c r="H110" s="75"/>
+      <c r="F110" s="82"/>
+      <c r="G110" s="82"/>
+      <c r="H110" s="82"/>
     </row>
     <row r="111">
-      <c r="A111" s="73" t="s">
+      <c r="A111" s="80" t="s">
         <v>344</v>
       </c>
-      <c r="B111" s="73" t="s">
+      <c r="B111" s="80" t="s">
         <v>345</v>
       </c>
-      <c r="C111" s="75"/>
-      <c r="D111" s="75"/>
-      <c r="E111" s="75" t="str">
+      <c r="C111" s="82"/>
+      <c r="D111" s="82"/>
+      <c r="E111" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F111" s="75"/>
-      <c r="G111" s="75"/>
-      <c r="H111" s="75"/>
+      <c r="F111" s="82"/>
+      <c r="G111" s="82"/>
+      <c r="H111" s="82"/>
     </row>
     <row r="112">
-      <c r="A112" s="73" t="s">
+      <c r="A112" s="80" t="s">
         <v>346</v>
       </c>
-      <c r="B112" s="73" t="s">
+      <c r="B112" s="80" t="s">
         <v>347</v>
       </c>
-      <c r="C112" s="75"/>
-      <c r="D112" s="75"/>
-      <c r="E112" s="75" t="str">
+      <c r="C112" s="82"/>
+      <c r="D112" s="82"/>
+      <c r="E112" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F112" s="75"/>
-      <c r="G112" s="75"/>
-      <c r="H112" s="75"/>
+      <c r="F112" s="82"/>
+      <c r="G112" s="82"/>
+      <c r="H112" s="82"/>
     </row>
     <row r="113">
-      <c r="A113" s="73" t="s">
+      <c r="A113" s="80" t="s">
         <v>348</v>
       </c>
-      <c r="B113" s="73" t="s">
+      <c r="B113" s="80" t="s">
         <v>349</v>
       </c>
-      <c r="C113" s="75"/>
-      <c r="D113" s="75"/>
-      <c r="E113" s="75" t="str">
+      <c r="C113" s="82"/>
+      <c r="D113" s="82"/>
+      <c r="E113" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F113" s="75"/>
-      <c r="G113" s="75"/>
-      <c r="H113" s="75"/>
+      <c r="F113" s="82"/>
+      <c r="G113" s="82"/>
+      <c r="H113" s="82"/>
     </row>
     <row r="114">
-      <c r="A114" s="73" t="s">
+      <c r="A114" s="80" t="s">
         <v>350</v>
       </c>
-      <c r="B114" s="73" t="s">
+      <c r="B114" s="80" t="s">
         <v>351</v>
       </c>
-      <c r="C114" s="75"/>
-      <c r="D114" s="75"/>
-      <c r="E114" s="75" t="str">
+      <c r="C114" s="82"/>
+      <c r="D114" s="82"/>
+      <c r="E114" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F114" s="75"/>
-      <c r="G114" s="75"/>
-      <c r="H114" s="75"/>
+      <c r="F114" s="82"/>
+      <c r="G114" s="82"/>
+      <c r="H114" s="82"/>
     </row>
     <row r="115">
-      <c r="A115" s="73" t="s">
+      <c r="A115" s="80" t="s">
         <v>352</v>
       </c>
-      <c r="B115" s="73" t="s">
+      <c r="B115" s="80" t="s">
         <v>353</v>
       </c>
-      <c r="C115" s="75"/>
-      <c r="D115" s="75"/>
-      <c r="E115" s="75" t="str">
+      <c r="C115" s="82"/>
+      <c r="D115" s="82"/>
+      <c r="E115" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F115" s="75"/>
-      <c r="G115" s="75"/>
-      <c r="H115" s="75"/>
+      <c r="F115" s="82"/>
+      <c r="G115" s="82"/>
+      <c r="H115" s="82"/>
     </row>
     <row r="116">
-      <c r="A116" s="73" t="s">
+      <c r="A116" s="80" t="s">
         <v>354</v>
       </c>
-      <c r="B116" s="73" t="s">
+      <c r="B116" s="80" t="s">
         <v>355</v>
       </c>
-      <c r="C116" s="75"/>
-      <c r="D116" s="75"/>
-      <c r="E116" s="75" t="str">
+      <c r="C116" s="82"/>
+      <c r="D116" s="82"/>
+      <c r="E116" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F116" s="75"/>
-      <c r="G116" s="75"/>
-      <c r="H116" s="75"/>
+      <c r="F116" s="82"/>
+      <c r="G116" s="82"/>
+      <c r="H116" s="82"/>
     </row>
     <row r="117">
-      <c r="A117" s="73" t="s">
+      <c r="A117" s="80" t="s">
         <v>356</v>
       </c>
-      <c r="B117" s="73" t="s">
+      <c r="B117" s="80" t="s">
         <v>357</v>
       </c>
-      <c r="C117" s="75"/>
-      <c r="D117" s="75"/>
-      <c r="E117" s="75" t="str">
+      <c r="C117" s="82"/>
+      <c r="D117" s="82"/>
+      <c r="E117" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F117" s="75"/>
-      <c r="G117" s="75"/>
-      <c r="H117" s="75"/>
+      <c r="F117" s="82"/>
+      <c r="G117" s="82"/>
+      <c r="H117" s="82"/>
     </row>
     <row r="118">
-      <c r="A118" s="73" t="s">
+      <c r="A118" s="80" t="s">
         <v>358</v>
       </c>
-      <c r="B118" s="73" t="s">
+      <c r="B118" s="80" t="s">
         <v>359</v>
       </c>
-      <c r="C118" s="75"/>
-      <c r="D118" s="75"/>
-      <c r="E118" s="75" t="str">
+      <c r="C118" s="82"/>
+      <c r="D118" s="82"/>
+      <c r="E118" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F118" s="75"/>
-      <c r="G118" s="75"/>
-      <c r="H118" s="75"/>
+      <c r="F118" s="82"/>
+      <c r="G118" s="82"/>
+      <c r="H118" s="82"/>
     </row>
     <row r="119">
-      <c r="A119" s="73" t="s">
+      <c r="A119" s="80" t="s">
         <v>360</v>
       </c>
-      <c r="B119" s="73" t="s">
+      <c r="B119" s="80" t="s">
         <v>361</v>
       </c>
-      <c r="C119" s="75"/>
-      <c r="D119" s="75"/>
-      <c r="E119" s="75" t="str">
+      <c r="C119" s="82"/>
+      <c r="D119" s="82"/>
+      <c r="E119" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F119" s="75"/>
-      <c r="G119" s="75"/>
-      <c r="H119" s="75"/>
+      <c r="F119" s="82"/>
+      <c r="G119" s="82"/>
+      <c r="H119" s="82"/>
     </row>
     <row r="120">
-      <c r="A120" s="73" t="s">
+      <c r="A120" s="80" t="s">
         <v>362</v>
       </c>
-      <c r="B120" s="73" t="s">
+      <c r="B120" s="80" t="s">
         <v>363</v>
       </c>
-      <c r="C120" s="75"/>
-      <c r="D120" s="75"/>
-      <c r="E120" s="75" t="str">
+      <c r="C120" s="82"/>
+      <c r="D120" s="82"/>
+      <c r="E120" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F120" s="75"/>
-      <c r="G120" s="75"/>
-      <c r="H120" s="75"/>
+      <c r="F120" s="82"/>
+      <c r="G120" s="82"/>
+      <c r="H120" s="82"/>
     </row>
     <row r="121">
-      <c r="A121" s="73" t="s">
+      <c r="A121" s="80" t="s">
         <v>364</v>
       </c>
-      <c r="B121" s="73" t="s">
+      <c r="B121" s="80" t="s">
         <v>365</v>
       </c>
-      <c r="C121" s="75"/>
-      <c r="D121" s="75"/>
-      <c r="E121" s="75" t="str">
+      <c r="C121" s="82"/>
+      <c r="D121" s="82"/>
+      <c r="E121" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F121" s="75"/>
-      <c r="G121" s="75"/>
-      <c r="H121" s="75"/>
+      <c r="F121" s="82"/>
+      <c r="G121" s="82"/>
+      <c r="H121" s="82"/>
     </row>
     <row r="122">
-      <c r="A122" s="73" t="s">
+      <c r="A122" s="80" t="s">
         <v>366</v>
       </c>
-      <c r="B122" s="73" t="s">
+      <c r="B122" s="80" t="s">
         <v>367</v>
       </c>
-      <c r="C122" s="75"/>
-      <c r="D122" s="75"/>
-      <c r="E122" s="75" t="str">
+      <c r="C122" s="82"/>
+      <c r="D122" s="82"/>
+      <c r="E122" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F122" s="75"/>
-      <c r="G122" s="75"/>
-      <c r="H122" s="75"/>
+      <c r="F122" s="82"/>
+      <c r="G122" s="82"/>
+      <c r="H122" s="82"/>
     </row>
     <row r="123">
-      <c r="A123" s="73" t="s">
+      <c r="A123" s="80" t="s">
         <v>368</v>
       </c>
-      <c r="B123" s="73" t="s">
+      <c r="B123" s="80" t="s">
         <v>369</v>
       </c>
-      <c r="C123" s="75"/>
-      <c r="D123" s="75"/>
-      <c r="E123" s="75" t="str">
+      <c r="C123" s="82"/>
+      <c r="D123" s="82"/>
+      <c r="E123" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F123" s="75"/>
-      <c r="G123" s="75"/>
-      <c r="H123" s="75"/>
+      <c r="F123" s="82"/>
+      <c r="G123" s="82"/>
+      <c r="H123" s="82"/>
     </row>
     <row r="124">
-      <c r="A124" s="73" t="s">
+      <c r="A124" s="80" t="s">
         <v>370</v>
       </c>
-      <c r="B124" s="73" t="s">
+      <c r="B124" s="80" t="s">
         <v>371</v>
       </c>
-      <c r="C124" s="75"/>
-      <c r="D124" s="75"/>
-      <c r="E124" s="75" t="str">
+      <c r="C124" s="82"/>
+      <c r="D124" s="82"/>
+      <c r="E124" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F124" s="75"/>
-      <c r="G124" s="75"/>
-      <c r="H124" s="75"/>
+      <c r="F124" s="82"/>
+      <c r="G124" s="82"/>
+      <c r="H124" s="82"/>
     </row>
     <row r="125">
-      <c r="A125" s="73" t="s">
+      <c r="A125" s="80" t="s">
         <v>372</v>
       </c>
-      <c r="B125" s="73" t="s">
+      <c r="B125" s="80" t="s">
         <v>373</v>
       </c>
-      <c r="C125" s="75"/>
-      <c r="D125" s="75"/>
-      <c r="E125" s="75" t="str">
+      <c r="C125" s="82"/>
+      <c r="D125" s="82"/>
+      <c r="E125" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F125" s="75"/>
-      <c r="G125" s="75"/>
-      <c r="H125" s="75"/>
+      <c r="F125" s="82"/>
+      <c r="G125" s="82"/>
+      <c r="H125" s="82"/>
     </row>
     <row r="126">
-      <c r="A126" s="73" t="s">
+      <c r="A126" s="80" t="s">
         <v>374</v>
       </c>
-      <c r="B126" s="73" t="s">
+      <c r="B126" s="80" t="s">
         <v>375</v>
       </c>
-      <c r="C126" s="75"/>
-      <c r="D126" s="75"/>
-      <c r="E126" s="75" t="str">
+      <c r="C126" s="82"/>
+      <c r="D126" s="82"/>
+      <c r="E126" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F126" s="75"/>
-      <c r="G126" s="75"/>
-      <c r="H126" s="75"/>
+      <c r="F126" s="82"/>
+      <c r="G126" s="82"/>
+      <c r="H126" s="82"/>
     </row>
     <row r="127">
-      <c r="A127" s="73" t="s">
+      <c r="A127" s="80" t="s">
         <v>376</v>
       </c>
-      <c r="B127" s="73" t="s">
+      <c r="B127" s="80" t="s">
         <v>377</v>
       </c>
-      <c r="C127" s="75"/>
-      <c r="D127" s="75"/>
-      <c r="E127" s="75" t="str">
+      <c r="C127" s="82"/>
+      <c r="D127" s="82"/>
+      <c r="E127" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F127" s="75"/>
-      <c r="G127" s="75"/>
-      <c r="H127" s="75"/>
+      <c r="F127" s="82"/>
+      <c r="G127" s="82"/>
+      <c r="H127" s="82"/>
     </row>
     <row r="128">
-      <c r="A128" s="73" t="s">
+      <c r="A128" s="80" t="s">
         <v>378</v>
       </c>
-      <c r="B128" s="73" t="s">
+      <c r="B128" s="80" t="s">
         <v>379</v>
       </c>
-      <c r="C128" s="75"/>
-      <c r="D128" s="75"/>
-      <c r="E128" s="75" t="str">
+      <c r="C128" s="82"/>
+      <c r="D128" s="82"/>
+      <c r="E128" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F128" s="75"/>
-      <c r="G128" s="75"/>
-      <c r="H128" s="75"/>
+      <c r="F128" s="82"/>
+      <c r="G128" s="82"/>
+      <c r="H128" s="82"/>
     </row>
     <row r="129">
-      <c r="A129" s="73" t="s">
+      <c r="A129" s="80" t="s">
         <v>380</v>
       </c>
-      <c r="B129" s="73" t="s">
+      <c r="B129" s="80" t="s">
         <v>381</v>
       </c>
-      <c r="C129" s="75"/>
-      <c r="D129" s="75"/>
-      <c r="E129" s="75" t="str">
+      <c r="C129" s="82"/>
+      <c r="D129" s="82"/>
+      <c r="E129" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F129" s="75"/>
-      <c r="G129" s="74"/>
-      <c r="H129" s="74"/>
+      <c r="F129" s="82"/>
+      <c r="G129" s="81"/>
+      <c r="H129" s="81"/>
     </row>
     <row r="130">
-      <c r="A130" s="73" t="s">
+      <c r="A130" s="80" t="s">
         <v>382</v>
       </c>
-      <c r="B130" s="73" t="s">
+      <c r="B130" s="80" t="s">
         <v>383</v>
       </c>
-      <c r="C130" s="75"/>
-      <c r="D130" s="75"/>
-      <c r="E130" s="75" t="str">
+      <c r="C130" s="82"/>
+      <c r="D130" s="82"/>
+      <c r="E130" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F130" s="75"/>
-      <c r="G130" s="74"/>
-      <c r="H130" s="74"/>
+      <c r="F130" s="82"/>
+      <c r="G130" s="81"/>
+      <c r="H130" s="81"/>
     </row>
     <row r="131">
-      <c r="A131" s="73" t="s">
+      <c r="A131" s="80" t="s">
         <v>384</v>
       </c>
-      <c r="B131" s="73" t="s">
+      <c r="B131" s="80" t="s">
         <v>385</v>
       </c>
-      <c r="C131" s="75"/>
-      <c r="D131" s="75"/>
-      <c r="E131" s="75" t="str">
+      <c r="C131" s="82"/>
+      <c r="D131" s="82"/>
+      <c r="E131" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F131" s="75"/>
-      <c r="G131" s="74"/>
-      <c r="H131" s="74"/>
+      <c r="F131" s="82"/>
+      <c r="G131" s="81"/>
+      <c r="H131" s="81"/>
     </row>
     <row r="132">
-      <c r="A132" s="73" t="s">
+      <c r="A132" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="B132" s="73" t="s">
+      <c r="B132" s="80" t="s">
         <v>387</v>
       </c>
-      <c r="C132" s="75"/>
-      <c r="D132" s="75"/>
-      <c r="E132" s="75" t="str">
+      <c r="C132" s="82"/>
+      <c r="D132" s="82"/>
+      <c r="E132" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F132" s="75"/>
-      <c r="G132" s="74"/>
-      <c r="H132" s="74"/>
+      <c r="F132" s="82"/>
+      <c r="G132" s="81"/>
+      <c r="H132" s="81"/>
     </row>
     <row r="133">
-      <c r="A133" s="73" t="s">
+      <c r="A133" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B133" s="73" t="s">
+      <c r="B133" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="C133" s="75"/>
-      <c r="D133" s="75"/>
-      <c r="E133" s="75" t="str">
+      <c r="C133" s="82"/>
+      <c r="D133" s="82"/>
+      <c r="E133" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F133" s="75"/>
-      <c r="G133" s="74"/>
-      <c r="H133" s="74"/>
+      <c r="F133" s="82"/>
+      <c r="G133" s="81"/>
+      <c r="H133" s="81"/>
     </row>
     <row r="134">
-      <c r="A134" s="73" t="s">
+      <c r="A134" s="80" t="s">
         <v>390</v>
       </c>
-      <c r="B134" s="73" t="s">
+      <c r="B134" s="80" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="75"/>
-      <c r="D134" s="75"/>
-      <c r="E134" s="75" t="str">
+      <c r="C134" s="82"/>
+      <c r="D134" s="82"/>
+      <c r="E134" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F134" s="75"/>
-      <c r="G134" s="75"/>
-      <c r="H134" s="75"/>
+      <c r="F134" s="82"/>
+      <c r="G134" s="82"/>
+      <c r="H134" s="82"/>
     </row>
     <row r="135">
-      <c r="A135" s="73" t="s">
+      <c r="A135" s="80" t="s">
         <v>392</v>
       </c>
-      <c r="B135" s="73" t="s">
+      <c r="B135" s="80" t="s">
         <v>393</v>
       </c>
-      <c r="C135" s="75"/>
-      <c r="D135" s="75"/>
-      <c r="E135" s="75" t="str">
+      <c r="C135" s="82"/>
+      <c r="D135" s="82"/>
+      <c r="E135" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F135" s="75"/>
-      <c r="G135" s="75"/>
-      <c r="H135" s="75"/>
+      <c r="F135" s="82"/>
+      <c r="G135" s="82"/>
+      <c r="H135" s="82"/>
     </row>
     <row r="136">
-      <c r="A136" s="73" t="s">
+      <c r="A136" s="80" t="s">
         <v>396</v>
       </c>
-      <c r="B136" s="73" t="s">
+      <c r="B136" s="80" t="s">
         <v>397</v>
       </c>
-      <c r="C136" s="75"/>
-      <c r="D136" s="75"/>
-      <c r="E136" s="75" t="str">
+      <c r="C136" s="82"/>
+      <c r="D136" s="82"/>
+      <c r="E136" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F136" s="75"/>
-      <c r="G136" s="75"/>
-      <c r="H136" s="75"/>
+      <c r="F136" s="82"/>
+      <c r="G136" s="82"/>
+      <c r="H136" s="82"/>
     </row>
     <row r="137">
-      <c r="A137" s="73" t="s">
+      <c r="A137" s="80" t="s">
         <v>398</v>
       </c>
-      <c r="B137" s="73" t="s">
+      <c r="B137" s="80" t="s">
         <v>399</v>
       </c>
-      <c r="C137" s="75"/>
-      <c r="D137" s="75"/>
-      <c r="E137" s="75" t="str">
+      <c r="C137" s="82"/>
+      <c r="D137" s="82"/>
+      <c r="E137" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F137" s="75"/>
-      <c r="G137" s="75"/>
-      <c r="H137" s="75"/>
+      <c r="F137" s="82"/>
+      <c r="G137" s="82"/>
+      <c r="H137" s="82"/>
     </row>
     <row r="138">
-      <c r="A138" s="73" t="s">
+      <c r="A138" s="80" t="s">
         <v>400</v>
       </c>
-      <c r="B138" s="73" t="s">
+      <c r="B138" s="80" t="s">
         <v>401</v>
       </c>
-      <c r="C138" s="75"/>
-      <c r="D138" s="75"/>
-      <c r="E138" s="75" t="str">
+      <c r="C138" s="82"/>
+      <c r="D138" s="82"/>
+      <c r="E138" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F138" s="75"/>
-      <c r="G138" s="75"/>
-      <c r="H138" s="75"/>
+      <c r="F138" s="82"/>
+      <c r="G138" s="82"/>
+      <c r="H138" s="82"/>
     </row>
     <row r="139">
-      <c r="A139" s="73" t="s">
+      <c r="A139" s="80" t="s">
         <v>402</v>
       </c>
-      <c r="B139" s="73" t="s">
+      <c r="B139" s="80" t="s">
         <v>403</v>
       </c>
-      <c r="C139" s="75"/>
-      <c r="D139" s="75"/>
-      <c r="E139" s="75" t="str">
+      <c r="C139" s="82"/>
+      <c r="D139" s="82"/>
+      <c r="E139" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F139" s="75"/>
-      <c r="G139" s="75"/>
-      <c r="H139" s="75"/>
+      <c r="F139" s="82"/>
+      <c r="G139" s="82"/>
+      <c r="H139" s="82"/>
     </row>
     <row r="140">
-      <c r="A140" s="73" t="s">
+      <c r="A140" s="80" t="s">
         <v>404</v>
       </c>
-      <c r="B140" s="73" t="s">
+      <c r="B140" s="80" t="s">
         <v>405</v>
       </c>
-      <c r="C140" s="75"/>
-      <c r="D140" s="75"/>
-      <c r="E140" s="75" t="str">
+      <c r="C140" s="82"/>
+      <c r="D140" s="82"/>
+      <c r="E140" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F140" s="75"/>
-      <c r="G140" s="75"/>
-      <c r="H140" s="75"/>
+      <c r="F140" s="82"/>
+      <c r="G140" s="82"/>
+      <c r="H140" s="82"/>
     </row>
     <row r="141">
-      <c r="A141" s="73" t="s">
+      <c r="A141" s="80" t="s">
         <v>406</v>
       </c>
-      <c r="B141" s="73" t="s">
+      <c r="B141" s="80" t="s">
         <v>407</v>
       </c>
-      <c r="C141" s="75"/>
-      <c r="D141" s="75"/>
-      <c r="E141" s="75" t="str">
+      <c r="C141" s="82"/>
+      <c r="D141" s="82"/>
+      <c r="E141" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F141" s="75"/>
-      <c r="G141" s="75"/>
-      <c r="H141" s="75"/>
+      <c r="F141" s="82"/>
+      <c r="G141" s="82"/>
+      <c r="H141" s="82"/>
     </row>
     <row r="142">
-      <c r="A142" s="73" t="s">
+      <c r="A142" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="B142" s="73" t="s">
+      <c r="B142" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C142" s="75"/>
-      <c r="D142" s="75"/>
-      <c r="E142" s="75" t="str">
+      <c r="C142" s="82"/>
+      <c r="D142" s="82"/>
+      <c r="E142" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F142" s="75"/>
-      <c r="G142" s="75"/>
-      <c r="H142" s="75"/>
+      <c r="F142" s="82"/>
+      <c r="G142" s="82"/>
+      <c r="H142" s="82"/>
     </row>
     <row r="143">
-      <c r="A143" s="73" t="s">
+      <c r="A143" s="80" t="s">
         <v>412</v>
       </c>
-      <c r="B143" s="73" t="s">
+      <c r="B143" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="C143" s="75"/>
-      <c r="D143" s="75"/>
-      <c r="E143" s="75" t="str">
+      <c r="C143" s="82"/>
+      <c r="D143" s="82"/>
+      <c r="E143" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F143" s="75"/>
-      <c r="G143" s="75"/>
-      <c r="H143" s="75"/>
+      <c r="F143" s="82"/>
+      <c r="G143" s="82"/>
+      <c r="H143" s="82"/>
     </row>
     <row r="144">
-      <c r="A144" s="73" t="s">
+      <c r="A144" s="80" t="s">
         <v>416</v>
       </c>
-      <c r="B144" s="73" t="s">
+      <c r="B144" s="80" t="s">
         <v>417</v>
       </c>
-      <c r="C144" s="75"/>
-      <c r="D144" s="75"/>
-      <c r="E144" s="75" t="str">
+      <c r="C144" s="82"/>
+      <c r="D144" s="82"/>
+      <c r="E144" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F144" s="75"/>
-      <c r="G144" s="75"/>
-      <c r="H144" s="75"/>
+      <c r="F144" s="82"/>
+      <c r="G144" s="82"/>
+      <c r="H144" s="82"/>
     </row>
     <row r="145">
-      <c r="A145" s="73" t="s">
+      <c r="A145" s="80" t="s">
         <v>835</v>
       </c>
-      <c r="B145" s="73" t="s">
+      <c r="B145" s="80" t="s">
         <v>436</v>
       </c>
-      <c r="C145" s="75"/>
-      <c r="D145" s="75"/>
-      <c r="E145" s="75" t="str">
+      <c r="C145" s="82"/>
+      <c r="D145" s="82"/>
+      <c r="E145" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F145" s="75"/>
-      <c r="G145" s="75"/>
-      <c r="H145" s="75"/>
+      <c r="F145" s="82"/>
+      <c r="G145" s="82"/>
+      <c r="H145" s="82"/>
     </row>
     <row r="146">
-      <c r="A146" s="73" t="s">
+      <c r="A146" s="80" t="s">
         <v>449</v>
       </c>
-      <c r="B146" s="73" t="s">
+      <c r="B146" s="80" t="s">
         <v>450</v>
       </c>
-      <c r="C146" s="75"/>
-      <c r="D146" s="75"/>
-      <c r="E146" s="75" t="str">
+      <c r="C146" s="82"/>
+      <c r="D146" s="82"/>
+      <c r="E146" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F146" s="75"/>
-      <c r="G146" s="75"/>
-      <c r="H146" s="75"/>
+      <c r="F146" s="82"/>
+      <c r="G146" s="82"/>
+      <c r="H146" s="82"/>
     </row>
     <row r="147">
-      <c r="A147" s="73" t="s">
+      <c r="A147" s="80" t="s">
         <v>455</v>
       </c>
-      <c r="B147" s="73" t="s">
+      <c r="B147" s="80" t="s">
         <v>456</v>
       </c>
-      <c r="C147" s="75"/>
-      <c r="D147" s="75"/>
-      <c r="E147" s="75" t="str">
+      <c r="C147" s="82"/>
+      <c r="D147" s="82"/>
+      <c r="E147" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F147" s="75"/>
-      <c r="G147" s="75"/>
-      <c r="H147" s="75"/>
+      <c r="F147" s="82"/>
+      <c r="G147" s="82"/>
+      <c r="H147" s="82"/>
     </row>
     <row r="148">
-      <c r="A148" s="73" t="s">
+      <c r="A148" s="80" t="s">
         <v>467</v>
       </c>
-      <c r="B148" s="73" t="s">
+      <c r="B148" s="80" t="s">
         <v>468</v>
       </c>
-      <c r="C148" s="75"/>
-      <c r="D148" s="75"/>
-      <c r="E148" s="75" t="str">
+      <c r="C148" s="82"/>
+      <c r="D148" s="82"/>
+      <c r="E148" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F148" s="75"/>
-      <c r="G148" s="75"/>
-      <c r="H148" s="75"/>
+      <c r="F148" s="82"/>
+      <c r="G148" s="82"/>
+      <c r="H148" s="82"/>
     </row>
     <row r="149">
-      <c r="A149" s="73" t="s">
+      <c r="A149" s="80" t="s">
         <v>475</v>
       </c>
-      <c r="B149" s="73" t="s">
+      <c r="B149" s="80" t="s">
         <v>476</v>
       </c>
-      <c r="C149" s="75"/>
-      <c r="D149" s="75"/>
-      <c r="E149" s="75" t="str">
+      <c r="C149" s="82"/>
+      <c r="D149" s="82"/>
+      <c r="E149" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F149" s="75"/>
-      <c r="G149" s="75"/>
-      <c r="H149" s="75"/>
+      <c r="F149" s="82"/>
+      <c r="G149" s="82"/>
+      <c r="H149" s="82"/>
     </row>
     <row r="150">
-      <c r="A150" s="73" t="s">
+      <c r="A150" s="80" t="s">
         <v>481</v>
       </c>
-      <c r="B150" s="73" t="s">
+      <c r="B150" s="80" t="s">
         <v>482</v>
       </c>
-      <c r="C150" s="75"/>
-      <c r="D150" s="75"/>
-      <c r="E150" s="75" t="str">
+      <c r="C150" s="82"/>
+      <c r="D150" s="82"/>
+      <c r="E150" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F150" s="75"/>
-      <c r="G150" s="75"/>
-      <c r="H150" s="75"/>
+      <c r="F150" s="82"/>
+      <c r="G150" s="82"/>
+      <c r="H150" s="82"/>
     </row>
     <row r="151">
-      <c r="A151" s="73" t="s">
+      <c r="A151" s="80" t="s">
         <v>487</v>
       </c>
-      <c r="B151" s="73" t="s">
+      <c r="B151" s="80" t="s">
         <v>488</v>
       </c>
-      <c r="C151" s="75"/>
-      <c r="D151" s="75"/>
-      <c r="E151" s="75" t="str">
+      <c r="C151" s="82"/>
+      <c r="D151" s="82"/>
+      <c r="E151" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F151" s="75"/>
-      <c r="G151" s="75"/>
-      <c r="H151" s="75"/>
+      <c r="F151" s="82"/>
+      <c r="G151" s="82"/>
+      <c r="H151" s="82"/>
     </row>
     <row r="152">
-      <c r="A152" s="73" t="s">
+      <c r="A152" s="80" t="s">
         <v>511</v>
       </c>
-      <c r="B152" s="73" t="s">
+      <c r="B152" s="80" t="s">
         <v>512</v>
       </c>
-      <c r="C152" s="75"/>
-      <c r="D152" s="75"/>
-      <c r="E152" s="75" t="str">
+      <c r="C152" s="82"/>
+      <c r="D152" s="82"/>
+      <c r="E152" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F152" s="75"/>
-      <c r="G152" s="75"/>
-      <c r="H152" s="75"/>
+      <c r="F152" s="82"/>
+      <c r="G152" s="82"/>
+      <c r="H152" s="82"/>
     </row>
     <row r="153">
-      <c r="A153" s="73" t="s">
+      <c r="A153" s="80" t="s">
         <v>513</v>
       </c>
-      <c r="B153" s="73" t="s">
+      <c r="B153" s="80" t="s">
         <v>514</v>
       </c>
-      <c r="C153" s="75"/>
-      <c r="D153" s="75"/>
-      <c r="E153" s="75" t="str">
+      <c r="C153" s="82"/>
+      <c r="D153" s="82"/>
+      <c r="E153" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F153" s="75"/>
-      <c r="G153" s="75"/>
-      <c r="H153" s="75"/>
+      <c r="F153" s="82"/>
+      <c r="G153" s="82"/>
+      <c r="H153" s="82"/>
     </row>
     <row r="154">
-      <c r="A154" s="73" t="s">
+      <c r="A154" s="80" t="s">
         <v>515</v>
       </c>
-      <c r="B154" s="73" t="s">
+      <c r="B154" s="80" t="s">
         <v>516</v>
       </c>
-      <c r="C154" s="75"/>
-      <c r="D154" s="75"/>
-      <c r="E154" s="75" t="str">
+      <c r="C154" s="82"/>
+      <c r="D154" s="82"/>
+      <c r="E154" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F154" s="75"/>
-      <c r="G154" s="75"/>
-      <c r="H154" s="75"/>
+      <c r="F154" s="82"/>
+      <c r="G154" s="82"/>
+      <c r="H154" s="82"/>
     </row>
     <row r="155">
-      <c r="A155" s="73" t="s">
+      <c r="A155" s="80" t="s">
         <v>517</v>
       </c>
-      <c r="B155" s="73" t="s">
+      <c r="B155" s="80" t="s">
         <v>518</v>
       </c>
-      <c r="C155" s="75"/>
-      <c r="D155" s="75"/>
-      <c r="E155" s="75" t="str">
+      <c r="C155" s="82"/>
+      <c r="D155" s="82"/>
+      <c r="E155" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F155" s="75"/>
-      <c r="G155" s="75"/>
-      <c r="H155" s="75"/>
+      <c r="F155" s="82"/>
+      <c r="G155" s="82"/>
+      <c r="H155" s="82"/>
     </row>
     <row r="156">
-      <c r="A156" s="73" t="s">
+      <c r="A156" s="80" t="s">
         <v>519</v>
       </c>
-      <c r="B156" s="73" t="s">
+      <c r="B156" s="80" t="s">
         <v>520</v>
       </c>
-      <c r="C156" s="75"/>
-      <c r="D156" s="75"/>
-      <c r="E156" s="75" t="str">
+      <c r="C156" s="82"/>
+      <c r="D156" s="82"/>
+      <c r="E156" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F156" s="75"/>
-      <c r="G156" s="75"/>
-      <c r="H156" s="75"/>
+      <c r="F156" s="82"/>
+      <c r="G156" s="82"/>
+      <c r="H156" s="82"/>
     </row>
     <row r="157">
-      <c r="A157" s="73" t="s">
+      <c r="A157" s="80" t="s">
         <v>521</v>
       </c>
-      <c r="B157" s="73" t="s">
+      <c r="B157" s="80" t="s">
         <v>522</v>
       </c>
-      <c r="C157" s="75"/>
-      <c r="D157" s="75"/>
-      <c r="E157" s="75" t="str">
+      <c r="C157" s="82"/>
+      <c r="D157" s="82"/>
+      <c r="E157" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F157" s="75"/>
-      <c r="G157" s="75"/>
-      <c r="H157" s="75"/>
+      <c r="F157" s="82"/>
+      <c r="G157" s="82"/>
+      <c r="H157" s="82"/>
     </row>
     <row r="158">
-      <c r="A158" s="73" t="s">
+      <c r="A158" s="80" t="s">
         <v>523</v>
       </c>
-      <c r="B158" s="73" t="s">
+      <c r="B158" s="80" t="s">
         <v>524</v>
       </c>
-      <c r="C158" s="75"/>
-      <c r="D158" s="75"/>
-      <c r="E158" s="75" t="str">
+      <c r="C158" s="82"/>
+      <c r="D158" s="82"/>
+      <c r="E158" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F158" s="75"/>
-      <c r="G158" s="75"/>
-      <c r="H158" s="75"/>
+      <c r="F158" s="82"/>
+      <c r="G158" s="82"/>
+      <c r="H158" s="82"/>
     </row>
     <row r="159">
-      <c r="A159" s="73" t="s">
+      <c r="A159" s="80" t="s">
         <v>525</v>
       </c>
-      <c r="B159" s="73" t="s">
+      <c r="B159" s="80" t="s">
         <v>526</v>
       </c>
-      <c r="C159" s="75"/>
-      <c r="D159" s="75"/>
-      <c r="E159" s="75" t="str">
+      <c r="C159" s="82"/>
+      <c r="D159" s="82"/>
+      <c r="E159" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F159" s="75"/>
-      <c r="G159" s="75"/>
-      <c r="H159" s="75"/>
+      <c r="F159" s="82"/>
+      <c r="G159" s="82"/>
+      <c r="H159" s="82"/>
     </row>
     <row r="160">
-      <c r="A160" s="73" t="s">
+      <c r="A160" s="80" t="s">
         <v>527</v>
       </c>
-      <c r="B160" s="73" t="s">
+      <c r="B160" s="80" t="s">
         <v>528</v>
       </c>
-      <c r="C160" s="75"/>
-      <c r="D160" s="75"/>
-      <c r="E160" s="75" t="str">
+      <c r="C160" s="82"/>
+      <c r="D160" s="82"/>
+      <c r="E160" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F160" s="75"/>
-      <c r="G160" s="75"/>
-      <c r="H160" s="75"/>
+      <c r="F160" s="82"/>
+      <c r="G160" s="82"/>
+      <c r="H160" s="82"/>
     </row>
     <row r="161">
-      <c r="A161" s="73" t="s">
+      <c r="A161" s="80" t="s">
         <v>529</v>
       </c>
-      <c r="B161" s="73" t="s">
+      <c r="B161" s="80" t="s">
         <v>530</v>
       </c>
-      <c r="C161" s="75"/>
-      <c r="D161" s="75"/>
-      <c r="E161" s="75" t="str">
+      <c r="C161" s="82"/>
+      <c r="D161" s="82"/>
+      <c r="E161" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F161" s="75"/>
-      <c r="G161" s="75"/>
-      <c r="H161" s="75"/>
+      <c r="F161" s="82"/>
+      <c r="G161" s="82"/>
+      <c r="H161" s="82"/>
     </row>
     <row r="162">
-      <c r="A162" s="73" t="s">
+      <c r="A162" s="80" t="s">
         <v>531</v>
       </c>
-      <c r="B162" s="73" t="s">
+      <c r="B162" s="80" t="s">
         <v>532</v>
       </c>
-      <c r="C162" s="75"/>
-      <c r="D162" s="75"/>
-      <c r="E162" s="75" t="str">
+      <c r="C162" s="82"/>
+      <c r="D162" s="82"/>
+      <c r="E162" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F162" s="75"/>
-      <c r="G162" s="75"/>
-      <c r="H162" s="75"/>
+      <c r="F162" s="82"/>
+      <c r="G162" s="82"/>
+      <c r="H162" s="82"/>
     </row>
     <row r="163">
-      <c r="A163" s="73" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B163" s="73" t="s">
+      <c r="A163" s="80" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B163" s="80" t="s">
         <v>534</v>
       </c>
-      <c r="C163" s="75"/>
-      <c r="D163" s="75"/>
-      <c r="E163" s="75" t="str">
+      <c r="C163" s="82"/>
+      <c r="D163" s="82"/>
+      <c r="E163" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F163" s="75"/>
-      <c r="G163" s="75"/>
-      <c r="H163" s="75"/>
+      <c r="F163" s="82"/>
+      <c r="G163" s="82"/>
+      <c r="H163" s="82"/>
     </row>
     <row r="164">
-      <c r="A164" s="73" t="s">
+      <c r="A164" s="80" t="s">
         <v>603</v>
       </c>
-      <c r="B164" s="73" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C164" s="75"/>
-      <c r="D164" s="75"/>
-      <c r="E164" s="75" t="str">
+      <c r="B164" s="80" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C164" s="82"/>
+      <c r="D164" s="82"/>
+      <c r="E164" s="82" t="str">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F164" s="75"/>
-      <c r="G164" s="75"/>
-      <c r="H164" s="75"/>
+      <c r="F164" s="82"/>
+      <c r="G164" s="82"/>
+      <c r="H164" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="1107">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1997,7 +1997,7 @@
     <t>price_distr</t>
   </si>
   <si>
-    <t>ACTUALIZAR</t>
+    <t>ACTUALIZADO</t>
   </si>
   <si>
     <t>CAMBIAR REFERENCIA</t>
@@ -3072,9 +3072,6 @@
   </si>
   <si>
     <t>BY-FBT05GCC</t>
-  </si>
-  <si>
-    <t>BY-FBT05C</t>
   </si>
   <si>
     <t>BY-FBT05VCC</t>
@@ -14239,18 +14236,18 @@
       <c r="A358" s="49" t="s">
         <v>1018</v>
       </c>
-      <c r="B358" s="52" t="s">
-        <v>1019</v>
+      <c r="B358" s="49" t="s">
+        <v>102</v>
       </c>
       <c r="C358" s="50" t="s">
-        <v>1019</v>
+        <v>102</v>
       </c>
       <c r="D358" s="51"/>
       <c r="E358" s="51"/>
     </row>
     <row r="359" ht="22.5" customHeight="1">
       <c r="A359" s="49" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B359" s="52" t="s">
         <v>106</v>
@@ -14263,7 +14260,7 @@
     </row>
     <row r="360" ht="22.5" customHeight="1">
       <c r="A360" s="49" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B360" s="52" t="s">
         <v>104</v>
@@ -14276,7 +14273,7 @@
     </row>
     <row r="361" ht="22.5" customHeight="1">
       <c r="A361" s="49" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B361" s="52" t="s">
         <v>78</v>
@@ -14289,10 +14286,10 @@
     </row>
     <row r="362" ht="22.5" customHeight="1">
       <c r="A362" s="49" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B362" s="49" t="s">
         <v>1023</v>
-      </c>
-      <c r="B362" s="49" t="s">
-        <v>1024</v>
       </c>
       <c r="C362" s="50"/>
       <c r="D362" s="51"/>
@@ -14300,10 +14297,10 @@
     </row>
     <row r="363" ht="22.5" customHeight="1">
       <c r="A363" s="49" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B363" s="49" t="s">
         <v>1025</v>
-      </c>
-      <c r="B363" s="49" t="s">
-        <v>1026</v>
       </c>
       <c r="C363" s="50"/>
       <c r="D363" s="51"/>
@@ -14614,7 +14611,7 @@
       <c r="A407" s="53"/>
       <c r="B407" s="54"/>
       <c r="C407" s="56" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D407" s="55"/>
       <c r="E407" s="55"/>
@@ -18788,78 +18785,78 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="57" t="s">
         <v>1029</v>
-      </c>
-      <c r="C1" s="57" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1031</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="57" t="s">
         <v>1032</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1034</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="57" t="s">
         <v>1035</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="E3" s="58" t="s">
         <v>1036</v>
-      </c>
-      <c r="E3" s="58" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="57" t="s">
         <v>1039</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>1040</v>
-      </c>
       <c r="E4" s="59" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C5" s="57" t="s">
         <v>1041</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>1042</v>
-      </c>
       <c r="E5" s="60" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="61"/>
       <c r="E6" s="62" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="61"/>
       <c r="E7" s="63" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8">
@@ -21864,24 +21861,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="64" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B1" s="64" t="s">
         <v>1043</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="C1" s="64" t="s">
         <v>1044</v>
-      </c>
-      <c r="C1" s="64" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="65" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B2" s="65" t="s">
         <v>770</v>
       </c>
       <c r="C2" s="65" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D2" s="66"/>
       <c r="E2" s="66"/>
@@ -21909,13 +21906,13 @@
     </row>
     <row r="3">
       <c r="A3" s="65" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B3" s="65" t="s">
         <v>766</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D3" s="66"/>
       <c r="E3" s="66"/>
@@ -21943,275 +21940,275 @@
     </row>
     <row r="4">
       <c r="A4" s="67" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B4" s="67" t="s">
         <v>745</v>
       </c>
       <c r="C4" s="67" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B5" s="67" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="67" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B6" s="67" t="s">
         <v>748</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B7" s="67" t="s">
         <v>50</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B8" s="67" t="s">
         <v>774</v>
       </c>
       <c r="C8" s="67" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B9" s="67" t="s">
         <v>780</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B10" s="67" t="s">
         <v>778</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B11" s="67" t="s">
         <v>775</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B12" s="67" t="s">
         <v>782</v>
       </c>
       <c r="C12" s="67" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B13" s="67" t="s">
         <v>785</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B14" s="67" t="s">
         <v>792</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B15" s="67" t="s">
         <v>789</v>
       </c>
       <c r="C15" s="67" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B16" s="67" t="s">
         <v>799</v>
       </c>
       <c r="C16" s="67" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B17" s="67" t="s">
         <v>802</v>
       </c>
       <c r="C17" s="67" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B18" s="67" t="s">
         <v>796</v>
       </c>
       <c r="C18" s="67" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B19" s="67" t="s">
         <v>798</v>
       </c>
       <c r="C19" s="67" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B20" s="67" t="s">
         <v>800</v>
       </c>
       <c r="C20" s="67" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B21" s="67" t="s">
         <v>797</v>
       </c>
       <c r="C21" s="67" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B22" s="67" t="s">
         <v>801</v>
       </c>
       <c r="C22" s="67" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B23" s="67" t="s">
         <v>1072</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="C23" s="67" t="s">
         <v>1073</v>
-      </c>
-      <c r="C23" s="67" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B24" s="67" t="s">
         <v>714</v>
       </c>
       <c r="C24" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B25" s="67" t="s">
         <v>1077</v>
       </c>
-      <c r="B25" s="67" t="s">
-        <v>1078</v>
-      </c>
       <c r="C25" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B26" s="67" t="s">
         <v>1079</v>
       </c>
-      <c r="B26" s="67" t="s">
-        <v>1080</v>
-      </c>
       <c r="C26" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B27" s="67" t="s">
         <v>715</v>
       </c>
       <c r="C27" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="68" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B28" s="69"/>
       <c r="C28" s="68" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D28" s="70"/>
       <c r="E28" s="70"/>
@@ -22239,11 +22236,11 @@
     </row>
     <row r="29">
       <c r="A29" s="71" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B29" s="72"/>
       <c r="C29" s="71" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D29" s="73"/>
       <c r="E29" s="73"/>
@@ -22271,11 +22268,11 @@
     </row>
     <row r="30">
       <c r="A30" s="71" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B30" s="72"/>
       <c r="C30" s="71" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D30" s="73"/>
       <c r="E30" s="73"/>
@@ -22303,11 +22300,11 @@
     </row>
     <row r="31">
       <c r="A31" s="71" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B31" s="72"/>
       <c r="C31" s="71" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D31" s="73"/>
       <c r="E31" s="73"/>
@@ -22335,11 +22332,11 @@
     </row>
     <row r="32">
       <c r="A32" s="71" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B32" s="72"/>
       <c r="C32" s="71" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D32" s="73"/>
       <c r="E32" s="73"/>
@@ -22367,11 +22364,11 @@
     </row>
     <row r="33">
       <c r="A33" s="68" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B33" s="69"/>
       <c r="C33" s="68" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D33" s="70"/>
       <c r="E33" s="70"/>
@@ -22399,102 +22396,102 @@
     </row>
     <row r="34">
       <c r="A34" s="67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B34" s="67" t="s">
         <v>819</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B35" s="67" t="s">
         <v>821</v>
       </c>
       <c r="C35" s="67" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B36" s="67" t="s">
         <v>823</v>
       </c>
       <c r="C36" s="67" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B37" s="67" t="s">
         <v>822</v>
       </c>
       <c r="C37" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B38" s="67" t="s">
         <v>820</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B39" s="74"/>
       <c r="C39" s="67" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B40" s="74"/>
       <c r="C40" s="67" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B41" s="74"/>
       <c r="C41" s="67" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B42" s="74"/>
       <c r="C42" s="67" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B43" s="69"/>
       <c r="C43" s="68" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D43" s="70"/>
       <c r="E43" s="70"/>
@@ -22522,11 +22519,11 @@
     </row>
     <row r="44">
       <c r="A44" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B44" s="69"/>
       <c r="C44" s="68" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D44" s="70"/>
       <c r="E44" s="70"/>
@@ -22554,11 +22551,11 @@
     </row>
     <row r="45">
       <c r="A45" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B45" s="69"/>
       <c r="C45" s="68" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D45" s="70"/>
       <c r="E45" s="70"/>
@@ -22586,11 +22583,11 @@
     </row>
     <row r="46">
       <c r="A46" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B46" s="69"/>
       <c r="C46" s="68" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D46" s="70"/>
       <c r="E46" s="70"/>
@@ -22618,11 +22615,11 @@
     </row>
     <row r="47">
       <c r="A47" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B47" s="69"/>
       <c r="C47" s="68" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D47" s="70"/>
       <c r="E47" s="70"/>
@@ -22650,11 +22647,11 @@
     </row>
     <row r="48">
       <c r="A48" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B48" s="69"/>
       <c r="C48" s="68" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D48" s="70"/>
       <c r="E48" s="70"/>
@@ -22682,11 +22679,11 @@
     </row>
     <row r="49">
       <c r="A49" s="68" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B49" s="69"/>
       <c r="C49" s="68" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D49" s="70"/>
       <c r="E49" s="70"/>
@@ -22738,12 +22735,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="76" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D1" s="77"/>
       <c r="E1" s="78"/>
       <c r="F1" s="76" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G1" s="77"/>
       <c r="H1" s="78"/>
@@ -22752,22 +22749,22 @@
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="80" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D2" s="80" t="s">
         <v>1100</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="E2" s="80" t="s">
         <v>1101</v>
       </c>
-      <c r="E2" s="80" t="s">
-        <v>1102</v>
-      </c>
       <c r="F2" s="80" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G2" s="80" t="s">
         <v>1100</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="H2" s="80" t="s">
         <v>1101</v>
-      </c>
-      <c r="H2" s="80" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="3">
@@ -22974,7 +22971,7 @@
     </row>
     <row r="13">
       <c r="A13" s="81" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B13" s="81" t="s">
         <v>39</v>
@@ -22995,7 +22992,7 @@
     </row>
     <row r="14">
       <c r="A14" s="81" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B14" s="81" t="s">
         <v>41</v>
@@ -23907,7 +23904,7 @@
         <v>793</v>
       </c>
       <c r="B63" s="81" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C63" s="83"/>
       <c r="D63" s="83"/>
@@ -25636,7 +25633,7 @@
     </row>
     <row r="163">
       <c r="A163" s="81" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B163" s="81" t="s">
         <v>534</v>
@@ -25656,7 +25653,7 @@
         <v>603</v>
       </c>
       <c r="B164" s="81" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C164" s="83"/>
       <c r="D164" s="83"/>
